--- a/artfynd/A 43533-2025 artfynd.xlsx
+++ b/artfynd/A 43533-2025 artfynd.xlsx
@@ -2921,48 +2921,62 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129131389</v>
+        <v>129127509</v>
       </c>
       <c r="B19" t="n">
-        <v>79034</v>
+        <v>92095</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>520611</v>
+        <v>520242</v>
       </c>
       <c r="R19" t="n">
-        <v>7001285</v>
+        <v>7001434</v>
       </c>
       <c r="S19" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2991,7 +3005,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3001,7 +3015,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3012,6 +3026,31 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Salix caprea</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -3028,62 +3067,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129127509</v>
+        <v>129131389</v>
       </c>
       <c r="B20" t="n">
-        <v>92095</v>
+        <v>79034</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>520242</v>
+        <v>520611</v>
       </c>
       <c r="R20" t="n">
-        <v>7001434</v>
+        <v>7001285</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3112,7 +3137,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3122,7 +3147,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3133,31 +3158,6 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Salix caprea</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -3784,10 +3784,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129131479</v>
+        <v>129127211</v>
       </c>
       <c r="B26" t="n">
-        <v>79034</v>
+        <v>80139</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3795,37 +3795,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>520712</v>
+        <v>520158</v>
       </c>
       <c r="R26" t="n">
-        <v>7001363</v>
+        <v>7001448</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3854,7 +3859,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3864,7 +3869,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3878,27 +3883,27 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3916,10 +3921,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129127211</v>
+        <v>129131479</v>
       </c>
       <c r="B27" t="n">
-        <v>80139</v>
+        <v>79034</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3927,42 +3932,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>520158</v>
+        <v>520712</v>
       </c>
       <c r="R27" t="n">
-        <v>7001448</v>
+        <v>7001363</v>
       </c>
       <c r="S27" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3991,7 +3991,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4001,7 +4001,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4015,27 +4015,27 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>

--- a/artfynd/A 43533-2025 artfynd.xlsx
+++ b/artfynd/A 43533-2025 artfynd.xlsx
@@ -675,47 +675,38 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129135545</v>
+        <v>129126527</v>
       </c>
       <c r="B2" t="n">
-        <v>98651</v>
+        <v>80139</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>520564</v>
+        <v>520189</v>
       </c>
       <c r="R2" t="n">
-        <v>7001441</v>
+        <v>7001448</v>
       </c>
       <c r="S2" t="n">
         <v>9</v>
@@ -759,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -783,7 +779,27 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -804,7 +820,7 @@
         <v>129135852</v>
       </c>
       <c r="B3" t="n">
-        <v>98985</v>
+        <v>98990</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,38 +934,47 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129126527</v>
+        <v>129135545</v>
       </c>
       <c r="B4" t="n">
-        <v>80139</v>
+        <v>98656</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -958,10 +983,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>520189</v>
+        <v>520564</v>
       </c>
       <c r="R4" t="n">
-        <v>7001448</v>
+        <v>7001441</v>
       </c>
       <c r="S4" t="n">
         <v>9</v>
@@ -993,7 +1018,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,12 +1028,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:12</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1022,27 +1042,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1182,7 +1182,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129131350</v>
+        <v>129127182</v>
       </c>
       <c r="B6" t="n">
         <v>57723</v>
@@ -1213,7 +1213,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1227,10 +1227,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>520520</v>
+        <v>520186</v>
       </c>
       <c r="R6" t="n">
-        <v>7001311</v>
+        <v>7001459</v>
       </c>
       <c r="S6" t="n">
         <v>8</v>
@@ -1262,7 +1262,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack, enstaka färska och rikligt med äldre på en tall.</t>
+          <t>Ringhack, äldre, på stambasen av en gran  intill en gammal sälg.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1291,17 +1291,17 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1329,47 +1329,38 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129126843</v>
+        <v>129131350</v>
       </c>
       <c r="B7" t="n">
-        <v>98651</v>
+        <v>57723</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1383,13 +1374,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>520211</v>
+        <v>520520</v>
       </c>
       <c r="R7" t="n">
-        <v>7001475</v>
+        <v>7001311</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1418,7 +1409,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1428,12 +1419,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Minst 100 plantor inom ca 0,5 m2 yta.</t>
+          <t>Ringhack, enstaka färska och rikligt med äldre på en tall.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1447,7 +1438,27 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1465,38 +1476,47 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129127182</v>
+        <v>129126843</v>
       </c>
       <c r="B8" t="n">
-        <v>57723</v>
+        <v>98656</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1510,13 +1530,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>520186</v>
+        <v>520211</v>
       </c>
       <c r="R8" t="n">
-        <v>7001459</v>
+        <v>7001475</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1545,7 +1565,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1555,12 +1575,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran  intill en gammal sälg.</t>
+          <t>Minst 100 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1575,26 +1595,6 @@
       <c r="AH8" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1612,38 +1612,38 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129135867</v>
+        <v>129135692</v>
       </c>
       <c r="B9" t="n">
-        <v>100839</v>
+        <v>80139</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1652,13 +1652,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>520192</v>
+        <v>520343</v>
       </c>
       <c r="R9" t="n">
-        <v>7001635</v>
+        <v>7001533</v>
       </c>
       <c r="S9" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1685,11 +1685,21 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>18:06</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>18:06</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1698,6 +1708,31 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1714,38 +1749,38 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129135692</v>
+        <v>129135867</v>
       </c>
       <c r="B10" t="n">
-        <v>80139</v>
+        <v>100844</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1754,13 +1789,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>520343</v>
+        <v>520192</v>
       </c>
       <c r="R10" t="n">
-        <v>7001533</v>
+        <v>7001635</v>
       </c>
       <c r="S10" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1787,21 +1822,11 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>18:06</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>18:06</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1810,31 +1835,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1851,10 +1851,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129127736</v>
+        <v>129128175</v>
       </c>
       <c r="B11" t="n">
-        <v>57723</v>
+        <v>79034</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1862,42 +1862,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>520237</v>
+        <v>520329</v>
       </c>
       <c r="R11" t="n">
-        <v>7001416</v>
+        <v>7001400</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1926,7 +1921,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1936,12 +1931,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:01</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1953,11 +1943,6 @@
       <c r="AG11" t="b">
         <v>0</v>
       </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AJ11" t="inlineStr">
         <is>
           <t>gran</t>
@@ -1968,14 +1953,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1993,10 +1973,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129128175</v>
+        <v>129126617</v>
       </c>
       <c r="B12" t="n">
-        <v>79034</v>
+        <v>80139</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2004,37 +1984,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>520329</v>
+        <v>520219</v>
       </c>
       <c r="R12" t="n">
-        <v>7001400</v>
+        <v>7001429</v>
       </c>
       <c r="S12" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2063,7 +2048,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2073,7 +2058,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2087,17 +2072,17 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2115,10 +2100,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129126617</v>
+        <v>129127736</v>
       </c>
       <c r="B13" t="n">
-        <v>80139</v>
+        <v>57723</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2126,27 +2111,27 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2155,13 +2140,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>520219</v>
+        <v>520237</v>
       </c>
       <c r="R13" t="n">
-        <v>7001429</v>
+        <v>7001416</v>
       </c>
       <c r="S13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2190,7 +2175,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2200,7 +2185,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2212,19 +2202,29 @@
       <c r="AG13" t="b">
         <v>0</v>
       </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2382,7 +2382,7 @@
         <v>129135822</v>
       </c>
       <c r="B15" t="n">
-        <v>104119</v>
+        <v>104124</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2505,10 +2505,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129128148</v>
+        <v>129127604</v>
       </c>
       <c r="B16" t="n">
-        <v>80140</v>
+        <v>80139</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2516,27 +2516,27 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2545,13 +2545,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>520338</v>
+        <v>520243</v>
       </c>
       <c r="R16" t="n">
-        <v>7001407</v>
+        <v>7001423</v>
       </c>
       <c r="S16" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2590,7 +2590,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Fertil lunglav på en sälg med doftticka.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2604,27 +2609,27 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Betula</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2642,7 +2647,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129127604</v>
+        <v>129128162</v>
       </c>
       <c r="B17" t="n">
         <v>80139</v>
@@ -2673,7 +2678,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2682,13 +2687,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>520243</v>
+        <v>520355</v>
       </c>
       <c r="R17" t="n">
-        <v>7001423</v>
+        <v>7001412</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2717,7 +2722,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2727,12 +2732,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:59</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Fertil lunglav på en sälg med doftticka.</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -2784,10 +2784,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129128162</v>
+        <v>129128148</v>
       </c>
       <c r="B18" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2795,21 +2795,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2824,13 +2824,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>520355</v>
+        <v>520338</v>
       </c>
       <c r="R18" t="n">
-        <v>7001412</v>
+        <v>7001407</v>
       </c>
       <c r="S18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2888,22 +2888,22 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark of dead wood # Betula</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2921,62 +2921,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129127509</v>
+        <v>129131389</v>
       </c>
       <c r="B19" t="n">
-        <v>92095</v>
+        <v>79034</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>520242</v>
+        <v>520611</v>
       </c>
       <c r="R19" t="n">
-        <v>7001434</v>
+        <v>7001285</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3005,7 +2991,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3015,7 +3001,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3026,31 +3012,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Salix caprea</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -3067,48 +3028,62 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129131389</v>
+        <v>129127509</v>
       </c>
       <c r="B20" t="n">
-        <v>79034</v>
+        <v>92100</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>520611</v>
+        <v>520242</v>
       </c>
       <c r="R20" t="n">
-        <v>7001285</v>
+        <v>7001434</v>
       </c>
       <c r="S20" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3137,7 +3112,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3147,7 +3122,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3158,6 +3133,31 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Salix caprea</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -3174,10 +3174,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129126633</v>
+        <v>129125122</v>
       </c>
       <c r="B21" t="n">
-        <v>80139</v>
+        <v>79034</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3185,21 +3185,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3209,13 +3209,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>520226</v>
+        <v>519973</v>
       </c>
       <c r="R21" t="n">
-        <v>7001438</v>
+        <v>7001540</v>
       </c>
       <c r="S21" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3242,26 +3242,11 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>11:19</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>11:19</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På grovbarkad gammal asp.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3270,31 +3255,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3311,10 +3271,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129125122</v>
+        <v>129126633</v>
       </c>
       <c r="B22" t="n">
-        <v>79034</v>
+        <v>80139</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3322,21 +3282,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3346,13 +3306,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>519973</v>
+        <v>520226</v>
       </c>
       <c r="R22" t="n">
-        <v>7001540</v>
+        <v>7001438</v>
       </c>
       <c r="S22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3379,11 +3339,26 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På grovbarkad gammal asp.</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3392,6 +3367,31 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3515,10 +3515,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129128128</v>
+        <v>129126703</v>
       </c>
       <c r="B24" t="n">
-        <v>80140</v>
+        <v>79034</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3526,39 +3526,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>520340</v>
+        <v>520253</v>
       </c>
       <c r="R24" t="n">
-        <v>7001392</v>
+        <v>7001454</v>
       </c>
       <c r="S24" t="n">
         <v>9</v>
@@ -3590,7 +3585,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3600,7 +3595,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3614,27 +3609,27 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3652,10 +3647,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129126703</v>
+        <v>129128128</v>
       </c>
       <c r="B25" t="n">
-        <v>79034</v>
+        <v>80140</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3663,34 +3658,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>520253</v>
+        <v>520340</v>
       </c>
       <c r="R25" t="n">
-        <v>7001454</v>
+        <v>7001392</v>
       </c>
       <c r="S25" t="n">
         <v>9</v>
@@ -3722,7 +3722,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3732,7 +3732,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3746,27 +3746,27 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3784,10 +3784,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129127211</v>
+        <v>129131479</v>
       </c>
       <c r="B26" t="n">
-        <v>80139</v>
+        <v>79034</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3795,42 +3795,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>520158</v>
+        <v>520712</v>
       </c>
       <c r="R26" t="n">
-        <v>7001448</v>
+        <v>7001363</v>
       </c>
       <c r="S26" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3859,7 +3854,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3869,7 +3864,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3883,27 +3878,27 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3921,10 +3916,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129131479</v>
+        <v>129127211</v>
       </c>
       <c r="B27" t="n">
-        <v>79034</v>
+        <v>80139</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3932,37 +3927,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>520712</v>
+        <v>520158</v>
       </c>
       <c r="R27" t="n">
-        <v>7001363</v>
+        <v>7001448</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3991,7 +3991,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4001,7 +4001,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4015,27 +4015,27 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4185,38 +4185,52 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129124933</v>
+        <v>129127084</v>
       </c>
       <c r="B29" t="n">
-        <v>57723</v>
+        <v>98656</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -4225,13 +4239,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>519886</v>
+        <v>520203</v>
       </c>
       <c r="R29" t="n">
-        <v>7001592</v>
+        <v>7001453</v>
       </c>
       <c r="S29" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4260,7 +4274,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4270,12 +4284,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:39</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran i hyggeskanten.</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4290,26 +4299,6 @@
       <c r="AH29" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4327,52 +4316,38 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129127084</v>
+        <v>129124933</v>
       </c>
       <c r="B30" t="n">
-        <v>98651</v>
+        <v>57723</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4381,13 +4356,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>520203</v>
+        <v>519886</v>
       </c>
       <c r="R30" t="n">
-        <v>7001453</v>
+        <v>7001592</v>
       </c>
       <c r="S30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4416,7 +4391,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4426,7 +4401,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>09:39</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran i hyggeskanten.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4441,6 +4421,26 @@
       <c r="AH30" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4862,7 +4862,7 @@
         <v>129135770</v>
       </c>
       <c r="B34" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4990,7 +4990,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129135454</v>
+        <v>129128023</v>
       </c>
       <c r="B35" t="n">
         <v>80139</v>
@@ -5030,10 +5030,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>520630</v>
+        <v>520326</v>
       </c>
       <c r="R35" t="n">
-        <v>7001400</v>
+        <v>7001449</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5065,7 +5065,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5075,12 +5075,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På både gran och sälg.</t>
+          <t>Rikligt med bålar på en rakväxt björk.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5094,27 +5094,27 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Betula</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5132,7 +5132,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129128023</v>
+        <v>129135454</v>
       </c>
       <c r="B36" t="n">
         <v>80139</v>
@@ -5172,10 +5172,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>520326</v>
+        <v>520630</v>
       </c>
       <c r="R36" t="n">
-        <v>7001449</v>
+        <v>7001400</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Rikligt med bålar på en rakväxt björk.</t>
+          <t>På både gran och sälg.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5236,27 +5236,27 @@
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Betula</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5277,7 +5277,7 @@
         <v>129128320</v>
       </c>
       <c r="B37" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 43533-2025 artfynd.xlsx
+++ b/artfynd/A 43533-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY39"/>
+  <dimension ref="A1:AY76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>129126527</v>
       </c>
       <c r="B2" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -817,38 +817,47 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129135852</v>
+        <v>129135545</v>
       </c>
       <c r="B3" t="n">
-        <v>98990</v>
+        <v>98659</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219880</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>gulnande löv/blad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -857,10 +866,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>520213</v>
+        <v>520564</v>
       </c>
       <c r="R3" t="n">
-        <v>7001609</v>
+        <v>7001441</v>
       </c>
       <c r="S3" t="n">
         <v>9</v>
@@ -892,7 +901,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -902,7 +911,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -934,47 +943,38 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129135545</v>
+        <v>129135852</v>
       </c>
       <c r="B4" t="n">
-        <v>98656</v>
+        <v>98993</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>219880</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>gulnande löv/blad</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -983,10 +983,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>520564</v>
+        <v>520213</v>
       </c>
       <c r="R4" t="n">
-        <v>7001441</v>
+        <v>7001609</v>
       </c>
       <c r="S4" t="n">
         <v>9</v>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1063,7 +1063,7 @@
         <v>129131270</v>
       </c>
       <c r="B5" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>129126843</v>
       </c>
       <c r="B8" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1615,7 +1615,7 @@
         <v>129135692</v>
       </c>
       <c r="B9" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>129135867</v>
       </c>
       <c r="B10" t="n">
-        <v>100844</v>
+        <v>100847</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1851,10 +1851,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129128175</v>
+        <v>129126617</v>
       </c>
       <c r="B11" t="n">
-        <v>79034</v>
+        <v>80140</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1862,37 +1862,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>520329</v>
+        <v>520219</v>
       </c>
       <c r="R11" t="n">
-        <v>7001400</v>
+        <v>7001429</v>
       </c>
       <c r="S11" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1921,7 +1926,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1931,7 +1936,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1945,17 +1950,17 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1973,10 +1978,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129126617</v>
+        <v>129127736</v>
       </c>
       <c r="B12" t="n">
-        <v>80139</v>
+        <v>57723</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1984,27 +1989,27 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -2013,13 +2018,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>520219</v>
+        <v>520237</v>
       </c>
       <c r="R12" t="n">
-        <v>7001429</v>
+        <v>7001416</v>
       </c>
       <c r="S12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2048,7 +2053,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2058,7 +2063,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2070,19 +2080,29 @@
       <c r="AG12" t="b">
         <v>0</v>
       </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2100,10 +2120,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129127736</v>
+        <v>129128175</v>
       </c>
       <c r="B13" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2111,42 +2131,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>520237</v>
+        <v>520329</v>
       </c>
       <c r="R13" t="n">
-        <v>7001416</v>
+        <v>7001400</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2175,7 +2190,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2185,12 +2200,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:01</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2202,11 +2212,6 @@
       <c r="AG13" t="b">
         <v>0</v>
       </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AJ13" t="inlineStr">
         <is>
           <t>gran</t>
@@ -2217,14 +2222,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2245,7 +2245,7 @@
         <v>129126547</v>
       </c>
       <c r="B14" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2382,7 +2382,7 @@
         <v>129135822</v>
       </c>
       <c r="B15" t="n">
-        <v>104124</v>
+        <v>104127</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
         <v>129127604</v>
       </c>
       <c r="B16" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2650,7 +2650,7 @@
         <v>129128162</v>
       </c>
       <c r="B17" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2787,7 +2787,7 @@
         <v>129128148</v>
       </c>
       <c r="B18" t="n">
-        <v>80140</v>
+        <v>80141</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2921,48 +2921,62 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129131389</v>
+        <v>129127509</v>
       </c>
       <c r="B19" t="n">
-        <v>79034</v>
+        <v>92103</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>520611</v>
+        <v>520242</v>
       </c>
       <c r="R19" t="n">
-        <v>7001285</v>
+        <v>7001434</v>
       </c>
       <c r="S19" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2991,7 +3005,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3001,7 +3015,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3012,6 +3026,31 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Salix caprea</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -3028,62 +3067,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129127509</v>
+        <v>129131389</v>
       </c>
       <c r="B20" t="n">
-        <v>92100</v>
+        <v>79035</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>520242</v>
+        <v>520611</v>
       </c>
       <c r="R20" t="n">
-        <v>7001434</v>
+        <v>7001285</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3112,7 +3137,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3122,7 +3147,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3133,31 +3158,6 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Salix caprea</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -3174,10 +3174,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129125122</v>
+        <v>129126633</v>
       </c>
       <c r="B21" t="n">
-        <v>79034</v>
+        <v>80140</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3185,21 +3185,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3209,13 +3209,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>519973</v>
+        <v>520226</v>
       </c>
       <c r="R21" t="n">
-        <v>7001540</v>
+        <v>7001438</v>
       </c>
       <c r="S21" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3242,11 +3242,26 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På grovbarkad gammal asp.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3255,6 +3270,31 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3271,10 +3311,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129126633</v>
+        <v>129125122</v>
       </c>
       <c r="B22" t="n">
-        <v>80139</v>
+        <v>79035</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3282,21 +3322,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3306,13 +3346,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>520226</v>
+        <v>519973</v>
       </c>
       <c r="R22" t="n">
-        <v>7001438</v>
+        <v>7001540</v>
       </c>
       <c r="S22" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3339,26 +3379,11 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>11:19</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>11:19</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>På grovbarkad gammal asp.</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3367,31 +3392,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3408,10 +3408,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129136001</v>
+        <v>129128128</v>
       </c>
       <c r="B23" t="n">
-        <v>79034</v>
+        <v>80141</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3419,37 +3419,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>520012</v>
+        <v>520340</v>
       </c>
       <c r="R23" t="n">
-        <v>7001652</v>
+        <v>7001392</v>
       </c>
       <c r="S23" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3478,7 +3483,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3488,7 +3493,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3499,6 +3504,31 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3515,10 +3545,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129126703</v>
+        <v>129136001</v>
       </c>
       <c r="B24" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3550,13 +3580,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>520253</v>
+        <v>520012</v>
       </c>
       <c r="R24" t="n">
-        <v>7001454</v>
+        <v>7001652</v>
       </c>
       <c r="S24" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3585,7 +3615,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3595,7 +3625,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3606,31 +3636,6 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3647,10 +3652,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129128128</v>
+        <v>129126703</v>
       </c>
       <c r="B25" t="n">
-        <v>80140</v>
+        <v>79035</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3658,39 +3663,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>520340</v>
+        <v>520253</v>
       </c>
       <c r="R25" t="n">
-        <v>7001392</v>
+        <v>7001454</v>
       </c>
       <c r="S25" t="n">
         <v>9</v>
@@ -3722,7 +3722,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3732,7 +3732,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3746,27 +3746,27 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3784,10 +3784,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129131479</v>
+        <v>129127211</v>
       </c>
       <c r="B26" t="n">
-        <v>79034</v>
+        <v>80140</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3795,37 +3795,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>520712</v>
+        <v>520158</v>
       </c>
       <c r="R26" t="n">
-        <v>7001363</v>
+        <v>7001448</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3854,7 +3859,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3864,7 +3869,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3878,27 +3883,27 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3916,10 +3921,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129127211</v>
+        <v>129131479</v>
       </c>
       <c r="B27" t="n">
-        <v>80139</v>
+        <v>79035</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3927,42 +3932,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>520158</v>
+        <v>520712</v>
       </c>
       <c r="R27" t="n">
-        <v>7001448</v>
+        <v>7001363</v>
       </c>
       <c r="S27" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3991,7 +3991,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4001,7 +4001,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4015,27 +4015,27 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4056,7 +4056,7 @@
         <v>129131418</v>
       </c>
       <c r="B28" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4185,52 +4185,38 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129127084</v>
+        <v>129124933</v>
       </c>
       <c r="B29" t="n">
-        <v>98656</v>
+        <v>57723</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -4239,13 +4225,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>520203</v>
+        <v>519886</v>
       </c>
       <c r="R29" t="n">
-        <v>7001453</v>
+        <v>7001592</v>
       </c>
       <c r="S29" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4274,7 +4260,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4284,7 +4270,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>09:39</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran i hyggeskanten.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4299,6 +4290,26 @@
       <c r="AH29" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4316,38 +4327,52 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129124933</v>
+        <v>129127084</v>
       </c>
       <c r="B30" t="n">
-        <v>57723</v>
+        <v>98659</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4356,13 +4381,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>519886</v>
+        <v>520203</v>
       </c>
       <c r="R30" t="n">
-        <v>7001592</v>
+        <v>7001453</v>
       </c>
       <c r="S30" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4391,7 +4416,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4401,12 +4426,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:39</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran i hyggeskanten.</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4421,26 +4441,6 @@
       <c r="AH30" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4461,7 +4461,7 @@
         <v>129135649</v>
       </c>
       <c r="B31" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4598,7 +4598,7 @@
         <v>129125106</v>
       </c>
       <c r="B32" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4725,7 +4725,7 @@
         <v>129128345</v>
       </c>
       <c r="B33" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4862,7 +4862,7 @@
         <v>129135770</v>
       </c>
       <c r="B34" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4993,7 +4993,7 @@
         <v>129128023</v>
       </c>
       <c r="B35" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5135,7 +5135,7 @@
         <v>129135454</v>
       </c>
       <c r="B36" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5274,62 +5274,48 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129128320</v>
+        <v>129135677</v>
       </c>
       <c r="B37" t="n">
-        <v>98656</v>
+        <v>79035</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>520352</v>
+        <v>520346</v>
       </c>
       <c r="R37" t="n">
-        <v>7001397</v>
+        <v>7001536</v>
       </c>
       <c r="S37" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5358,7 +5344,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5368,12 +5354,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:20</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Minst 10 plantor inom ca 0,5 m2 yta.</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5384,11 +5365,6 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -5405,48 +5381,62 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129135677</v>
+        <v>129128320</v>
       </c>
       <c r="B38" t="n">
-        <v>79034</v>
+        <v>98659</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>520346</v>
+        <v>520352</v>
       </c>
       <c r="R38" t="n">
-        <v>7001536</v>
+        <v>7001397</v>
       </c>
       <c r="S38" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5475,7 +5465,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5485,7 +5475,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Minst 10 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5496,6 +5491,11 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -5515,7 +5515,7 @@
         <v>129135697</v>
       </c>
       <c r="B39" t="n">
-        <v>80168</v>
+        <v>80169</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5646,6 +5646,3784 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>129193543</v>
+      </c>
+      <c r="B40" t="n">
+        <v>57723</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Fisksjölandsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>520321</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7001391</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>129193558</v>
+      </c>
+      <c r="B41" t="n">
+        <v>80140</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Fisksjölandsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>520415</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7001416</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>129193518</v>
+      </c>
+      <c r="B42" t="n">
+        <v>57723</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Fisksjölandsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>520676</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7001377</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>129193568</v>
+      </c>
+      <c r="B43" t="n">
+        <v>80140</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Fisksjölandsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>520159</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7001489</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>129193576</v>
+      </c>
+      <c r="B44" t="n">
+        <v>98659</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Fisksjölandsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>520675</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7001377</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>129193582</v>
+      </c>
+      <c r="B45" t="n">
+        <v>98659</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Fisksjölandsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>520388</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7001418</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Minst 50</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>129193542</v>
+      </c>
+      <c r="B46" t="n">
+        <v>57723</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Fisksjölandsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>520422</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7001418</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>129193583</v>
+      </c>
+      <c r="B47" t="n">
+        <v>98659</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Fisksjölandsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>520338</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7001427</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Minst 100</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>129193565</v>
+      </c>
+      <c r="B48" t="n">
+        <v>80140</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Fisksjölandsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>520156</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7001442</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>129193591</v>
+      </c>
+      <c r="B49" t="n">
+        <v>92855</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Fisksjölandsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>520063</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7001567</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>129193590</v>
+      </c>
+      <c r="B50" t="n">
+        <v>79035</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Fisksjölandsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>520187</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7001471</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>129193523</v>
+      </c>
+      <c r="B51" t="n">
+        <v>57723</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Fisksjölandsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>520478</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7001335</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>129193517</v>
+      </c>
+      <c r="B52" t="n">
+        <v>57723</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Fisksjölandsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>520301</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7001547</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>129193566</v>
+      </c>
+      <c r="B53" t="n">
+        <v>80140</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Fisksjölandsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>520180</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7001458</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>129193581</v>
+      </c>
+      <c r="B54" t="n">
+        <v>98659</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Fisksjölandsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>520425</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7001407</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Minst 80</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>129193570</v>
+      </c>
+      <c r="B55" t="n">
+        <v>80140</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Fisksjölandsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>519997</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7001586</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>129193550</v>
+      </c>
+      <c r="B56" t="n">
+        <v>80140</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Fisksjölandsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>520344</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7001502</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>129193561</v>
+      </c>
+      <c r="B57" t="n">
+        <v>80140</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Fisksjölandsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>520344</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7001402</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>129193567</v>
+      </c>
+      <c r="B58" t="n">
+        <v>80140</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Fisksjölandsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>520184</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7001482</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>129193524</v>
+      </c>
+      <c r="B59" t="n">
+        <v>57723</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Fisksjölandsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>520478</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7001328</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>129193544</v>
+      </c>
+      <c r="B60" t="n">
+        <v>57723</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Fisksjölandsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>520270</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7001484</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>129193564</v>
+      </c>
+      <c r="B61" t="n">
+        <v>80140</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Fisksjölandsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>520225</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7001483</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>129193557</v>
+      </c>
+      <c r="B62" t="n">
+        <v>80140</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Fisksjölandsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>520374</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7001329</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>129193585</v>
+      </c>
+      <c r="B63" t="n">
+        <v>98659</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Fisksjölandsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>520122</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7001476</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Fler än 200</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF63" t="inlineStr"/>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>129193560</v>
+      </c>
+      <c r="B64" t="n">
+        <v>80140</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Fisksjölandsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>520346</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7001396</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>129193569</v>
+      </c>
+      <c r="B65" t="n">
+        <v>80140</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Fisksjölandsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>520094</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7001525</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>129193593</v>
+      </c>
+      <c r="B66" t="n">
+        <v>100847</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Fisksjölandsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>520101</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7001658</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>129193562</v>
+      </c>
+      <c r="B67" t="n">
+        <v>80140</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Fisksjölandsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>520335</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7001429</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>129193545</v>
+      </c>
+      <c r="B68" t="n">
+        <v>57723</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Fisksjölandsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>519958</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7001547</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>129193584</v>
+      </c>
+      <c r="B69" t="n">
+        <v>98659</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Fisksjölandsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>520320</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7001451</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Minst 100</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF69" t="inlineStr"/>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>129193573</v>
+      </c>
+      <c r="B70" t="n">
+        <v>57827</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Fisksjölandsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>520153</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7001500</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>129193563</v>
+      </c>
+      <c r="B71" t="n">
+        <v>80140</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Fisksjölandsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>520326</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7001451</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>129193559</v>
+      </c>
+      <c r="B72" t="n">
+        <v>80140</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Fisksjölandsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>520330</v>
+      </c>
+      <c r="R72" t="n">
+        <v>7001396</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>129193548</v>
+      </c>
+      <c r="B73" t="n">
+        <v>92464</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Fisksjölandsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>520063</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7001569</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>129193546</v>
+      </c>
+      <c r="B74" t="n">
+        <v>57723</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Fisksjölandsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>519958</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7001542</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>129193575</v>
+      </c>
+      <c r="B75" t="n">
+        <v>98659</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Fisksjölandsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>520528</v>
+      </c>
+      <c r="R75" t="n">
+        <v>7001465</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Minst 50</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="inlineStr"/>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>129193549</v>
+      </c>
+      <c r="B76" t="n">
+        <v>80141</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Fisksjölandsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>520345</v>
+      </c>
+      <c r="R76" t="n">
+        <v>7001396</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 43533-2025 artfynd.xlsx
+++ b/artfynd/A 43533-2025 artfynd.xlsx
@@ -675,38 +675,47 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129126527</v>
+        <v>129135545</v>
       </c>
       <c r="B2" t="n">
-        <v>80140</v>
+        <v>98659</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -715,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>520189</v>
+        <v>520564</v>
       </c>
       <c r="R2" t="n">
-        <v>7001448</v>
+        <v>7001441</v>
       </c>
       <c r="S2" t="n">
         <v>9</v>
@@ -750,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:12</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,27 +783,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -817,47 +801,38 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129135545</v>
+        <v>129126527</v>
       </c>
       <c r="B3" t="n">
-        <v>98659</v>
+        <v>80140</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -866,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>520564</v>
+        <v>520189</v>
       </c>
       <c r="R3" t="n">
-        <v>7001441</v>
+        <v>7001448</v>
       </c>
       <c r="S3" t="n">
         <v>9</v>
@@ -901,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -911,7 +886,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,7 +905,27 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -1182,38 +1182,47 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129127182</v>
+        <v>129126843</v>
       </c>
       <c r="B6" t="n">
-        <v>57723</v>
+        <v>98659</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1227,13 +1236,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>520186</v>
+        <v>520211</v>
       </c>
       <c r="R6" t="n">
-        <v>7001459</v>
+        <v>7001475</v>
       </c>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1262,7 +1271,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1272,12 +1281,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran  intill en gammal sälg.</t>
+          <t>Minst 100 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1292,26 +1301,6 @@
       <c r="AH6" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1329,7 +1318,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129131350</v>
+        <v>129127182</v>
       </c>
       <c r="B7" t="n">
         <v>57723</v>
@@ -1360,7 +1349,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1374,10 +1363,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>520520</v>
+        <v>520186</v>
       </c>
       <c r="R7" t="n">
-        <v>7001311</v>
+        <v>7001459</v>
       </c>
       <c r="S7" t="n">
         <v>8</v>
@@ -1409,7 +1398,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1419,12 +1408,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack, enstaka färska och rikligt med äldre på en tall.</t>
+          <t>Ringhack, äldre, på stambasen av en gran  intill en gammal sälg.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1438,17 +1427,17 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -1458,7 +1447,7 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1476,47 +1465,38 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129126843</v>
+        <v>129131350</v>
       </c>
       <c r="B8" t="n">
-        <v>98659</v>
+        <v>57723</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1530,13 +1510,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>520211</v>
+        <v>520520</v>
       </c>
       <c r="R8" t="n">
-        <v>7001475</v>
+        <v>7001311</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1565,7 +1545,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1575,12 +1555,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Minst 100 plantor inom ca 0,5 m2 yta.</t>
+          <t>Ringhack, enstaka färska och rikligt med äldre på en tall.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1594,7 +1574,27 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1851,10 +1851,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129126617</v>
+        <v>129128175</v>
       </c>
       <c r="B11" t="n">
-        <v>80140</v>
+        <v>79035</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1862,42 +1862,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>520219</v>
+        <v>520329</v>
       </c>
       <c r="R11" t="n">
-        <v>7001429</v>
+        <v>7001400</v>
       </c>
       <c r="S11" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1926,7 +1921,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1936,7 +1931,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1950,17 +1945,17 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1978,10 +1973,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129127736</v>
+        <v>129126617</v>
       </c>
       <c r="B12" t="n">
-        <v>57723</v>
+        <v>80140</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1989,27 +1984,27 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -2018,13 +2013,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>520237</v>
+        <v>520219</v>
       </c>
       <c r="R12" t="n">
-        <v>7001416</v>
+        <v>7001429</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2053,7 +2048,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2063,12 +2058,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:01</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2080,29 +2070,19 @@
       <c r="AG12" t="b">
         <v>0</v>
       </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2120,10 +2100,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129128175</v>
+        <v>129127736</v>
       </c>
       <c r="B13" t="n">
-        <v>79035</v>
+        <v>57723</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2131,37 +2111,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>520329</v>
+        <v>520237</v>
       </c>
       <c r="R13" t="n">
-        <v>7001400</v>
+        <v>7001416</v>
       </c>
       <c r="S13" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2190,7 +2175,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2200,7 +2185,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2212,6 +2202,11 @@
       <c r="AG13" t="b">
         <v>0</v>
       </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AJ13" t="inlineStr">
         <is>
           <t>gran</t>
@@ -2222,9 +2217,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2505,10 +2505,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129127604</v>
+        <v>129128148</v>
       </c>
       <c r="B16" t="n">
-        <v>80140</v>
+        <v>80141</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2516,27 +2516,27 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2545,13 +2545,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>520243</v>
+        <v>520338</v>
       </c>
       <c r="R16" t="n">
-        <v>7001423</v>
+        <v>7001407</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2590,12 +2590,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:59</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Fertil lunglav på en sälg med doftticka.</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2609,27 +2604,27 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark of dead wood # Betula</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2784,10 +2779,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129128148</v>
+        <v>129127604</v>
       </c>
       <c r="B18" t="n">
-        <v>80141</v>
+        <v>80140</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2795,27 +2790,27 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2824,13 +2819,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>520338</v>
+        <v>520243</v>
       </c>
       <c r="R18" t="n">
-        <v>7001407</v>
+        <v>7001423</v>
       </c>
       <c r="S18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2859,7 +2854,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2869,7 +2864,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Fertil lunglav på en sälg med doftticka.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2883,27 +2883,27 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Betula</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -3174,10 +3174,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129126633</v>
+        <v>129125122</v>
       </c>
       <c r="B21" t="n">
-        <v>80140</v>
+        <v>79035</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3185,21 +3185,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3209,13 +3209,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>520226</v>
+        <v>519973</v>
       </c>
       <c r="R21" t="n">
-        <v>7001438</v>
+        <v>7001540</v>
       </c>
       <c r="S21" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3242,26 +3242,11 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>11:19</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>11:19</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På grovbarkad gammal asp.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3270,31 +3255,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3311,10 +3271,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129125122</v>
+        <v>129126633</v>
       </c>
       <c r="B22" t="n">
-        <v>79035</v>
+        <v>80140</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3322,21 +3282,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3346,13 +3306,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>519973</v>
+        <v>520226</v>
       </c>
       <c r="R22" t="n">
-        <v>7001540</v>
+        <v>7001438</v>
       </c>
       <c r="S22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3379,11 +3339,26 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På grovbarkad gammal asp.</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3392,6 +3367,31 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3784,10 +3784,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129127211</v>
+        <v>129131479</v>
       </c>
       <c r="B26" t="n">
-        <v>80140</v>
+        <v>79035</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3795,42 +3795,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>520158</v>
+        <v>520712</v>
       </c>
       <c r="R26" t="n">
-        <v>7001448</v>
+        <v>7001363</v>
       </c>
       <c r="S26" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3859,7 +3854,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3869,7 +3864,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3883,27 +3878,27 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3921,10 +3916,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129131479</v>
+        <v>129127211</v>
       </c>
       <c r="B27" t="n">
-        <v>79035</v>
+        <v>80140</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3932,37 +3927,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>520712</v>
+        <v>520158</v>
       </c>
       <c r="R27" t="n">
-        <v>7001363</v>
+        <v>7001448</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3991,7 +3991,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4001,7 +4001,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4015,27 +4015,27 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4053,10 +4053,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129131418</v>
+        <v>129124933</v>
       </c>
       <c r="B28" t="n">
-        <v>79035</v>
+        <v>57723</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4064,37 +4064,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>520682</v>
+        <v>519886</v>
       </c>
       <c r="R28" t="n">
-        <v>7001354</v>
+        <v>7001592</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4123,7 +4128,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4133,7 +4138,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>09:39</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran i hyggeskanten.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4147,7 +4157,7 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
@@ -4162,12 +4172,12 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4185,38 +4195,52 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129124933</v>
+        <v>129127084</v>
       </c>
       <c r="B29" t="n">
-        <v>57723</v>
+        <v>98659</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -4225,13 +4249,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>519886</v>
+        <v>520203</v>
       </c>
       <c r="R29" t="n">
-        <v>7001592</v>
+        <v>7001453</v>
       </c>
       <c r="S29" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4260,7 +4284,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4270,12 +4294,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:39</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran i hyggeskanten.</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4290,26 +4309,6 @@
       <c r="AH29" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4327,67 +4326,48 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129127084</v>
+        <v>129131418</v>
       </c>
       <c r="B30" t="n">
-        <v>98659</v>
+        <v>79035</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>520203</v>
+        <v>520682</v>
       </c>
       <c r="R30" t="n">
-        <v>7001453</v>
+        <v>7001354</v>
       </c>
       <c r="S30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4416,7 +4396,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4426,7 +4406,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4440,7 +4420,27 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4722,48 +4722,62 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129128345</v>
+        <v>129135770</v>
       </c>
       <c r="B33" t="n">
-        <v>79035</v>
+        <v>98659</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>520362</v>
+        <v>520226</v>
       </c>
       <c r="R33" t="n">
-        <v>7001381</v>
+        <v>7001601</v>
       </c>
       <c r="S33" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4792,7 +4806,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4802,12 +4816,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Minst 120 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4821,27 +4835,7 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4859,62 +4853,48 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129135770</v>
+        <v>129128345</v>
       </c>
       <c r="B34" t="n">
-        <v>98659</v>
+        <v>79035</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>520226</v>
+        <v>520362</v>
       </c>
       <c r="R34" t="n">
-        <v>7001601</v>
+        <v>7001381</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4943,7 +4923,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4953,12 +4933,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Minst 120 plantor inom ca 1 m2 yta.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4972,7 +4952,27 @@
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4990,7 +4990,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129128023</v>
+        <v>129135454</v>
       </c>
       <c r="B35" t="n">
         <v>80140</v>
@@ -5030,10 +5030,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>520326</v>
+        <v>520630</v>
       </c>
       <c r="R35" t="n">
-        <v>7001449</v>
+        <v>7001400</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5065,7 +5065,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5075,12 +5075,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Rikligt med bålar på en rakväxt björk.</t>
+          <t>På både gran och sälg.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5094,27 +5094,27 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Betula</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5132,7 +5132,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129135454</v>
+        <v>129128023</v>
       </c>
       <c r="B36" t="n">
         <v>80140</v>
@@ -5172,10 +5172,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>520630</v>
+        <v>520326</v>
       </c>
       <c r="R36" t="n">
-        <v>7001400</v>
+        <v>7001449</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På både gran och sälg.</t>
+          <t>Rikligt med bålar på en rakväxt björk.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5236,27 +5236,27 @@
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Betula</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5950,32 +5950,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129193568</v>
+        <v>129193576</v>
       </c>
       <c r="B43" t="n">
-        <v>80140</v>
+        <v>98659</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5985,10 +5985,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>520159</v>
+        <v>520675</v>
       </c>
       <c r="R43" t="n">
-        <v>7001489</v>
+        <v>7001377</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6047,7 +6047,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129193576</v>
+        <v>129193582</v>
       </c>
       <c r="B44" t="n">
         <v>98659</v>
@@ -6075,17 +6075,33 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>520675</v>
+        <v>520388</v>
       </c>
       <c r="R44" t="n">
-        <v>7001377</v>
+        <v>7001418</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6120,12 +6136,18 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Minst 50</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -6144,61 +6166,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129193582</v>
+        <v>129193568</v>
       </c>
       <c r="B45" t="n">
-        <v>98659</v>
+        <v>80140</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>520388</v>
+        <v>520159</v>
       </c>
       <c r="R45" t="n">
-        <v>7001418</v>
+        <v>7001489</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6233,18 +6239,12 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Minst 50</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -6263,45 +6263,61 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129193542</v>
+        <v>129193583</v>
       </c>
       <c r="B46" t="n">
-        <v>57723</v>
+        <v>98659</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>520422</v>
+        <v>520338</v>
       </c>
       <c r="R46" t="n">
-        <v>7001418</v>
+        <v>7001427</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6338,7 +6354,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Minst 100</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6347,6 +6363,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -6365,61 +6382,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129193583</v>
+        <v>129193542</v>
       </c>
       <c r="B47" t="n">
-        <v>98659</v>
+        <v>57723</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>520338</v>
+        <v>520422</v>
       </c>
       <c r="R47" t="n">
-        <v>7001427</v>
+        <v>7001418</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6456,7 +6457,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Minst 100</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6465,7 +6466,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -6678,10 +6678,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129193590</v>
+        <v>129193566</v>
       </c>
       <c r="B50" t="n">
-        <v>79035</v>
+        <v>80140</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6689,21 +6689,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6713,10 +6713,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>520187</v>
+        <v>520180</v>
       </c>
       <c r="R50" t="n">
-        <v>7001471</v>
+        <v>7001458</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6979,45 +6979,61 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129193566</v>
+        <v>129193581</v>
       </c>
       <c r="B53" t="n">
-        <v>80140</v>
+        <v>98659</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>520180</v>
+        <v>520425</v>
       </c>
       <c r="R53" t="n">
-        <v>7001458</v>
+        <v>7001407</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7052,12 +7068,18 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Minst 80</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -7076,61 +7098,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129193581</v>
+        <v>129193590</v>
       </c>
       <c r="B54" t="n">
-        <v>98659</v>
+        <v>79035</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>520425</v>
+        <v>520187</v>
       </c>
       <c r="R54" t="n">
-        <v>7001407</v>
+        <v>7001471</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7165,18 +7171,12 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Minst 80</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -7389,10 +7389,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129193561</v>
+        <v>129193524</v>
       </c>
       <c r="B57" t="n">
-        <v>80140</v>
+        <v>57723</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7400,21 +7400,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7424,10 +7424,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>520344</v>
+        <v>520478</v>
       </c>
       <c r="R57" t="n">
-        <v>7001402</v>
+        <v>7001328</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7460,6 +7460,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7486,10 +7491,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129193567</v>
+        <v>129193544</v>
       </c>
       <c r="B58" t="n">
-        <v>80140</v>
+        <v>57723</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7497,21 +7502,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7521,10 +7526,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>520184</v>
+        <v>520270</v>
       </c>
       <c r="R58" t="n">
-        <v>7001482</v>
+        <v>7001484</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7557,6 +7562,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7583,10 +7593,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129193524</v>
+        <v>129193561</v>
       </c>
       <c r="B59" t="n">
-        <v>57723</v>
+        <v>80140</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7594,21 +7604,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7618,10 +7628,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>520478</v>
+        <v>520344</v>
       </c>
       <c r="R59" t="n">
-        <v>7001328</v>
+        <v>7001402</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7654,11 +7664,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7685,10 +7690,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129193544</v>
+        <v>129193567</v>
       </c>
       <c r="B60" t="n">
-        <v>57723</v>
+        <v>80140</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7696,21 +7701,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7720,10 +7725,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>520270</v>
+        <v>520184</v>
       </c>
       <c r="R60" t="n">
-        <v>7001484</v>
+        <v>7001482</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7756,11 +7761,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8096,32 +8096,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129193560</v>
+        <v>129193593</v>
       </c>
       <c r="B64" t="n">
-        <v>80140</v>
+        <v>100847</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>222498</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -8131,10 +8131,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>520346</v>
+        <v>520101</v>
       </c>
       <c r="R64" t="n">
-        <v>7001396</v>
+        <v>7001658</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8193,7 +8193,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129193569</v>
+        <v>129193560</v>
       </c>
       <c r="B65" t="n">
         <v>80140</v>
@@ -8228,10 +8228,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>520094</v>
+        <v>520346</v>
       </c>
       <c r="R65" t="n">
-        <v>7001525</v>
+        <v>7001396</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8290,32 +8290,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129193593</v>
+        <v>129193569</v>
       </c>
       <c r="B66" t="n">
-        <v>100847</v>
+        <v>80140</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>222498</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -8325,10 +8325,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>520101</v>
+        <v>520094</v>
       </c>
       <c r="R66" t="n">
-        <v>7001658</v>
+        <v>7001525</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -9109,10 +9109,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129193546</v>
+        <v>129193549</v>
       </c>
       <c r="B74" t="n">
-        <v>57723</v>
+        <v>80141</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9120,21 +9120,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -9144,10 +9144,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>519958</v>
+        <v>520345</v>
       </c>
       <c r="R74" t="n">
-        <v>7001542</v>
+        <v>7001396</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9180,11 +9180,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9211,61 +9206,45 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129193575</v>
+        <v>129193546</v>
       </c>
       <c r="B75" t="n">
-        <v>98659</v>
+        <v>57723</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="N75" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>520528</v>
+        <v>519958</v>
       </c>
       <c r="R75" t="n">
-        <v>7001465</v>
+        <v>7001542</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9302,7 +9281,7 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Minst 50</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9311,7 +9290,6 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -9330,45 +9308,61 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129193549</v>
+        <v>129193575</v>
       </c>
       <c r="B76" t="n">
-        <v>80141</v>
+        <v>98659</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>520345</v>
+        <v>520528</v>
       </c>
       <c r="R76" t="n">
-        <v>7001396</v>
+        <v>7001465</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9403,12 +9397,18 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Minst 50</t>
+        </is>
+      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 43533-2025 artfynd.xlsx
+++ b/artfynd/A 43533-2025 artfynd.xlsx
@@ -675,47 +675,38 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129135545</v>
+        <v>129126527</v>
       </c>
       <c r="B2" t="n">
-        <v>98659</v>
+        <v>80140</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>520564</v>
+        <v>520189</v>
       </c>
       <c r="R2" t="n">
-        <v>7001441</v>
+        <v>7001448</v>
       </c>
       <c r="S2" t="n">
         <v>9</v>
@@ -759,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -783,7 +779,27 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -801,38 +817,38 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129126527</v>
+        <v>129135852</v>
       </c>
       <c r="B3" t="n">
-        <v>80140</v>
+        <v>98993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>219880</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>gulnande löv/blad</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -841,10 +857,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>520189</v>
+        <v>520213</v>
       </c>
       <c r="R3" t="n">
-        <v>7001448</v>
+        <v>7001609</v>
       </c>
       <c r="S3" t="n">
         <v>9</v>
@@ -876,7 +892,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,12 +902,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:12</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,27 +916,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -943,38 +934,47 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129135852</v>
+        <v>129135545</v>
       </c>
       <c r="B4" t="n">
-        <v>98993</v>
+        <v>98659</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219880</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>gulnande löv/blad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -983,10 +983,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>520213</v>
+        <v>520564</v>
       </c>
       <c r="R4" t="n">
-        <v>7001609</v>
+        <v>7001441</v>
       </c>
       <c r="S4" t="n">
         <v>9</v>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 43533-2025 artfynd.xlsx
+++ b/artfynd/A 43533-2025 artfynd.xlsx
@@ -1612,38 +1612,38 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129135692</v>
+        <v>129135867</v>
       </c>
       <c r="B9" t="n">
-        <v>80140</v>
+        <v>100847</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1652,13 +1652,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>520343</v>
+        <v>520192</v>
       </c>
       <c r="R9" t="n">
-        <v>7001533</v>
+        <v>7001635</v>
       </c>
       <c r="S9" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1685,21 +1685,11 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>18:06</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>18:06</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1708,31 +1698,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1749,38 +1714,38 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129135867</v>
+        <v>129135692</v>
       </c>
       <c r="B10" t="n">
-        <v>100847</v>
+        <v>80140</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1789,13 +1754,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>520192</v>
+        <v>520343</v>
       </c>
       <c r="R10" t="n">
-        <v>7001635</v>
+        <v>7001533</v>
       </c>
       <c r="S10" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1822,11 +1787,21 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>18:06</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>18:06</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1835,6 +1810,31 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -2642,7 +2642,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129128162</v>
+        <v>129127604</v>
       </c>
       <c r="B17" t="n">
         <v>80140</v>
@@ -2673,7 +2673,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>520355</v>
+        <v>520243</v>
       </c>
       <c r="R17" t="n">
-        <v>7001412</v>
+        <v>7001423</v>
       </c>
       <c r="S17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2727,7 +2727,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Fertil lunglav på en sälg med doftticka.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2741,7 +2746,7 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -2779,7 +2784,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129127604</v>
+        <v>129128162</v>
       </c>
       <c r="B18" t="n">
         <v>80140</v>
@@ -2810,7 +2815,7 @@
       <c r="I18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2819,13 +2824,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>520243</v>
+        <v>520355</v>
       </c>
       <c r="R18" t="n">
-        <v>7001423</v>
+        <v>7001412</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2854,7 +2859,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2864,12 +2869,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:59</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Fertil lunglav på en sälg med doftticka.</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2883,7 +2883,7 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -2921,62 +2921,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129127509</v>
+        <v>129131389</v>
       </c>
       <c r="B19" t="n">
-        <v>92103</v>
+        <v>79035</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>520242</v>
+        <v>520611</v>
       </c>
       <c r="R19" t="n">
-        <v>7001434</v>
+        <v>7001285</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3005,7 +2991,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3015,7 +3001,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3026,31 +3012,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Salix caprea</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -3067,48 +3028,62 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129131389</v>
+        <v>129127509</v>
       </c>
       <c r="B20" t="n">
-        <v>79035</v>
+        <v>92103</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>520611</v>
+        <v>520242</v>
       </c>
       <c r="R20" t="n">
-        <v>7001285</v>
+        <v>7001434</v>
       </c>
       <c r="S20" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3137,7 +3112,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3147,7 +3122,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3158,6 +3133,31 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Salix caprea</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -3174,10 +3174,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129125122</v>
+        <v>129126633</v>
       </c>
       <c r="B21" t="n">
-        <v>79035</v>
+        <v>80140</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3185,21 +3185,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3209,13 +3209,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>519973</v>
+        <v>520226</v>
       </c>
       <c r="R21" t="n">
-        <v>7001540</v>
+        <v>7001438</v>
       </c>
       <c r="S21" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3242,11 +3242,26 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På grovbarkad gammal asp.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3255,6 +3270,31 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3271,10 +3311,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129126633</v>
+        <v>129125122</v>
       </c>
       <c r="B22" t="n">
-        <v>80140</v>
+        <v>79035</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3282,21 +3322,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3306,13 +3346,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>520226</v>
+        <v>519973</v>
       </c>
       <c r="R22" t="n">
-        <v>7001438</v>
+        <v>7001540</v>
       </c>
       <c r="S22" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3339,26 +3379,11 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>11:19</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>11:19</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>På grovbarkad gammal asp.</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3367,31 +3392,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3784,10 +3784,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129131479</v>
+        <v>129127211</v>
       </c>
       <c r="B26" t="n">
-        <v>79035</v>
+        <v>80140</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3795,37 +3795,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>520712</v>
+        <v>520158</v>
       </c>
       <c r="R26" t="n">
-        <v>7001363</v>
+        <v>7001448</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3854,7 +3859,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3864,7 +3869,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3878,27 +3883,27 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3916,10 +3921,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129127211</v>
+        <v>129131479</v>
       </c>
       <c r="B27" t="n">
-        <v>80140</v>
+        <v>79035</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3927,42 +3932,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>520158</v>
+        <v>520712</v>
       </c>
       <c r="R27" t="n">
-        <v>7001448</v>
+        <v>7001363</v>
       </c>
       <c r="S27" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3991,7 +3991,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4001,7 +4001,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4015,27 +4015,27 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4053,10 +4053,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129124933</v>
+        <v>129131418</v>
       </c>
       <c r="B28" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4064,42 +4064,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>519886</v>
+        <v>520682</v>
       </c>
       <c r="R28" t="n">
-        <v>7001592</v>
+        <v>7001354</v>
       </c>
       <c r="S28" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4128,7 +4123,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4138,12 +4133,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:39</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran i hyggeskanten.</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4157,7 +4147,7 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
@@ -4172,12 +4162,12 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4195,52 +4185,38 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129127084</v>
+        <v>129124933</v>
       </c>
       <c r="B29" t="n">
-        <v>98659</v>
+        <v>57723</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -4249,13 +4225,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>520203</v>
+        <v>519886</v>
       </c>
       <c r="R29" t="n">
-        <v>7001453</v>
+        <v>7001592</v>
       </c>
       <c r="S29" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4284,7 +4260,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4294,7 +4270,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>09:39</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran i hyggeskanten.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4309,6 +4290,26 @@
       <c r="AH29" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4326,48 +4327,67 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129131418</v>
+        <v>129127084</v>
       </c>
       <c r="B30" t="n">
-        <v>79035</v>
+        <v>98659</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>520682</v>
+        <v>520203</v>
       </c>
       <c r="R30" t="n">
-        <v>7001354</v>
+        <v>7001453</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4396,7 +4416,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4406,7 +4426,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4420,27 +4440,7 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4722,62 +4722,48 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129135770</v>
+        <v>129128345</v>
       </c>
       <c r="B33" t="n">
-        <v>98659</v>
+        <v>79035</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>520226</v>
+        <v>520362</v>
       </c>
       <c r="R33" t="n">
-        <v>7001601</v>
+        <v>7001381</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4806,7 +4792,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4816,12 +4802,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Minst 120 plantor inom ca 1 m2 yta.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4835,7 +4821,27 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4853,48 +4859,62 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129128345</v>
+        <v>129135770</v>
       </c>
       <c r="B34" t="n">
-        <v>79035</v>
+        <v>98659</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>520362</v>
+        <v>520226</v>
       </c>
       <c r="R34" t="n">
-        <v>7001381</v>
+        <v>7001601</v>
       </c>
       <c r="S34" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4923,7 +4943,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4933,12 +4953,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Minst 120 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4952,27 +4972,7 @@
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4990,7 +4990,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129135454</v>
+        <v>129128023</v>
       </c>
       <c r="B35" t="n">
         <v>80140</v>
@@ -5030,10 +5030,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>520630</v>
+        <v>520326</v>
       </c>
       <c r="R35" t="n">
-        <v>7001400</v>
+        <v>7001449</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5065,7 +5065,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5075,12 +5075,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På både gran och sälg.</t>
+          <t>Rikligt med bålar på en rakväxt björk.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5094,27 +5094,27 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Betula</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5132,7 +5132,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129128023</v>
+        <v>129135454</v>
       </c>
       <c r="B36" t="n">
         <v>80140</v>
@@ -5172,10 +5172,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>520326</v>
+        <v>520630</v>
       </c>
       <c r="R36" t="n">
-        <v>7001449</v>
+        <v>7001400</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Rikligt med bålar på en rakväxt björk.</t>
+          <t>På både gran och sälg.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5236,27 +5236,27 @@
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Betula</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5950,32 +5950,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129193576</v>
+        <v>129193568</v>
       </c>
       <c r="B43" t="n">
-        <v>98659</v>
+        <v>80140</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5985,10 +5985,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>520675</v>
+        <v>520159</v>
       </c>
       <c r="R43" t="n">
-        <v>7001377</v>
+        <v>7001489</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6166,32 +6166,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129193568</v>
+        <v>129193576</v>
       </c>
       <c r="B45" t="n">
-        <v>80140</v>
+        <v>98659</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>520159</v>
+        <v>520675</v>
       </c>
       <c r="R45" t="n">
-        <v>7001489</v>
+        <v>7001377</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6775,10 +6775,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129193523</v>
+        <v>129193590</v>
       </c>
       <c r="B51" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6786,21 +6786,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6810,10 +6810,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>520478</v>
+        <v>520187</v>
       </c>
       <c r="R51" t="n">
-        <v>7001335</v>
+        <v>7001471</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6846,11 +6846,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6877,7 +6872,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129193517</v>
+        <v>129193523</v>
       </c>
       <c r="B52" t="n">
         <v>57723</v>
@@ -6912,10 +6907,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>520301</v>
+        <v>520478</v>
       </c>
       <c r="R52" t="n">
-        <v>7001547</v>
+        <v>7001335</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6952,7 +6947,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6979,61 +6974,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129193581</v>
+        <v>129193517</v>
       </c>
       <c r="B53" t="n">
-        <v>98659</v>
+        <v>57723</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>520425</v>
+        <v>520301</v>
       </c>
       <c r="R53" t="n">
-        <v>7001407</v>
+        <v>7001547</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7070,7 +7049,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Minst 80</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7079,7 +7058,6 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -7098,45 +7076,61 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129193590</v>
+        <v>129193581</v>
       </c>
       <c r="B54" t="n">
-        <v>79035</v>
+        <v>98659</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>520187</v>
+        <v>520425</v>
       </c>
       <c r="R54" t="n">
-        <v>7001471</v>
+        <v>7001407</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7171,12 +7165,18 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Minst 80</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -7389,10 +7389,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129193524</v>
+        <v>129193561</v>
       </c>
       <c r="B57" t="n">
-        <v>57723</v>
+        <v>80140</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7400,21 +7400,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7424,10 +7424,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>520478</v>
+        <v>520344</v>
       </c>
       <c r="R57" t="n">
-        <v>7001328</v>
+        <v>7001402</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7460,11 +7460,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7491,10 +7486,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129193544</v>
+        <v>129193567</v>
       </c>
       <c r="B58" t="n">
-        <v>57723</v>
+        <v>80140</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7502,21 +7497,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7526,10 +7521,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>520270</v>
+        <v>520184</v>
       </c>
       <c r="R58" t="n">
-        <v>7001484</v>
+        <v>7001482</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7562,11 +7557,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7593,10 +7583,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129193561</v>
+        <v>129193544</v>
       </c>
       <c r="B59" t="n">
-        <v>80140</v>
+        <v>57723</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7604,21 +7594,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7628,10 +7618,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>520344</v>
+        <v>520270</v>
       </c>
       <c r="R59" t="n">
-        <v>7001402</v>
+        <v>7001484</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7664,6 +7654,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7690,10 +7685,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129193567</v>
+        <v>129193524</v>
       </c>
       <c r="B60" t="n">
-        <v>80140</v>
+        <v>57723</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7701,21 +7696,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7725,10 +7720,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>520184</v>
+        <v>520478</v>
       </c>
       <c r="R60" t="n">
-        <v>7001482</v>
+        <v>7001328</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7761,6 +7756,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8096,32 +8096,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129193593</v>
+        <v>129193560</v>
       </c>
       <c r="B64" t="n">
-        <v>100847</v>
+        <v>80140</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>222498</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -8131,10 +8131,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>520101</v>
+        <v>520346</v>
       </c>
       <c r="R64" t="n">
-        <v>7001658</v>
+        <v>7001396</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8193,7 +8193,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129193560</v>
+        <v>129193569</v>
       </c>
       <c r="B65" t="n">
         <v>80140</v>
@@ -8228,10 +8228,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>520346</v>
+        <v>520094</v>
       </c>
       <c r="R65" t="n">
-        <v>7001396</v>
+        <v>7001525</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8290,32 +8290,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129193569</v>
+        <v>129193593</v>
       </c>
       <c r="B66" t="n">
-        <v>80140</v>
+        <v>100847</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>222498</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -8325,10 +8325,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>520094</v>
+        <v>520101</v>
       </c>
       <c r="R66" t="n">
-        <v>7001525</v>
+        <v>7001658</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8586,46 +8586,46 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129193584</v>
+        <v>129193573</v>
       </c>
       <c r="B69" t="n">
-        <v>98659</v>
+        <v>57827</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>103031</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N69" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -8637,10 +8637,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>520320</v>
+        <v>520153</v>
       </c>
       <c r="R69" t="n">
-        <v>7001451</v>
+        <v>7001500</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8675,18 +8675,12 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Minst 100</t>
-        </is>
-      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -8705,46 +8699,46 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129193573</v>
+        <v>129193584</v>
       </c>
       <c r="B70" t="n">
-        <v>57827</v>
+        <v>98659</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>103031</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N70" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -8756,10 +8750,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>520153</v>
+        <v>520320</v>
       </c>
       <c r="R70" t="n">
-        <v>7001500</v>
+        <v>7001451</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8794,12 +8788,18 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Minst 100</t>
+        </is>
+      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -8915,32 +8915,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129193559</v>
+        <v>129193548</v>
       </c>
       <c r="B72" t="n">
-        <v>80140</v>
+        <v>92464</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>4769</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8950,10 +8950,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>520330</v>
+        <v>520063</v>
       </c>
       <c r="R72" t="n">
-        <v>7001396</v>
+        <v>7001569</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9012,32 +9012,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129193548</v>
+        <v>129193559</v>
       </c>
       <c r="B73" t="n">
-        <v>92464</v>
+        <v>80140</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4769</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -9047,10 +9047,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>520063</v>
+        <v>520330</v>
       </c>
       <c r="R73" t="n">
-        <v>7001569</v>
+        <v>7001396</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9109,10 +9109,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129193549</v>
+        <v>129193546</v>
       </c>
       <c r="B74" t="n">
-        <v>80141</v>
+        <v>57723</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9120,21 +9120,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -9144,10 +9144,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>520345</v>
+        <v>519958</v>
       </c>
       <c r="R74" t="n">
-        <v>7001396</v>
+        <v>7001542</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9180,6 +9180,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9206,45 +9211,61 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129193546</v>
+        <v>129193575</v>
       </c>
       <c r="B75" t="n">
-        <v>57723</v>
+        <v>98659</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>519958</v>
+        <v>520528</v>
       </c>
       <c r="R75" t="n">
-        <v>7001542</v>
+        <v>7001465</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9281,7 +9302,7 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Minst 50</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9290,6 +9311,7 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -9308,61 +9330,45 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129193575</v>
+        <v>129193549</v>
       </c>
       <c r="B76" t="n">
-        <v>98659</v>
+        <v>80141</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="N76" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>520528</v>
+        <v>520345</v>
       </c>
       <c r="R76" t="n">
-        <v>7001465</v>
+        <v>7001396</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9397,18 +9403,12 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Minst 50</t>
-        </is>
-      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 43533-2025 artfynd.xlsx
+++ b/artfynd/A 43533-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129126527</v>
       </c>
       <c r="B2" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>129135852</v>
       </c>
       <c r="B3" t="n">
-        <v>98993</v>
+        <v>99003</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>129135545</v>
       </c>
       <c r="B4" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1063,7 +1063,7 @@
         <v>129131270</v>
       </c>
       <c r="B5" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1182,47 +1182,38 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129126843</v>
+        <v>129127182</v>
       </c>
       <c r="B6" t="n">
-        <v>98659</v>
+        <v>57725</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1236,13 +1227,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>520211</v>
+        <v>520186</v>
       </c>
       <c r="R6" t="n">
-        <v>7001475</v>
+        <v>7001459</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1271,7 +1262,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1281,12 +1272,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Minst 100 plantor inom ca 0,5 m2 yta.</t>
+          <t>Ringhack, äldre, på stambasen av en gran  intill en gammal sälg.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1301,6 +1292,26 @@
       <c r="AH6" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1318,10 +1329,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129127182</v>
+        <v>129131350</v>
       </c>
       <c r="B7" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1360,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1363,10 +1374,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>520186</v>
+        <v>520520</v>
       </c>
       <c r="R7" t="n">
-        <v>7001459</v>
+        <v>7001311</v>
       </c>
       <c r="S7" t="n">
         <v>8</v>
@@ -1398,7 +1409,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1408,12 +1419,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran  intill en gammal sälg.</t>
+          <t>Ringhack, enstaka färska och rikligt med äldre på en tall.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1427,17 +1438,17 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -1447,7 +1458,7 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Stem on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1465,38 +1476,47 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129131350</v>
+        <v>129126843</v>
       </c>
       <c r="B8" t="n">
-        <v>57723</v>
+        <v>98669</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1510,13 +1530,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>520520</v>
+        <v>520211</v>
       </c>
       <c r="R8" t="n">
-        <v>7001311</v>
+        <v>7001475</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1545,7 +1565,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1555,12 +1575,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack, enstaka färska och rikligt med äldre på en tall.</t>
+          <t>Minst 100 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1574,27 +1594,7 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1612,38 +1612,38 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129135867</v>
+        <v>129135692</v>
       </c>
       <c r="B9" t="n">
-        <v>100847</v>
+        <v>80144</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1652,13 +1652,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>520192</v>
+        <v>520343</v>
       </c>
       <c r="R9" t="n">
-        <v>7001635</v>
+        <v>7001533</v>
       </c>
       <c r="S9" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1685,11 +1685,21 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>18:06</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>18:06</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1698,6 +1708,31 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1714,38 +1749,38 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129135692</v>
+        <v>129135867</v>
       </c>
       <c r="B10" t="n">
-        <v>80140</v>
+        <v>100857</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1754,13 +1789,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>520343</v>
+        <v>520192</v>
       </c>
       <c r="R10" t="n">
-        <v>7001533</v>
+        <v>7001635</v>
       </c>
       <c r="S10" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1787,21 +1822,11 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>18:06</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>18:06</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1810,31 +1835,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1851,10 +1851,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129128175</v>
+        <v>129126617</v>
       </c>
       <c r="B11" t="n">
-        <v>79035</v>
+        <v>80144</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1862,37 +1862,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>520329</v>
+        <v>520219</v>
       </c>
       <c r="R11" t="n">
-        <v>7001400</v>
+        <v>7001429</v>
       </c>
       <c r="S11" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1921,7 +1926,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1931,7 +1936,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1945,17 +1950,17 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1973,10 +1978,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129126617</v>
+        <v>129127736</v>
       </c>
       <c r="B12" t="n">
-        <v>80140</v>
+        <v>57725</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1984,27 +1989,27 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -2013,13 +2018,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>520219</v>
+        <v>520237</v>
       </c>
       <c r="R12" t="n">
-        <v>7001429</v>
+        <v>7001416</v>
       </c>
       <c r="S12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2048,7 +2053,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2058,7 +2063,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2070,19 +2080,29 @@
       <c r="AG12" t="b">
         <v>0</v>
       </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2100,10 +2120,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129127736</v>
+        <v>129128175</v>
       </c>
       <c r="B13" t="n">
-        <v>57723</v>
+        <v>79039</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2111,42 +2131,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>520237</v>
+        <v>520329</v>
       </c>
       <c r="R13" t="n">
-        <v>7001416</v>
+        <v>7001400</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2175,7 +2190,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2185,12 +2200,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:01</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2202,11 +2212,6 @@
       <c r="AG13" t="b">
         <v>0</v>
       </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AJ13" t="inlineStr">
         <is>
           <t>gran</t>
@@ -2217,14 +2222,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2245,7 +2245,7 @@
         <v>129126547</v>
       </c>
       <c r="B14" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2382,7 +2382,7 @@
         <v>129135822</v>
       </c>
       <c r="B15" t="n">
-        <v>104127</v>
+        <v>104137</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2505,10 +2505,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129128148</v>
+        <v>129127604</v>
       </c>
       <c r="B16" t="n">
-        <v>80141</v>
+        <v>80144</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2516,27 +2516,27 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2545,13 +2545,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>520338</v>
+        <v>520243</v>
       </c>
       <c r="R16" t="n">
-        <v>7001407</v>
+        <v>7001423</v>
       </c>
       <c r="S16" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2590,7 +2590,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Fertil lunglav på en sälg med doftticka.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2604,27 +2609,27 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Betula</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2642,10 +2647,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129127604</v>
+        <v>129128162</v>
       </c>
       <c r="B17" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2673,7 +2678,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2682,13 +2687,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>520243</v>
+        <v>520355</v>
       </c>
       <c r="R17" t="n">
-        <v>7001423</v>
+        <v>7001412</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2717,7 +2722,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2727,12 +2732,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:59</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Fertil lunglav på en sälg med doftticka.</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -2784,10 +2784,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129128162</v>
+        <v>129128148</v>
       </c>
       <c r="B18" t="n">
-        <v>80140</v>
+        <v>80145</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2795,21 +2795,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2824,13 +2824,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>520355</v>
+        <v>520338</v>
       </c>
       <c r="R18" t="n">
-        <v>7001412</v>
+        <v>7001407</v>
       </c>
       <c r="S18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2888,22 +2888,22 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark of dead wood # Betula</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2921,48 +2921,62 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129131389</v>
+        <v>129127509</v>
       </c>
       <c r="B19" t="n">
-        <v>79035</v>
+        <v>92110</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>520611</v>
+        <v>520242</v>
       </c>
       <c r="R19" t="n">
-        <v>7001285</v>
+        <v>7001434</v>
       </c>
       <c r="S19" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2991,7 +3005,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3001,7 +3015,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3012,6 +3026,31 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Salix caprea</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -3028,62 +3067,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129127509</v>
+        <v>129131389</v>
       </c>
       <c r="B20" t="n">
-        <v>92103</v>
+        <v>79039</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>520242</v>
+        <v>520611</v>
       </c>
       <c r="R20" t="n">
-        <v>7001434</v>
+        <v>7001285</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3112,7 +3137,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3122,7 +3147,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3133,31 +3158,6 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Salix caprea</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -3177,7 +3177,7 @@
         <v>129126633</v>
       </c>
       <c r="B21" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3314,7 +3314,7 @@
         <v>129125122</v>
       </c>
       <c r="B22" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3411,7 +3411,7 @@
         <v>129128128</v>
       </c>
       <c r="B23" t="n">
-        <v>80141</v>
+        <v>80145</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3545,10 +3545,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129136001</v>
+        <v>129126703</v>
       </c>
       <c r="B24" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3580,13 +3580,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>520012</v>
+        <v>520253</v>
       </c>
       <c r="R24" t="n">
-        <v>7001652</v>
+        <v>7001454</v>
       </c>
       <c r="S24" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3625,7 +3625,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3636,6 +3636,31 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3652,10 +3677,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129126703</v>
+        <v>129136001</v>
       </c>
       <c r="B25" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3687,13 +3712,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>520253</v>
+        <v>520012</v>
       </c>
       <c r="R25" t="n">
-        <v>7001454</v>
+        <v>7001652</v>
       </c>
       <c r="S25" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3722,7 +3747,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3732,7 +3757,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3743,31 +3768,6 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3784,10 +3784,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129127211</v>
+        <v>129131479</v>
       </c>
       <c r="B26" t="n">
-        <v>80140</v>
+        <v>79039</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3795,42 +3795,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>520158</v>
+        <v>520712</v>
       </c>
       <c r="R26" t="n">
-        <v>7001448</v>
+        <v>7001363</v>
       </c>
       <c r="S26" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3859,7 +3854,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3869,7 +3864,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3883,27 +3878,27 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3921,10 +3916,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129131479</v>
+        <v>129127211</v>
       </c>
       <c r="B27" t="n">
-        <v>79035</v>
+        <v>80144</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3932,37 +3927,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>520712</v>
+        <v>520158</v>
       </c>
       <c r="R27" t="n">
-        <v>7001363</v>
+        <v>7001448</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3991,7 +3991,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4001,7 +4001,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4015,27 +4015,27 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4056,7 +4056,7 @@
         <v>129131418</v>
       </c>
       <c r="B28" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4185,38 +4185,52 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129124933</v>
+        <v>129127084</v>
       </c>
       <c r="B29" t="n">
-        <v>57723</v>
+        <v>98669</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -4225,13 +4239,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>519886</v>
+        <v>520203</v>
       </c>
       <c r="R29" t="n">
-        <v>7001592</v>
+        <v>7001453</v>
       </c>
       <c r="S29" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4260,7 +4274,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4270,12 +4284,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:39</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran i hyggeskanten.</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4290,26 +4299,6 @@
       <c r="AH29" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4327,52 +4316,38 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129127084</v>
+        <v>129124933</v>
       </c>
       <c r="B30" t="n">
-        <v>98659</v>
+        <v>57725</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4381,13 +4356,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>520203</v>
+        <v>519886</v>
       </c>
       <c r="R30" t="n">
-        <v>7001453</v>
+        <v>7001592</v>
       </c>
       <c r="S30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4416,7 +4391,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4426,7 +4401,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>09:39</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran i hyggeskanten.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4441,6 +4421,26 @@
       <c r="AH30" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4461,7 +4461,7 @@
         <v>129135649</v>
       </c>
       <c r="B31" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4598,7 +4598,7 @@
         <v>129125106</v>
       </c>
       <c r="B32" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4725,7 +4725,7 @@
         <v>129128345</v>
       </c>
       <c r="B33" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4862,7 +4862,7 @@
         <v>129135770</v>
       </c>
       <c r="B34" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4993,7 +4993,7 @@
         <v>129128023</v>
       </c>
       <c r="B35" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5135,7 +5135,7 @@
         <v>129135454</v>
       </c>
       <c r="B36" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5274,48 +5274,62 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129135677</v>
+        <v>129128320</v>
       </c>
       <c r="B37" t="n">
-        <v>79035</v>
+        <v>98669</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>520346</v>
+        <v>520352</v>
       </c>
       <c r="R37" t="n">
-        <v>7001536</v>
+        <v>7001397</v>
       </c>
       <c r="S37" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5344,7 +5358,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5354,7 +5368,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Minst 10 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5365,6 +5384,11 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -5381,62 +5405,48 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129128320</v>
+        <v>129135677</v>
       </c>
       <c r="B38" t="n">
-        <v>98659</v>
+        <v>79039</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>520352</v>
+        <v>520346</v>
       </c>
       <c r="R38" t="n">
-        <v>7001397</v>
+        <v>7001536</v>
       </c>
       <c r="S38" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5465,7 +5475,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5475,12 +5485,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:20</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Minst 10 plantor inom ca 0,5 m2 yta.</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5491,11 +5496,6 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -5515,7 +5515,7 @@
         <v>129135697</v>
       </c>
       <c r="B39" t="n">
-        <v>80169</v>
+        <v>80173</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5652,7 +5652,7 @@
         <v>129193543</v>
       </c>
       <c r="B40" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5751,10 +5751,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129193558</v>
+        <v>129193518</v>
       </c>
       <c r="B41" t="n">
-        <v>80140</v>
+        <v>57725</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5762,21 +5762,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5786,10 +5786,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>520415</v>
+        <v>520676</v>
       </c>
       <c r="R41" t="n">
-        <v>7001416</v>
+        <v>7001377</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5822,6 +5822,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5848,10 +5853,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129193518</v>
+        <v>129193558</v>
       </c>
       <c r="B42" t="n">
-        <v>57723</v>
+        <v>80144</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5859,21 +5864,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5883,10 +5888,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>520676</v>
+        <v>520415</v>
       </c>
       <c r="R42" t="n">
-        <v>7001377</v>
+        <v>7001416</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5919,11 +5924,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5953,7 +5953,7 @@
         <v>129193568</v>
       </c>
       <c r="B43" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6047,10 +6047,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129193582</v>
+        <v>129193576</v>
       </c>
       <c r="B44" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6075,33 +6075,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>520388</v>
+        <v>520675</v>
       </c>
       <c r="R44" t="n">
-        <v>7001418</v>
+        <v>7001377</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6136,18 +6120,12 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Minst 50</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -6166,10 +6144,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129193576</v>
+        <v>129193582</v>
       </c>
       <c r="B45" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6194,17 +6172,33 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>520675</v>
+        <v>520388</v>
       </c>
       <c r="R45" t="n">
-        <v>7001377</v>
+        <v>7001418</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6239,12 +6233,18 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Minst 50</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -6263,61 +6263,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129193583</v>
+        <v>129193542</v>
       </c>
       <c r="B46" t="n">
-        <v>98659</v>
+        <v>57725</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>520338</v>
+        <v>520422</v>
       </c>
       <c r="R46" t="n">
-        <v>7001427</v>
+        <v>7001418</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6354,7 +6338,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Minst 100</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6363,7 +6347,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -6382,45 +6365,61 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129193542</v>
+        <v>129193583</v>
       </c>
       <c r="B47" t="n">
-        <v>57723</v>
+        <v>98669</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>520422</v>
+        <v>520338</v>
       </c>
       <c r="R47" t="n">
-        <v>7001418</v>
+        <v>7001427</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6457,7 +6456,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Minst 100</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6466,6 +6465,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -6487,7 +6487,7 @@
         <v>129193565</v>
       </c>
       <c r="B48" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6584,7 +6584,7 @@
         <v>129193591</v>
       </c>
       <c r="B49" t="n">
-        <v>92855</v>
+        <v>92862</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6678,10 +6678,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129193566</v>
+        <v>129193523</v>
       </c>
       <c r="B50" t="n">
-        <v>80140</v>
+        <v>57725</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6689,21 +6689,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6713,10 +6713,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>520180</v>
+        <v>520478</v>
       </c>
       <c r="R50" t="n">
-        <v>7001458</v>
+        <v>7001335</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6749,6 +6749,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6775,10 +6780,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129193590</v>
+        <v>129193517</v>
       </c>
       <c r="B51" t="n">
-        <v>79035</v>
+        <v>57725</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6786,21 +6791,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6810,10 +6815,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>520187</v>
+        <v>520301</v>
       </c>
       <c r="R51" t="n">
-        <v>7001471</v>
+        <v>7001547</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6846,6 +6851,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6872,45 +6882,61 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129193523</v>
+        <v>129193581</v>
       </c>
       <c r="B52" t="n">
-        <v>57723</v>
+        <v>98669</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>520478</v>
+        <v>520425</v>
       </c>
       <c r="R52" t="n">
-        <v>7001335</v>
+        <v>7001407</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6947,7 +6973,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Minst 80</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6956,6 +6982,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6974,10 +7001,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129193517</v>
+        <v>129193590</v>
       </c>
       <c r="B53" t="n">
-        <v>57723</v>
+        <v>79039</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6985,21 +7012,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -7009,10 +7036,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>520301</v>
+        <v>520187</v>
       </c>
       <c r="R53" t="n">
-        <v>7001547</v>
+        <v>7001471</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7045,11 +7072,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7076,61 +7098,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129193581</v>
+        <v>129193566</v>
       </c>
       <c r="B54" t="n">
-        <v>98659</v>
+        <v>80144</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>520425</v>
+        <v>520180</v>
       </c>
       <c r="R54" t="n">
-        <v>7001407</v>
+        <v>7001458</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7165,18 +7171,12 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Minst 80</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -7198,7 +7198,7 @@
         <v>129193570</v>
       </c>
       <c r="B55" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7295,7 +7295,7 @@
         <v>129193550</v>
       </c>
       <c r="B56" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7389,10 +7389,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129193561</v>
+        <v>129193524</v>
       </c>
       <c r="B57" t="n">
-        <v>80140</v>
+        <v>57725</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7400,21 +7400,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7424,10 +7424,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>520344</v>
+        <v>520478</v>
       </c>
       <c r="R57" t="n">
-        <v>7001402</v>
+        <v>7001328</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7460,6 +7460,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7486,10 +7491,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129193567</v>
+        <v>129193544</v>
       </c>
       <c r="B58" t="n">
-        <v>80140</v>
+        <v>57725</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7497,21 +7502,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7521,10 +7526,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>520184</v>
+        <v>520270</v>
       </c>
       <c r="R58" t="n">
-        <v>7001482</v>
+        <v>7001484</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7557,6 +7562,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7583,10 +7593,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129193544</v>
+        <v>129193561</v>
       </c>
       <c r="B59" t="n">
-        <v>57723</v>
+        <v>80144</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7594,21 +7604,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7618,10 +7628,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>520270</v>
+        <v>520344</v>
       </c>
       <c r="R59" t="n">
-        <v>7001484</v>
+        <v>7001402</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7654,11 +7664,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7685,10 +7690,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129193524</v>
+        <v>129193567</v>
       </c>
       <c r="B60" t="n">
-        <v>57723</v>
+        <v>80144</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7696,21 +7701,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7720,10 +7725,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>520478</v>
+        <v>520184</v>
       </c>
       <c r="R60" t="n">
-        <v>7001328</v>
+        <v>7001482</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7756,11 +7761,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7787,45 +7787,57 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129193564</v>
+        <v>129193585</v>
       </c>
       <c r="B61" t="n">
-        <v>80140</v>
+        <v>98669</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>520225</v>
+        <v>520122</v>
       </c>
       <c r="R61" t="n">
-        <v>7001483</v>
+        <v>7001476</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7860,12 +7872,18 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Fler än 200</t>
+        </is>
+      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7884,10 +7902,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129193557</v>
+        <v>129193564</v>
       </c>
       <c r="B62" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7919,10 +7937,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>520374</v>
+        <v>520225</v>
       </c>
       <c r="R62" t="n">
-        <v>7001329</v>
+        <v>7001483</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7981,57 +7999,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129193585</v>
+        <v>129193557</v>
       </c>
       <c r="B63" t="n">
-        <v>98659</v>
+        <v>80144</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>520122</v>
+        <v>520374</v>
       </c>
       <c r="R63" t="n">
-        <v>7001476</v>
+        <v>7001329</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8066,18 +8072,12 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Fler än 200</t>
-        </is>
-      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -8096,32 +8096,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129193560</v>
+        <v>129193593</v>
       </c>
       <c r="B64" t="n">
-        <v>80140</v>
+        <v>100857</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>222498</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -8131,10 +8131,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>520346</v>
+        <v>520101</v>
       </c>
       <c r="R64" t="n">
-        <v>7001396</v>
+        <v>7001658</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8193,10 +8193,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129193569</v>
+        <v>129193560</v>
       </c>
       <c r="B65" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8228,10 +8228,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>520094</v>
+        <v>520346</v>
       </c>
       <c r="R65" t="n">
-        <v>7001525</v>
+        <v>7001396</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8290,32 +8290,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129193593</v>
+        <v>129193569</v>
       </c>
       <c r="B66" t="n">
-        <v>100847</v>
+        <v>80144</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>222498</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -8325,10 +8325,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>520101</v>
+        <v>520094</v>
       </c>
       <c r="R66" t="n">
-        <v>7001658</v>
+        <v>7001525</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8387,10 +8387,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129193562</v>
+        <v>129193545</v>
       </c>
       <c r="B67" t="n">
-        <v>80140</v>
+        <v>57725</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8398,21 +8398,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8422,10 +8422,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>520335</v>
+        <v>519958</v>
       </c>
       <c r="R67" t="n">
-        <v>7001429</v>
+        <v>7001547</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8458,6 +8458,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8484,10 +8489,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129193545</v>
+        <v>129193562</v>
       </c>
       <c r="B68" t="n">
-        <v>57723</v>
+        <v>80144</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8495,21 +8500,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8519,10 +8524,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>519958</v>
+        <v>520335</v>
       </c>
       <c r="R68" t="n">
-        <v>7001547</v>
+        <v>7001429</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8555,11 +8560,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8586,46 +8586,46 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129193573</v>
+        <v>129193584</v>
       </c>
       <c r="B69" t="n">
-        <v>57827</v>
+        <v>98669</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>103031</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N69" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -8637,10 +8637,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>520153</v>
+        <v>520320</v>
       </c>
       <c r="R69" t="n">
-        <v>7001500</v>
+        <v>7001451</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8675,12 +8675,18 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Minst 100</t>
+        </is>
+      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -8699,46 +8705,46 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129193584</v>
+        <v>129193573</v>
       </c>
       <c r="B70" t="n">
-        <v>98659</v>
+        <v>57829</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>103031</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N70" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -8750,10 +8756,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>520320</v>
+        <v>520153</v>
       </c>
       <c r="R70" t="n">
-        <v>7001451</v>
+        <v>7001500</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8788,18 +8794,12 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Minst 100</t>
-        </is>
-      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -8821,7 +8821,7 @@
         <v>129193563</v>
       </c>
       <c r="B71" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8918,7 +8918,7 @@
         <v>129193548</v>
       </c>
       <c r="B72" t="n">
-        <v>92464</v>
+        <v>92471</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9015,7 +9015,7 @@
         <v>129193559</v>
       </c>
       <c r="B73" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9112,7 +9112,7 @@
         <v>129193546</v>
       </c>
       <c r="B74" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9214,7 +9214,7 @@
         <v>129193575</v>
       </c>
       <c r="B75" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9333,7 +9333,7 @@
         <v>129193549</v>
       </c>
       <c r="B76" t="n">
-        <v>80141</v>
+        <v>80145</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 43533-2025 artfynd.xlsx
+++ b/artfynd/A 43533-2025 artfynd.xlsx
@@ -1851,10 +1851,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129126617</v>
+        <v>129128175</v>
       </c>
       <c r="B11" t="n">
-        <v>80144</v>
+        <v>79039</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1862,42 +1862,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>520219</v>
+        <v>520329</v>
       </c>
       <c r="R11" t="n">
-        <v>7001429</v>
+        <v>7001400</v>
       </c>
       <c r="S11" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1926,7 +1921,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1936,7 +1931,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1950,17 +1945,17 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1978,10 +1973,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129127736</v>
+        <v>129126617</v>
       </c>
       <c r="B12" t="n">
-        <v>57725</v>
+        <v>80144</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1989,27 +1984,27 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -2018,13 +2013,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>520237</v>
+        <v>520219</v>
       </c>
       <c r="R12" t="n">
-        <v>7001416</v>
+        <v>7001429</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2053,7 +2048,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2063,12 +2058,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:01</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2080,29 +2070,19 @@
       <c r="AG12" t="b">
         <v>0</v>
       </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2120,10 +2100,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129128175</v>
+        <v>129127736</v>
       </c>
       <c r="B13" t="n">
-        <v>79039</v>
+        <v>57725</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2131,37 +2111,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>520329</v>
+        <v>520237</v>
       </c>
       <c r="R13" t="n">
-        <v>7001400</v>
+        <v>7001416</v>
       </c>
       <c r="S13" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2190,7 +2175,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2200,7 +2185,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2212,6 +2202,11 @@
       <c r="AG13" t="b">
         <v>0</v>
       </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AJ13" t="inlineStr">
         <is>
           <t>gran</t>
@@ -2222,9 +2217,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2505,10 +2505,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129127604</v>
+        <v>129128148</v>
       </c>
       <c r="B16" t="n">
-        <v>80144</v>
+        <v>80145</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2516,27 +2516,27 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2545,13 +2545,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>520243</v>
+        <v>520338</v>
       </c>
       <c r="R16" t="n">
-        <v>7001423</v>
+        <v>7001407</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2590,12 +2590,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:59</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Fertil lunglav på en sälg med doftticka.</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2609,27 +2604,27 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark of dead wood # Betula</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2647,7 +2642,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129128162</v>
+        <v>129127604</v>
       </c>
       <c r="B17" t="n">
         <v>80144</v>
@@ -2678,7 +2673,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2687,13 +2682,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>520355</v>
+        <v>520243</v>
       </c>
       <c r="R17" t="n">
-        <v>7001412</v>
+        <v>7001423</v>
       </c>
       <c r="S17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2722,7 +2717,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2732,7 +2727,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Fertil lunglav på en sälg med doftticka.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -2784,10 +2784,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129128148</v>
+        <v>129128162</v>
       </c>
       <c r="B18" t="n">
-        <v>80145</v>
+        <v>80144</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2795,21 +2795,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2824,13 +2824,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>520338</v>
+        <v>520355</v>
       </c>
       <c r="R18" t="n">
-        <v>7001407</v>
+        <v>7001412</v>
       </c>
       <c r="S18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2888,22 +2888,22 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Betula</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -3174,10 +3174,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129126633</v>
+        <v>129125122</v>
       </c>
       <c r="B21" t="n">
-        <v>80144</v>
+        <v>79039</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3185,21 +3185,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3209,13 +3209,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>520226</v>
+        <v>519973</v>
       </c>
       <c r="R21" t="n">
-        <v>7001438</v>
+        <v>7001540</v>
       </c>
       <c r="S21" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3242,26 +3242,11 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>11:19</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>11:19</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På grovbarkad gammal asp.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3270,31 +3255,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3311,10 +3271,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129125122</v>
+        <v>129126633</v>
       </c>
       <c r="B22" t="n">
-        <v>79039</v>
+        <v>80144</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3322,21 +3282,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3346,13 +3306,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>519973</v>
+        <v>520226</v>
       </c>
       <c r="R22" t="n">
-        <v>7001540</v>
+        <v>7001438</v>
       </c>
       <c r="S22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3379,11 +3339,26 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På grovbarkad gammal asp.</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3392,6 +3367,31 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -4053,10 +4053,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129131418</v>
+        <v>129124933</v>
       </c>
       <c r="B28" t="n">
-        <v>79039</v>
+        <v>57725</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4064,37 +4064,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>520682</v>
+        <v>519886</v>
       </c>
       <c r="R28" t="n">
-        <v>7001354</v>
+        <v>7001592</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4123,7 +4128,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4133,7 +4138,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>09:39</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran i hyggeskanten.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4147,7 +4157,7 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
@@ -4162,12 +4172,12 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4185,67 +4195,48 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129127084</v>
+        <v>129131418</v>
       </c>
       <c r="B29" t="n">
-        <v>98669</v>
+        <v>79039</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>520203</v>
+        <v>520682</v>
       </c>
       <c r="R29" t="n">
-        <v>7001453</v>
+        <v>7001354</v>
       </c>
       <c r="S29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4274,7 +4265,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4284,7 +4275,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4298,7 +4289,27 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4316,38 +4327,52 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129124933</v>
+        <v>129127084</v>
       </c>
       <c r="B30" t="n">
-        <v>57725</v>
+        <v>98669</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4356,13 +4381,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>519886</v>
+        <v>520203</v>
       </c>
       <c r="R30" t="n">
-        <v>7001592</v>
+        <v>7001453</v>
       </c>
       <c r="S30" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4391,7 +4416,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4401,12 +4426,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:39</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran i hyggeskanten.</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4421,26 +4441,6 @@
       <c r="AH30" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -6263,45 +6263,61 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129193542</v>
+        <v>129193583</v>
       </c>
       <c r="B46" t="n">
-        <v>57725</v>
+        <v>98669</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>520422</v>
+        <v>520338</v>
       </c>
       <c r="R46" t="n">
-        <v>7001418</v>
+        <v>7001427</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6338,7 +6354,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Minst 100</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6347,6 +6363,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -6365,61 +6382,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129193583</v>
+        <v>129193542</v>
       </c>
       <c r="B47" t="n">
-        <v>98669</v>
+        <v>57725</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>520338</v>
+        <v>520422</v>
       </c>
       <c r="R47" t="n">
-        <v>7001427</v>
+        <v>7001418</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6456,7 +6457,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Minst 100</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6465,7 +6466,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 43533-2025 artfynd.xlsx
+++ b/artfynd/A 43533-2025 artfynd.xlsx
@@ -817,38 +817,47 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129135852</v>
+        <v>129135545</v>
       </c>
       <c r="B3" t="n">
-        <v>99003</v>
+        <v>98676</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219880</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>gulnande löv/blad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -857,10 +866,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>520213</v>
+        <v>520564</v>
       </c>
       <c r="R3" t="n">
-        <v>7001609</v>
+        <v>7001441</v>
       </c>
       <c r="S3" t="n">
         <v>9</v>
@@ -892,7 +901,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -902,7 +911,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -934,47 +943,38 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129135545</v>
+        <v>129135852</v>
       </c>
       <c r="B4" t="n">
-        <v>98669</v>
+        <v>99010</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>219880</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>gulnande löv/blad</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -983,10 +983,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>520564</v>
+        <v>520213</v>
       </c>
       <c r="R4" t="n">
-        <v>7001441</v>
+        <v>7001609</v>
       </c>
       <c r="S4" t="n">
         <v>9</v>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1479,7 +1479,7 @@
         <v>129126843</v>
       </c>
       <c r="B8" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>129135867</v>
       </c>
       <c r="B10" t="n">
-        <v>100857</v>
+        <v>100864</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2382,7 +2382,7 @@
         <v>129135822</v>
       </c>
       <c r="B15" t="n">
-        <v>104137</v>
+        <v>104144</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2921,62 +2921,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129127509</v>
+        <v>129131389</v>
       </c>
       <c r="B19" t="n">
-        <v>92110</v>
+        <v>79039</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>520242</v>
+        <v>520611</v>
       </c>
       <c r="R19" t="n">
-        <v>7001434</v>
+        <v>7001285</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3005,7 +2991,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3015,7 +3001,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3026,31 +3012,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Salix caprea</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -3067,48 +3028,62 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129131389</v>
+        <v>129127509</v>
       </c>
       <c r="B20" t="n">
-        <v>79039</v>
+        <v>92117</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>520611</v>
+        <v>520242</v>
       </c>
       <c r="R20" t="n">
-        <v>7001285</v>
+        <v>7001434</v>
       </c>
       <c r="S20" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3137,7 +3112,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3147,7 +3122,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3158,6 +3133,31 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Salix caprea</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -3408,10 +3408,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129128128</v>
+        <v>129136001</v>
       </c>
       <c r="B23" t="n">
-        <v>80145</v>
+        <v>79039</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3419,42 +3419,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>520340</v>
+        <v>520012</v>
       </c>
       <c r="R23" t="n">
-        <v>7001392</v>
+        <v>7001652</v>
       </c>
       <c r="S23" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3483,7 +3478,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3493,7 +3488,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3504,31 +3499,6 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3677,10 +3647,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129136001</v>
+        <v>129128128</v>
       </c>
       <c r="B25" t="n">
-        <v>79039</v>
+        <v>80145</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3688,37 +3658,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>520012</v>
+        <v>520340</v>
       </c>
       <c r="R25" t="n">
-        <v>7001652</v>
+        <v>7001392</v>
       </c>
       <c r="S25" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3747,7 +3722,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3757,7 +3732,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3768,6 +3743,31 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -4053,38 +4053,52 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129124933</v>
+        <v>129127084</v>
       </c>
       <c r="B28" t="n">
-        <v>57725</v>
+        <v>98676</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -4093,13 +4107,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>519886</v>
+        <v>520203</v>
       </c>
       <c r="R28" t="n">
-        <v>7001592</v>
+        <v>7001453</v>
       </c>
       <c r="S28" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4128,7 +4142,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4138,12 +4152,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:39</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran i hyggeskanten.</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4158,26 +4167,6 @@
       <c r="AH28" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4327,52 +4316,38 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129127084</v>
+        <v>129124933</v>
       </c>
       <c r="B30" t="n">
-        <v>98669</v>
+        <v>57725</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4381,13 +4356,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>520203</v>
+        <v>519886</v>
       </c>
       <c r="R30" t="n">
-        <v>7001453</v>
+        <v>7001592</v>
       </c>
       <c r="S30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4416,7 +4391,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4426,7 +4401,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>09:39</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran i hyggeskanten.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4441,6 +4421,26 @@
       <c r="AH30" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4862,7 +4862,7 @@
         <v>129135770</v>
       </c>
       <c r="B34" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5277,7 +5277,7 @@
         <v>129128320</v>
       </c>
       <c r="B37" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -6050,7 +6050,7 @@
         <v>129193576</v>
       </c>
       <c r="B44" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6147,7 +6147,7 @@
         <v>129193582</v>
       </c>
       <c r="B45" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6263,61 +6263,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129193583</v>
+        <v>129193542</v>
       </c>
       <c r="B46" t="n">
-        <v>98669</v>
+        <v>57725</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>520338</v>
+        <v>520422</v>
       </c>
       <c r="R46" t="n">
-        <v>7001427</v>
+        <v>7001418</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6354,7 +6338,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Minst 100</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6363,7 +6347,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -6382,45 +6365,61 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129193542</v>
+        <v>129193583</v>
       </c>
       <c r="B47" t="n">
-        <v>57725</v>
+        <v>98676</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>520422</v>
+        <v>520338</v>
       </c>
       <c r="R47" t="n">
-        <v>7001418</v>
+        <v>7001427</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6457,7 +6456,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Minst 100</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6466,6 +6465,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -6584,7 +6584,7 @@
         <v>129193591</v>
       </c>
       <c r="B49" t="n">
-        <v>92862</v>
+        <v>92869</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6678,10 +6678,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129193523</v>
+        <v>129193590</v>
       </c>
       <c r="B50" t="n">
-        <v>57725</v>
+        <v>79039</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6689,21 +6689,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6713,10 +6713,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>520478</v>
+        <v>520187</v>
       </c>
       <c r="R50" t="n">
-        <v>7001335</v>
+        <v>7001471</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6749,11 +6749,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6780,10 +6775,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129193517</v>
+        <v>129193566</v>
       </c>
       <c r="B51" t="n">
-        <v>57725</v>
+        <v>80144</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6791,21 +6786,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6815,10 +6810,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>520301</v>
+        <v>520180</v>
       </c>
       <c r="R51" t="n">
-        <v>7001547</v>
+        <v>7001458</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6851,11 +6846,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6885,7 +6875,7 @@
         <v>129193581</v>
       </c>
       <c r="B52" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7001,10 +6991,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129193590</v>
+        <v>129193523</v>
       </c>
       <c r="B53" t="n">
-        <v>79039</v>
+        <v>57725</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7012,21 +7002,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -7036,10 +7026,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>520187</v>
+        <v>520478</v>
       </c>
       <c r="R53" t="n">
-        <v>7001471</v>
+        <v>7001335</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7072,6 +7062,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7098,10 +7093,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129193566</v>
+        <v>129193517</v>
       </c>
       <c r="B54" t="n">
-        <v>80144</v>
+        <v>57725</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7109,21 +7104,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -7133,10 +7128,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>520180</v>
+        <v>520301</v>
       </c>
       <c r="R54" t="n">
-        <v>7001458</v>
+        <v>7001547</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7169,6 +7164,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7389,10 +7389,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129193524</v>
+        <v>129193561</v>
       </c>
       <c r="B57" t="n">
-        <v>57725</v>
+        <v>80144</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7400,21 +7400,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7424,10 +7424,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>520478</v>
+        <v>520344</v>
       </c>
       <c r="R57" t="n">
-        <v>7001328</v>
+        <v>7001402</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7460,11 +7460,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7491,10 +7486,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129193544</v>
+        <v>129193567</v>
       </c>
       <c r="B58" t="n">
-        <v>57725</v>
+        <v>80144</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7502,21 +7497,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7526,10 +7521,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>520270</v>
+        <v>520184</v>
       </c>
       <c r="R58" t="n">
-        <v>7001484</v>
+        <v>7001482</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7562,11 +7557,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7593,10 +7583,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129193561</v>
+        <v>129193524</v>
       </c>
       <c r="B59" t="n">
-        <v>80144</v>
+        <v>57725</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7604,21 +7594,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7628,10 +7618,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>520344</v>
+        <v>520478</v>
       </c>
       <c r="R59" t="n">
-        <v>7001402</v>
+        <v>7001328</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7664,6 +7654,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7690,10 +7685,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129193567</v>
+        <v>129193544</v>
       </c>
       <c r="B60" t="n">
-        <v>80144</v>
+        <v>57725</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7701,21 +7696,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7725,10 +7720,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>520184</v>
+        <v>520270</v>
       </c>
       <c r="R60" t="n">
-        <v>7001482</v>
+        <v>7001484</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7761,6 +7756,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7787,57 +7787,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129193585</v>
+        <v>129193564</v>
       </c>
       <c r="B61" t="n">
-        <v>98669</v>
+        <v>80144</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>520122</v>
+        <v>520225</v>
       </c>
       <c r="R61" t="n">
-        <v>7001476</v>
+        <v>7001483</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7872,18 +7860,12 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Fler än 200</t>
-        </is>
-      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7902,45 +7884,57 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129193564</v>
+        <v>129193585</v>
       </c>
       <c r="B62" t="n">
-        <v>80144</v>
+        <v>98676</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>520225</v>
+        <v>520122</v>
       </c>
       <c r="R62" t="n">
-        <v>7001483</v>
+        <v>7001476</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7975,12 +7969,18 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Fler än 200</t>
+        </is>
+      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -8096,32 +8096,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129193593</v>
+        <v>129193560</v>
       </c>
       <c r="B64" t="n">
-        <v>100857</v>
+        <v>80144</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>222498</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -8131,10 +8131,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>520101</v>
+        <v>520346</v>
       </c>
       <c r="R64" t="n">
-        <v>7001658</v>
+        <v>7001396</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8193,7 +8193,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129193560</v>
+        <v>129193569</v>
       </c>
       <c r="B65" t="n">
         <v>80144</v>
@@ -8228,10 +8228,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>520346</v>
+        <v>520094</v>
       </c>
       <c r="R65" t="n">
-        <v>7001396</v>
+        <v>7001525</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8290,32 +8290,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129193569</v>
+        <v>129193593</v>
       </c>
       <c r="B66" t="n">
-        <v>80144</v>
+        <v>100864</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>222498</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -8325,10 +8325,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>520094</v>
+        <v>520101</v>
       </c>
       <c r="R66" t="n">
-        <v>7001525</v>
+        <v>7001658</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8387,10 +8387,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129193545</v>
+        <v>129193562</v>
       </c>
       <c r="B67" t="n">
-        <v>57725</v>
+        <v>80144</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8398,21 +8398,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8422,10 +8422,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>519958</v>
+        <v>520335</v>
       </c>
       <c r="R67" t="n">
-        <v>7001547</v>
+        <v>7001429</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8458,11 +8458,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8489,10 +8484,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129193562</v>
+        <v>129193545</v>
       </c>
       <c r="B68" t="n">
-        <v>80144</v>
+        <v>57725</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8500,21 +8495,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8524,10 +8519,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>520335</v>
+        <v>519958</v>
       </c>
       <c r="R68" t="n">
-        <v>7001429</v>
+        <v>7001547</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8560,6 +8555,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8589,7 +8589,7 @@
         <v>129193584</v>
       </c>
       <c r="B69" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8918,7 +8918,7 @@
         <v>129193548</v>
       </c>
       <c r="B72" t="n">
-        <v>92471</v>
+        <v>92478</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9109,45 +9109,61 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129193546</v>
+        <v>129193575</v>
       </c>
       <c r="B74" t="n">
-        <v>57725</v>
+        <v>98676</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>519958</v>
+        <v>520528</v>
       </c>
       <c r="R74" t="n">
-        <v>7001542</v>
+        <v>7001465</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9184,7 +9200,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Minst 50</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9193,6 +9209,7 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -9211,61 +9228,45 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129193575</v>
+        <v>129193549</v>
       </c>
       <c r="B75" t="n">
-        <v>98669</v>
+        <v>80145</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="N75" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>520528</v>
+        <v>520345</v>
       </c>
       <c r="R75" t="n">
-        <v>7001465</v>
+        <v>7001396</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9300,18 +9301,12 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Minst 50</t>
-        </is>
-      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -9330,10 +9325,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129193549</v>
+        <v>129193546</v>
       </c>
       <c r="B76" t="n">
-        <v>80145</v>
+        <v>57725</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9341,21 +9336,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9365,10 +9360,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>520345</v>
+        <v>519958</v>
       </c>
       <c r="R76" t="n">
-        <v>7001396</v>
+        <v>7001542</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9401,6 +9396,11 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD76" t="b">

--- a/artfynd/A 43533-2025 artfynd.xlsx
+++ b/artfynd/A 43533-2025 artfynd.xlsx
@@ -675,38 +675,47 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129126527</v>
+        <v>129135545</v>
       </c>
       <c r="B2" t="n">
-        <v>80144</v>
+        <v>98678</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -715,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>520189</v>
+        <v>520564</v>
       </c>
       <c r="R2" t="n">
-        <v>7001448</v>
+        <v>7001441</v>
       </c>
       <c r="S2" t="n">
         <v>9</v>
@@ -750,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:12</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,27 +783,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -817,47 +801,38 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129135545</v>
+        <v>129135852</v>
       </c>
       <c r="B3" t="n">
-        <v>98676</v>
+        <v>99012</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>219880</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>gulnande löv/blad</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -866,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>520564</v>
+        <v>520213</v>
       </c>
       <c r="R3" t="n">
-        <v>7001441</v>
+        <v>7001609</v>
       </c>
       <c r="S3" t="n">
         <v>9</v>
@@ -901,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -911,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -943,38 +918,38 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129135852</v>
+        <v>129126527</v>
       </c>
       <c r="B4" t="n">
-        <v>99010</v>
+        <v>80146</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219880</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>gulnande löv/blad</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -983,10 +958,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>520213</v>
+        <v>520189</v>
       </c>
       <c r="R4" t="n">
-        <v>7001609</v>
+        <v>7001448</v>
       </c>
       <c r="S4" t="n">
         <v>9</v>
@@ -1018,7 +993,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1028,7 +1003,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1042,7 +1022,27 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1063,7 +1063,7 @@
         <v>129131270</v>
       </c>
       <c r="B5" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1185,7 +1185,7 @@
         <v>129127182</v>
       </c>
       <c r="B6" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>129131350</v>
       </c>
       <c r="B7" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>129126843</v>
       </c>
       <c r="B8" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1615,7 +1615,7 @@
         <v>129135692</v>
       </c>
       <c r="B9" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>129135867</v>
       </c>
       <c r="B10" t="n">
-        <v>100864</v>
+        <v>100866</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1851,10 +1851,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129128175</v>
+        <v>129126617</v>
       </c>
       <c r="B11" t="n">
-        <v>79039</v>
+        <v>80146</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1862,37 +1862,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>520329</v>
+        <v>520219</v>
       </c>
       <c r="R11" t="n">
-        <v>7001400</v>
+        <v>7001429</v>
       </c>
       <c r="S11" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1921,7 +1926,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1931,7 +1936,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1945,17 +1950,17 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1973,10 +1978,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129126617</v>
+        <v>129128175</v>
       </c>
       <c r="B12" t="n">
-        <v>80144</v>
+        <v>79041</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1984,42 +1989,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>520219</v>
+        <v>520329</v>
       </c>
       <c r="R12" t="n">
-        <v>7001429</v>
+        <v>7001400</v>
       </c>
       <c r="S12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2048,7 +2048,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2058,7 +2058,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2072,17 +2072,17 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2103,7 +2103,7 @@
         <v>129127736</v>
       </c>
       <c r="B13" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         <v>129126547</v>
       </c>
       <c r="B14" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2382,7 +2382,7 @@
         <v>129135822</v>
       </c>
       <c r="B15" t="n">
-        <v>104144</v>
+        <v>104146</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2505,10 +2505,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129128148</v>
+        <v>129127604</v>
       </c>
       <c r="B16" t="n">
-        <v>80145</v>
+        <v>80146</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2516,27 +2516,27 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2545,13 +2545,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>520338</v>
+        <v>520243</v>
       </c>
       <c r="R16" t="n">
-        <v>7001407</v>
+        <v>7001423</v>
       </c>
       <c r="S16" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2590,7 +2590,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Fertil lunglav på en sälg med doftticka.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2604,27 +2609,27 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Betula</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2642,10 +2647,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129127604</v>
+        <v>129128162</v>
       </c>
       <c r="B17" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2673,7 +2678,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2682,13 +2687,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>520243</v>
+        <v>520355</v>
       </c>
       <c r="R17" t="n">
-        <v>7001423</v>
+        <v>7001412</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2717,7 +2722,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2727,12 +2732,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:59</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Fertil lunglav på en sälg med doftticka.</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -2784,10 +2784,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129128162</v>
+        <v>129128148</v>
       </c>
       <c r="B18" t="n">
-        <v>80144</v>
+        <v>80147</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2795,21 +2795,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2824,13 +2824,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>520355</v>
+        <v>520338</v>
       </c>
       <c r="R18" t="n">
-        <v>7001412</v>
+        <v>7001407</v>
       </c>
       <c r="S18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2888,22 +2888,22 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark of dead wood # Betula</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2921,48 +2921,62 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129131389</v>
+        <v>129127509</v>
       </c>
       <c r="B19" t="n">
-        <v>79039</v>
+        <v>92119</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>520611</v>
+        <v>520242</v>
       </c>
       <c r="R19" t="n">
-        <v>7001285</v>
+        <v>7001434</v>
       </c>
       <c r="S19" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2991,7 +3005,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3001,7 +3015,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3012,6 +3026,31 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Salix caprea</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -3028,62 +3067,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129127509</v>
+        <v>129131389</v>
       </c>
       <c r="B20" t="n">
-        <v>92117</v>
+        <v>79041</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>520242</v>
+        <v>520611</v>
       </c>
       <c r="R20" t="n">
-        <v>7001434</v>
+        <v>7001285</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3112,7 +3137,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3122,7 +3147,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3133,31 +3158,6 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Salix caprea</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -3177,7 +3177,7 @@
         <v>129125122</v>
       </c>
       <c r="B21" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
         <v>129126633</v>
       </c>
       <c r="B22" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3408,10 +3408,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129136001</v>
+        <v>129128128</v>
       </c>
       <c r="B23" t="n">
-        <v>79039</v>
+        <v>80147</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3419,37 +3419,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>520012</v>
+        <v>520340</v>
       </c>
       <c r="R23" t="n">
-        <v>7001652</v>
+        <v>7001392</v>
       </c>
       <c r="S23" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3478,7 +3483,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3488,7 +3493,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3499,6 +3504,31 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3515,10 +3545,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129126703</v>
+        <v>129136001</v>
       </c>
       <c r="B24" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3550,13 +3580,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>520253</v>
+        <v>520012</v>
       </c>
       <c r="R24" t="n">
-        <v>7001454</v>
+        <v>7001652</v>
       </c>
       <c r="S24" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3585,7 +3615,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3595,7 +3625,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3606,31 +3636,6 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3647,10 +3652,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129128128</v>
+        <v>129126703</v>
       </c>
       <c r="B25" t="n">
-        <v>80145</v>
+        <v>79041</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3658,39 +3663,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>520340</v>
+        <v>520253</v>
       </c>
       <c r="R25" t="n">
-        <v>7001392</v>
+        <v>7001454</v>
       </c>
       <c r="S25" t="n">
         <v>9</v>
@@ -3722,7 +3722,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3732,7 +3732,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3746,27 +3746,27 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3787,7 +3787,7 @@
         <v>129131479</v>
       </c>
       <c r="B26" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3919,7 +3919,7 @@
         <v>129127211</v>
       </c>
       <c r="B27" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4053,67 +4053,48 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129127084</v>
+        <v>129131418</v>
       </c>
       <c r="B28" t="n">
-        <v>98676</v>
+        <v>79041</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>520203</v>
+        <v>520682</v>
       </c>
       <c r="R28" t="n">
-        <v>7001453</v>
+        <v>7001354</v>
       </c>
       <c r="S28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4142,7 +4123,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4152,7 +4133,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4166,7 +4147,27 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4184,10 +4185,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129131418</v>
+        <v>129124933</v>
       </c>
       <c r="B29" t="n">
-        <v>79039</v>
+        <v>57727</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4195,37 +4196,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>520682</v>
+        <v>519886</v>
       </c>
       <c r="R29" t="n">
-        <v>7001354</v>
+        <v>7001592</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4254,7 +4260,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4264,7 +4270,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>09:39</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran i hyggeskanten.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4278,7 +4289,7 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
@@ -4293,12 +4304,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4316,38 +4327,52 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129124933</v>
+        <v>129127084</v>
       </c>
       <c r="B30" t="n">
-        <v>57725</v>
+        <v>98678</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4356,13 +4381,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>519886</v>
+        <v>520203</v>
       </c>
       <c r="R30" t="n">
-        <v>7001592</v>
+        <v>7001453</v>
       </c>
       <c r="S30" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4391,7 +4416,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4401,12 +4426,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:39</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran i hyggeskanten.</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4421,26 +4441,6 @@
       <c r="AH30" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4461,7 +4461,7 @@
         <v>129135649</v>
       </c>
       <c r="B31" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4598,7 +4598,7 @@
         <v>129125106</v>
       </c>
       <c r="B32" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4725,7 +4725,7 @@
         <v>129128345</v>
       </c>
       <c r="B33" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4862,7 +4862,7 @@
         <v>129135770</v>
       </c>
       <c r="B34" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4993,7 +4993,7 @@
         <v>129128023</v>
       </c>
       <c r="B35" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5135,7 +5135,7 @@
         <v>129135454</v>
       </c>
       <c r="B36" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5274,62 +5274,48 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129128320</v>
+        <v>129135677</v>
       </c>
       <c r="B37" t="n">
-        <v>98676</v>
+        <v>79041</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>520352</v>
+        <v>520346</v>
       </c>
       <c r="R37" t="n">
-        <v>7001397</v>
+        <v>7001536</v>
       </c>
       <c r="S37" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5358,7 +5344,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5368,12 +5354,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:20</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Minst 10 plantor inom ca 0,5 m2 yta.</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5384,11 +5365,6 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -5405,48 +5381,62 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129135677</v>
+        <v>129128320</v>
       </c>
       <c r="B38" t="n">
-        <v>79039</v>
+        <v>98678</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>520346</v>
+        <v>520352</v>
       </c>
       <c r="R38" t="n">
-        <v>7001536</v>
+        <v>7001397</v>
       </c>
       <c r="S38" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5475,7 +5465,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5485,7 +5475,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Minst 10 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5496,6 +5491,11 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -5515,7 +5515,7 @@
         <v>129135697</v>
       </c>
       <c r="B39" t="n">
-        <v>80173</v>
+        <v>80175</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5652,7 +5652,7 @@
         <v>129193543</v>
       </c>
       <c r="B40" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5751,10 +5751,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129193518</v>
+        <v>129193558</v>
       </c>
       <c r="B41" t="n">
-        <v>57725</v>
+        <v>80146</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5762,21 +5762,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5786,10 +5786,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>520676</v>
+        <v>520415</v>
       </c>
       <c r="R41" t="n">
-        <v>7001377</v>
+        <v>7001416</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5822,11 +5822,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5853,10 +5848,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129193558</v>
+        <v>129193518</v>
       </c>
       <c r="B42" t="n">
-        <v>80144</v>
+        <v>57727</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5864,21 +5859,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5888,10 +5883,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>520415</v>
+        <v>520676</v>
       </c>
       <c r="R42" t="n">
-        <v>7001416</v>
+        <v>7001377</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5924,6 +5919,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5953,7 +5953,7 @@
         <v>129193568</v>
       </c>
       <c r="B43" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6050,7 +6050,7 @@
         <v>129193576</v>
       </c>
       <c r="B44" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6147,7 +6147,7 @@
         <v>129193582</v>
       </c>
       <c r="B45" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6263,45 +6263,61 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129193542</v>
+        <v>129193583</v>
       </c>
       <c r="B46" t="n">
-        <v>57725</v>
+        <v>98678</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>520422</v>
+        <v>520338</v>
       </c>
       <c r="R46" t="n">
-        <v>7001418</v>
+        <v>7001427</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6338,7 +6354,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Minst 100</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6347,6 +6363,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -6365,61 +6382,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129193583</v>
+        <v>129193542</v>
       </c>
       <c r="B47" t="n">
-        <v>98676</v>
+        <v>57727</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>520338</v>
+        <v>520422</v>
       </c>
       <c r="R47" t="n">
-        <v>7001427</v>
+        <v>7001418</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6456,7 +6457,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Minst 100</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6465,7 +6466,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -6487,7 +6487,7 @@
         <v>129193565</v>
       </c>
       <c r="B48" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6584,7 +6584,7 @@
         <v>129193591</v>
       </c>
       <c r="B49" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6681,7 +6681,7 @@
         <v>129193590</v>
       </c>
       <c r="B50" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6775,10 +6775,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129193566</v>
+        <v>129193523</v>
       </c>
       <c r="B51" t="n">
-        <v>80144</v>
+        <v>57727</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6786,21 +6786,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6810,10 +6810,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>520180</v>
+        <v>520478</v>
       </c>
       <c r="R51" t="n">
-        <v>7001458</v>
+        <v>7001335</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6846,6 +6846,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6872,61 +6877,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129193581</v>
+        <v>129193517</v>
       </c>
       <c r="B52" t="n">
-        <v>98676</v>
+        <v>57727</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>520425</v>
+        <v>520301</v>
       </c>
       <c r="R52" t="n">
-        <v>7001407</v>
+        <v>7001547</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6963,7 +6952,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Minst 80</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6972,7 +6961,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6991,45 +6979,61 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129193523</v>
+        <v>129193581</v>
       </c>
       <c r="B53" t="n">
-        <v>57725</v>
+        <v>98678</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>520478</v>
+        <v>520425</v>
       </c>
       <c r="R53" t="n">
-        <v>7001335</v>
+        <v>7001407</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7066,7 +7070,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Minst 80</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7075,6 +7079,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -7093,10 +7098,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129193517</v>
+        <v>129193566</v>
       </c>
       <c r="B54" t="n">
-        <v>57725</v>
+        <v>80146</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7104,21 +7109,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -7128,10 +7133,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>520301</v>
+        <v>520180</v>
       </c>
       <c r="R54" t="n">
-        <v>7001547</v>
+        <v>7001458</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7164,11 +7169,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7198,7 +7198,7 @@
         <v>129193570</v>
       </c>
       <c r="B55" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7295,7 +7295,7 @@
         <v>129193550</v>
       </c>
       <c r="B56" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7392,7 +7392,7 @@
         <v>129193561</v>
       </c>
       <c r="B57" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7489,7 +7489,7 @@
         <v>129193567</v>
       </c>
       <c r="B58" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7586,7 +7586,7 @@
         <v>129193524</v>
       </c>
       <c r="B59" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         <v>129193544</v>
       </c>
       <c r="B60" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7790,7 +7790,7 @@
         <v>129193564</v>
       </c>
       <c r="B61" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7884,57 +7884,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129193585</v>
+        <v>129193557</v>
       </c>
       <c r="B62" t="n">
-        <v>98676</v>
+        <v>80146</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>520122</v>
+        <v>520374</v>
       </c>
       <c r="R62" t="n">
-        <v>7001476</v>
+        <v>7001329</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7969,18 +7957,12 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Fler än 200</t>
-        </is>
-      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -7999,45 +7981,57 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129193557</v>
+        <v>129193585</v>
       </c>
       <c r="B63" t="n">
-        <v>80144</v>
+        <v>98678</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>520374</v>
+        <v>520122</v>
       </c>
       <c r="R63" t="n">
-        <v>7001329</v>
+        <v>7001476</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8072,12 +8066,18 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Fler än 200</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -8099,7 +8099,7 @@
         <v>129193560</v>
       </c>
       <c r="B64" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8196,7 +8196,7 @@
         <v>129193569</v>
       </c>
       <c r="B65" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8293,7 +8293,7 @@
         <v>129193593</v>
       </c>
       <c r="B66" t="n">
-        <v>100864</v>
+        <v>100866</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8390,7 +8390,7 @@
         <v>129193562</v>
       </c>
       <c r="B67" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8487,7 +8487,7 @@
         <v>129193545</v>
       </c>
       <c r="B68" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8586,46 +8586,46 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129193584</v>
+        <v>129193573</v>
       </c>
       <c r="B69" t="n">
-        <v>98676</v>
+        <v>57831</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>103031</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N69" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -8637,10 +8637,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>520320</v>
+        <v>520153</v>
       </c>
       <c r="R69" t="n">
-        <v>7001451</v>
+        <v>7001500</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8675,18 +8675,12 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Minst 100</t>
-        </is>
-      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -8705,46 +8699,46 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129193573</v>
+        <v>129193584</v>
       </c>
       <c r="B70" t="n">
-        <v>57829</v>
+        <v>98678</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>103031</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N70" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -8756,10 +8750,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>520153</v>
+        <v>520320</v>
       </c>
       <c r="R70" t="n">
-        <v>7001500</v>
+        <v>7001451</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8794,12 +8788,18 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Minst 100</t>
+        </is>
+      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -8821,7 +8821,7 @@
         <v>129193563</v>
       </c>
       <c r="B71" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8918,7 +8918,7 @@
         <v>129193548</v>
       </c>
       <c r="B72" t="n">
-        <v>92478</v>
+        <v>92480</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9015,7 +9015,7 @@
         <v>129193559</v>
       </c>
       <c r="B73" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9109,61 +9109,45 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129193575</v>
+        <v>129193549</v>
       </c>
       <c r="B74" t="n">
-        <v>98676</v>
+        <v>80147</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="N74" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>520528</v>
+        <v>520345</v>
       </c>
       <c r="R74" t="n">
-        <v>7001465</v>
+        <v>7001396</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9198,18 +9182,12 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Minst 50</t>
-        </is>
-      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -9228,10 +9206,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129193549</v>
+        <v>129193546</v>
       </c>
       <c r="B75" t="n">
-        <v>80145</v>
+        <v>57727</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9239,21 +9217,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -9263,10 +9241,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>520345</v>
+        <v>519958</v>
       </c>
       <c r="R75" t="n">
-        <v>7001396</v>
+        <v>7001542</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9299,6 +9277,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9325,45 +9308,61 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129193546</v>
+        <v>129193575</v>
       </c>
       <c r="B76" t="n">
-        <v>57725</v>
+        <v>98678</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>519958</v>
+        <v>520528</v>
       </c>
       <c r="R76" t="n">
-        <v>7001542</v>
+        <v>7001465</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9400,7 +9399,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Minst 50</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9409,6 +9408,7 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 43533-2025 artfynd.xlsx
+++ b/artfynd/A 43533-2025 artfynd.xlsx
@@ -675,47 +675,38 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129135545</v>
+        <v>129135852</v>
       </c>
       <c r="B2" t="n">
-        <v>98678</v>
+        <v>99012</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>219880</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>gulnande löv/blad</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>520564</v>
+        <v>520213</v>
       </c>
       <c r="R2" t="n">
-        <v>7001441</v>
+        <v>7001609</v>
       </c>
       <c r="S2" t="n">
         <v>9</v>
@@ -759,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,38 +792,38 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129135852</v>
+        <v>129126527</v>
       </c>
       <c r="B3" t="n">
-        <v>99012</v>
+        <v>80146</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219880</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>gulnande löv/blad</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -841,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>520213</v>
+        <v>520189</v>
       </c>
       <c r="R3" t="n">
-        <v>7001609</v>
+        <v>7001448</v>
       </c>
       <c r="S3" t="n">
         <v>9</v>
@@ -876,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,7 +896,27 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -918,38 +934,47 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129126527</v>
+        <v>129135545</v>
       </c>
       <c r="B4" t="n">
-        <v>80146</v>
+        <v>98678</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -958,10 +983,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>520189</v>
+        <v>520564</v>
       </c>
       <c r="R4" t="n">
-        <v>7001448</v>
+        <v>7001441</v>
       </c>
       <c r="S4" t="n">
         <v>9</v>
@@ -993,7 +1018,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,12 +1028,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:12</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1022,27 +1042,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1182,38 +1182,47 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129127182</v>
+        <v>129126843</v>
       </c>
       <c r="B6" t="n">
-        <v>57727</v>
+        <v>98678</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1227,13 +1236,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>520186</v>
+        <v>520211</v>
       </c>
       <c r="R6" t="n">
-        <v>7001459</v>
+        <v>7001475</v>
       </c>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1262,7 +1271,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1272,12 +1281,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran  intill en gammal sälg.</t>
+          <t>Minst 100 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1292,26 +1301,6 @@
       <c r="AH6" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1329,7 +1318,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129131350</v>
+        <v>129127182</v>
       </c>
       <c r="B7" t="n">
         <v>57727</v>
@@ -1360,7 +1349,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1374,10 +1363,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>520520</v>
+        <v>520186</v>
       </c>
       <c r="R7" t="n">
-        <v>7001311</v>
+        <v>7001459</v>
       </c>
       <c r="S7" t="n">
         <v>8</v>
@@ -1409,7 +1398,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1419,12 +1408,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack, enstaka färska och rikligt med äldre på en tall.</t>
+          <t>Ringhack, äldre, på stambasen av en gran  intill en gammal sälg.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1438,17 +1427,17 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -1458,7 +1447,7 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1476,47 +1465,38 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129126843</v>
+        <v>129131350</v>
       </c>
       <c r="B8" t="n">
-        <v>98678</v>
+        <v>57727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1530,13 +1510,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>520211</v>
+        <v>520520</v>
       </c>
       <c r="R8" t="n">
-        <v>7001475</v>
+        <v>7001311</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1565,7 +1545,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1575,12 +1555,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Minst 100 plantor inom ca 0,5 m2 yta.</t>
+          <t>Ringhack, enstaka färska och rikligt med äldre på en tall.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1594,7 +1574,27 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1851,10 +1851,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129126617</v>
+        <v>129128175</v>
       </c>
       <c r="B11" t="n">
-        <v>80146</v>
+        <v>79041</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1862,42 +1862,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>520219</v>
+        <v>520329</v>
       </c>
       <c r="R11" t="n">
-        <v>7001429</v>
+        <v>7001400</v>
       </c>
       <c r="S11" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1926,7 +1921,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1936,7 +1931,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1950,17 +1945,17 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1978,10 +1973,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129128175</v>
+        <v>129127736</v>
       </c>
       <c r="B12" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1989,37 +1984,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>520329</v>
+        <v>520237</v>
       </c>
       <c r="R12" t="n">
-        <v>7001400</v>
+        <v>7001416</v>
       </c>
       <c r="S12" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2048,7 +2048,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2058,7 +2058,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2070,6 +2075,11 @@
       <c r="AG12" t="b">
         <v>0</v>
       </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AJ12" t="inlineStr">
         <is>
           <t>gran</t>
@@ -2080,9 +2090,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2100,10 +2115,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129127736</v>
+        <v>129126617</v>
       </c>
       <c r="B13" t="n">
-        <v>57727</v>
+        <v>80146</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2111,27 +2126,27 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2140,13 +2155,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>520237</v>
+        <v>520219</v>
       </c>
       <c r="R13" t="n">
-        <v>7001416</v>
+        <v>7001429</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2175,7 +2190,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2185,12 +2200,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:01</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2202,29 +2212,19 @@
       <c r="AG13" t="b">
         <v>0</v>
       </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -3408,10 +3408,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129128128</v>
+        <v>129136001</v>
       </c>
       <c r="B23" t="n">
-        <v>80147</v>
+        <v>79041</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3419,42 +3419,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>520340</v>
+        <v>520012</v>
       </c>
       <c r="R23" t="n">
-        <v>7001392</v>
+        <v>7001652</v>
       </c>
       <c r="S23" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3483,7 +3478,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3493,7 +3488,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3504,31 +3499,6 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3545,7 +3515,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129136001</v>
+        <v>129126703</v>
       </c>
       <c r="B24" t="n">
         <v>79041</v>
@@ -3580,13 +3550,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>520012</v>
+        <v>520253</v>
       </c>
       <c r="R24" t="n">
-        <v>7001652</v>
+        <v>7001454</v>
       </c>
       <c r="S24" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3615,7 +3585,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3625,7 +3595,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3636,6 +3606,31 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3652,10 +3647,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129126703</v>
+        <v>129128128</v>
       </c>
       <c r="B25" t="n">
-        <v>79041</v>
+        <v>80147</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3663,34 +3658,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>520253</v>
+        <v>520340</v>
       </c>
       <c r="R25" t="n">
-        <v>7001454</v>
+        <v>7001392</v>
       </c>
       <c r="S25" t="n">
         <v>9</v>
@@ -3722,7 +3722,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3732,7 +3732,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3746,27 +3746,27 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -4053,48 +4053,67 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129131418</v>
+        <v>129127084</v>
       </c>
       <c r="B28" t="n">
-        <v>79041</v>
+        <v>98678</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>520682</v>
+        <v>520203</v>
       </c>
       <c r="R28" t="n">
-        <v>7001354</v>
+        <v>7001453</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4123,7 +4142,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4133,7 +4152,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4147,27 +4166,7 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4185,10 +4184,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129124933</v>
+        <v>129131418</v>
       </c>
       <c r="B29" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4196,42 +4195,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>519886</v>
+        <v>520682</v>
       </c>
       <c r="R29" t="n">
-        <v>7001592</v>
+        <v>7001354</v>
       </c>
       <c r="S29" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4260,7 +4254,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4270,12 +4264,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:39</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran i hyggeskanten.</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4289,7 +4278,7 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
@@ -4304,12 +4293,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4327,52 +4316,38 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129127084</v>
+        <v>129124933</v>
       </c>
       <c r="B30" t="n">
-        <v>98678</v>
+        <v>57727</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4381,13 +4356,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>520203</v>
+        <v>519886</v>
       </c>
       <c r="R30" t="n">
-        <v>7001453</v>
+        <v>7001592</v>
       </c>
       <c r="S30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4416,7 +4391,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4426,7 +4401,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>09:39</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran i hyggeskanten.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4441,6 +4421,26 @@
       <c r="AH30" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -5950,32 +5950,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129193568</v>
+        <v>129193576</v>
       </c>
       <c r="B43" t="n">
-        <v>80146</v>
+        <v>98678</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5985,10 +5985,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>520159</v>
+        <v>520675</v>
       </c>
       <c r="R43" t="n">
-        <v>7001489</v>
+        <v>7001377</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6047,7 +6047,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129193576</v>
+        <v>129193582</v>
       </c>
       <c r="B44" t="n">
         <v>98678</v>
@@ -6075,17 +6075,33 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>520675</v>
+        <v>520388</v>
       </c>
       <c r="R44" t="n">
-        <v>7001377</v>
+        <v>7001418</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6120,12 +6136,18 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Minst 50</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -6144,61 +6166,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129193582</v>
+        <v>129193568</v>
       </c>
       <c r="B45" t="n">
-        <v>98678</v>
+        <v>80146</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>520388</v>
+        <v>520159</v>
       </c>
       <c r="R45" t="n">
-        <v>7001418</v>
+        <v>7001489</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6233,18 +6239,12 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Minst 50</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -6263,61 +6263,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129193583</v>
+        <v>129193542</v>
       </c>
       <c r="B46" t="n">
-        <v>98678</v>
+        <v>57727</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>520338</v>
+        <v>520422</v>
       </c>
       <c r="R46" t="n">
-        <v>7001427</v>
+        <v>7001418</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6354,7 +6338,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Minst 100</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6363,7 +6347,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -6382,45 +6365,61 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129193542</v>
+        <v>129193583</v>
       </c>
       <c r="B47" t="n">
-        <v>57727</v>
+        <v>98678</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>520422</v>
+        <v>520338</v>
       </c>
       <c r="R47" t="n">
-        <v>7001418</v>
+        <v>7001427</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6457,7 +6456,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Minst 100</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6466,6 +6465,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -6775,10 +6775,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129193523</v>
+        <v>129193566</v>
       </c>
       <c r="B51" t="n">
-        <v>57727</v>
+        <v>80146</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6786,21 +6786,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6810,10 +6810,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>520478</v>
+        <v>520180</v>
       </c>
       <c r="R51" t="n">
-        <v>7001335</v>
+        <v>7001458</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6846,11 +6846,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6979,61 +6974,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129193581</v>
+        <v>129193523</v>
       </c>
       <c r="B53" t="n">
-        <v>98678</v>
+        <v>57727</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>520425</v>
+        <v>520478</v>
       </c>
       <c r="R53" t="n">
-        <v>7001407</v>
+        <v>7001335</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7070,7 +7049,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Minst 80</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7079,7 +7058,6 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -7098,45 +7076,61 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129193566</v>
+        <v>129193581</v>
       </c>
       <c r="B54" t="n">
-        <v>80146</v>
+        <v>98678</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>520180</v>
+        <v>520425</v>
       </c>
       <c r="R54" t="n">
-        <v>7001458</v>
+        <v>7001407</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7171,12 +7165,18 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Minst 80</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -7583,7 +7583,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129193524</v>
+        <v>129193544</v>
       </c>
       <c r="B59" t="n">
         <v>57727</v>
@@ -7618,10 +7618,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>520478</v>
+        <v>520270</v>
       </c>
       <c r="R59" t="n">
-        <v>7001328</v>
+        <v>7001484</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7658,7 +7658,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7685,7 +7685,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129193544</v>
+        <v>129193524</v>
       </c>
       <c r="B60" t="n">
         <v>57727</v>
@@ -7720,10 +7720,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>520270</v>
+        <v>520478</v>
       </c>
       <c r="R60" t="n">
-        <v>7001484</v>
+        <v>7001328</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7760,7 +7760,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7787,45 +7787,57 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129193564</v>
+        <v>129193585</v>
       </c>
       <c r="B61" t="n">
-        <v>80146</v>
+        <v>98678</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>520225</v>
+        <v>520122</v>
       </c>
       <c r="R61" t="n">
-        <v>7001483</v>
+        <v>7001476</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7860,12 +7872,18 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Fler än 200</t>
+        </is>
+      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7884,7 +7902,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129193557</v>
+        <v>129193564</v>
       </c>
       <c r="B62" t="n">
         <v>80146</v>
@@ -7919,10 +7937,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>520374</v>
+        <v>520225</v>
       </c>
       <c r="R62" t="n">
-        <v>7001329</v>
+        <v>7001483</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7981,57 +7999,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129193585</v>
+        <v>129193557</v>
       </c>
       <c r="B63" t="n">
-        <v>98678</v>
+        <v>80146</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>520122</v>
+        <v>520374</v>
       </c>
       <c r="R63" t="n">
-        <v>7001476</v>
+        <v>7001329</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8066,18 +8072,12 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Fler än 200</t>
-        </is>
-      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -8586,46 +8586,46 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129193573</v>
+        <v>129193584</v>
       </c>
       <c r="B69" t="n">
-        <v>57831</v>
+        <v>98678</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>103031</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N69" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -8637,10 +8637,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>520153</v>
+        <v>520320</v>
       </c>
       <c r="R69" t="n">
-        <v>7001500</v>
+        <v>7001451</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8675,12 +8675,18 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Minst 100</t>
+        </is>
+      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -8699,46 +8705,46 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129193584</v>
+        <v>129193573</v>
       </c>
       <c r="B70" t="n">
-        <v>98678</v>
+        <v>57831</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>103031</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N70" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -8750,10 +8756,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>520320</v>
+        <v>520153</v>
       </c>
       <c r="R70" t="n">
-        <v>7001451</v>
+        <v>7001500</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8788,18 +8794,12 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Minst 100</t>
-        </is>
-      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -8915,32 +8915,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129193548</v>
+        <v>129193559</v>
       </c>
       <c r="B72" t="n">
-        <v>92480</v>
+        <v>80146</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4769</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8950,10 +8950,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>520063</v>
+        <v>520330</v>
       </c>
       <c r="R72" t="n">
-        <v>7001569</v>
+        <v>7001396</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9012,32 +9012,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129193559</v>
+        <v>129193548</v>
       </c>
       <c r="B73" t="n">
-        <v>80146</v>
+        <v>92480</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>4769</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -9047,10 +9047,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>520330</v>
+        <v>520063</v>
       </c>
       <c r="R73" t="n">
-        <v>7001396</v>
+        <v>7001569</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>

--- a/artfynd/A 43533-2025 artfynd.xlsx
+++ b/artfynd/A 43533-2025 artfynd.xlsx
@@ -675,38 +675,38 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129135852</v>
+        <v>129126527</v>
       </c>
       <c r="B2" t="n">
-        <v>99012</v>
+        <v>80146</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219880</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>gulnande löv/blad</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>520213</v>
+        <v>520189</v>
       </c>
       <c r="R2" t="n">
-        <v>7001609</v>
+        <v>7001448</v>
       </c>
       <c r="S2" t="n">
         <v>9</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,7 +779,27 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -792,38 +817,47 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129126527</v>
+        <v>129135545</v>
       </c>
       <c r="B3" t="n">
-        <v>80146</v>
+        <v>98678</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -832,10 +866,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>520189</v>
+        <v>520564</v>
       </c>
       <c r="R3" t="n">
-        <v>7001448</v>
+        <v>7001441</v>
       </c>
       <c r="S3" t="n">
         <v>9</v>
@@ -867,7 +901,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +911,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:12</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,27 +925,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -934,47 +943,38 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129135545</v>
+        <v>129135852</v>
       </c>
       <c r="B4" t="n">
-        <v>98678</v>
+        <v>99012</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>219880</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>gulnande löv/blad</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -983,10 +983,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>520564</v>
+        <v>520213</v>
       </c>
       <c r="R4" t="n">
-        <v>7001441</v>
+        <v>7001609</v>
       </c>
       <c r="S4" t="n">
         <v>9</v>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -8586,46 +8586,46 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129193584</v>
+        <v>129193573</v>
       </c>
       <c r="B69" t="n">
-        <v>98678</v>
+        <v>57831</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>103031</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N69" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -8637,10 +8637,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>520320</v>
+        <v>520153</v>
       </c>
       <c r="R69" t="n">
-        <v>7001451</v>
+        <v>7001500</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8675,18 +8675,12 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Minst 100</t>
-        </is>
-      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -8705,46 +8699,46 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129193573</v>
+        <v>129193584</v>
       </c>
       <c r="B70" t="n">
-        <v>57831</v>
+        <v>98678</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>103031</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N70" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -8756,10 +8750,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>520153</v>
+        <v>520320</v>
       </c>
       <c r="R70" t="n">
-        <v>7001500</v>
+        <v>7001451</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8794,12 +8788,18 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Minst 100</t>
+        </is>
+      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 43533-2025 artfynd.xlsx
+++ b/artfynd/A 43533-2025 artfynd.xlsx
@@ -820,7 +820,7 @@
         <v>129135545</v>
       </c>
       <c r="B3" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>129135852</v>
       </c>
       <c r="B4" t="n">
-        <v>99012</v>
+        <v>99038</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1182,47 +1182,38 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129126843</v>
+        <v>129127182</v>
       </c>
       <c r="B6" t="n">
-        <v>98678</v>
+        <v>57727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1236,13 +1227,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>520211</v>
+        <v>520186</v>
       </c>
       <c r="R6" t="n">
-        <v>7001475</v>
+        <v>7001459</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1271,7 +1262,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1281,12 +1272,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Minst 100 plantor inom ca 0,5 m2 yta.</t>
+          <t>Ringhack, äldre, på stambasen av en gran  intill en gammal sälg.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1301,6 +1292,26 @@
       <c r="AH6" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1318,7 +1329,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129127182</v>
+        <v>129131350</v>
       </c>
       <c r="B7" t="n">
         <v>57727</v>
@@ -1349,7 +1360,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1363,10 +1374,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>520186</v>
+        <v>520520</v>
       </c>
       <c r="R7" t="n">
-        <v>7001459</v>
+        <v>7001311</v>
       </c>
       <c r="S7" t="n">
         <v>8</v>
@@ -1398,7 +1409,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1408,12 +1419,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran  intill en gammal sälg.</t>
+          <t>Ringhack, enstaka färska och rikligt med äldre på en tall.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1427,17 +1438,17 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -1447,7 +1458,7 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Stem on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1465,38 +1476,47 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129131350</v>
+        <v>129126843</v>
       </c>
       <c r="B8" t="n">
-        <v>57727</v>
+        <v>98704</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1510,13 +1530,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>520520</v>
+        <v>520211</v>
       </c>
       <c r="R8" t="n">
-        <v>7001311</v>
+        <v>7001475</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1545,7 +1565,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1555,12 +1575,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack, enstaka färska och rikligt med äldre på en tall.</t>
+          <t>Minst 100 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1574,27 +1594,7 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1752,7 +1752,7 @@
         <v>129135867</v>
       </c>
       <c r="B10" t="n">
-        <v>100866</v>
+        <v>100892</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1851,10 +1851,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129128175</v>
+        <v>129127736</v>
       </c>
       <c r="B11" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1862,37 +1862,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>520329</v>
+        <v>520237</v>
       </c>
       <c r="R11" t="n">
-        <v>7001400</v>
+        <v>7001416</v>
       </c>
       <c r="S11" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1921,7 +1926,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1931,7 +1936,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1943,6 +1953,11 @@
       <c r="AG11" t="b">
         <v>0</v>
       </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AJ11" t="inlineStr">
         <is>
           <t>gran</t>
@@ -1953,9 +1968,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1973,10 +1993,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129127736</v>
+        <v>129128175</v>
       </c>
       <c r="B12" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1984,42 +2004,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>520237</v>
+        <v>520329</v>
       </c>
       <c r="R12" t="n">
-        <v>7001416</v>
+        <v>7001400</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2048,7 +2063,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2058,12 +2073,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:01</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2075,11 +2085,6 @@
       <c r="AG12" t="b">
         <v>0</v>
       </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AJ12" t="inlineStr">
         <is>
           <t>gran</t>
@@ -2090,14 +2095,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2382,7 +2382,7 @@
         <v>129135822</v>
       </c>
       <c r="B15" t="n">
-        <v>104146</v>
+        <v>104172</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2505,7 +2505,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129127604</v>
+        <v>129128162</v>
       </c>
       <c r="B16" t="n">
         <v>80146</v>
@@ -2536,7 +2536,7 @@
       <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2545,13 +2545,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>520243</v>
+        <v>520355</v>
       </c>
       <c r="R16" t="n">
-        <v>7001423</v>
+        <v>7001412</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2590,12 +2590,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:59</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Fertil lunglav på en sälg med doftticka.</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2609,7 +2604,7 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -2647,10 +2642,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129128162</v>
+        <v>129128148</v>
       </c>
       <c r="B17" t="n">
-        <v>80146</v>
+        <v>80147</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2658,21 +2653,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2687,13 +2682,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>520355</v>
+        <v>520338</v>
       </c>
       <c r="R17" t="n">
-        <v>7001412</v>
+        <v>7001407</v>
       </c>
       <c r="S17" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2751,22 +2746,22 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark of dead wood # Betula</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2784,10 +2779,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129128148</v>
+        <v>129127604</v>
       </c>
       <c r="B18" t="n">
-        <v>80147</v>
+        <v>80146</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2795,27 +2790,27 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2824,13 +2819,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>520338</v>
+        <v>520243</v>
       </c>
       <c r="R18" t="n">
-        <v>7001407</v>
+        <v>7001423</v>
       </c>
       <c r="S18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2859,7 +2854,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2869,7 +2864,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Fertil lunglav på en sälg med doftticka.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2883,27 +2883,27 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Betula</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2924,7 +2924,7 @@
         <v>129127509</v>
       </c>
       <c r="B19" t="n">
-        <v>92119</v>
+        <v>92134</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3408,10 +3408,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129136001</v>
+        <v>129128128</v>
       </c>
       <c r="B23" t="n">
-        <v>79041</v>
+        <v>80147</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3419,37 +3419,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>520012</v>
+        <v>520340</v>
       </c>
       <c r="R23" t="n">
-        <v>7001652</v>
+        <v>7001392</v>
       </c>
       <c r="S23" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3478,7 +3483,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3488,7 +3493,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3499,6 +3504,31 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3515,7 +3545,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129126703</v>
+        <v>129136001</v>
       </c>
       <c r="B24" t="n">
         <v>79041</v>
@@ -3550,13 +3580,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>520253</v>
+        <v>520012</v>
       </c>
       <c r="R24" t="n">
-        <v>7001454</v>
+        <v>7001652</v>
       </c>
       <c r="S24" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3585,7 +3615,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3595,7 +3625,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3606,31 +3636,6 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3647,10 +3652,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129128128</v>
+        <v>129126703</v>
       </c>
       <c r="B25" t="n">
-        <v>80147</v>
+        <v>79041</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3658,39 +3663,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>520340</v>
+        <v>520253</v>
       </c>
       <c r="R25" t="n">
-        <v>7001392</v>
+        <v>7001454</v>
       </c>
       <c r="S25" t="n">
         <v>9</v>
@@ -3722,7 +3722,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3732,7 +3732,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3746,27 +3746,27 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -4053,52 +4053,38 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129127084</v>
+        <v>129124933</v>
       </c>
       <c r="B28" t="n">
-        <v>98678</v>
+        <v>57727</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -4107,13 +4093,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>520203</v>
+        <v>519886</v>
       </c>
       <c r="R28" t="n">
-        <v>7001453</v>
+        <v>7001592</v>
       </c>
       <c r="S28" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4142,7 +4128,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4152,7 +4138,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>09:39</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran i hyggeskanten.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4167,6 +4158,26 @@
       <c r="AH28" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4184,48 +4195,67 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129131418</v>
+        <v>129127084</v>
       </c>
       <c r="B29" t="n">
-        <v>79041</v>
+        <v>98704</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>520682</v>
+        <v>520203</v>
       </c>
       <c r="R29" t="n">
-        <v>7001354</v>
+        <v>7001453</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4254,7 +4284,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4264,7 +4294,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4278,27 +4308,7 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4316,10 +4326,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129124933</v>
+        <v>129131418</v>
       </c>
       <c r="B30" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4327,42 +4337,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>519886</v>
+        <v>520682</v>
       </c>
       <c r="R30" t="n">
-        <v>7001592</v>
+        <v>7001354</v>
       </c>
       <c r="S30" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4391,7 +4396,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4401,12 +4406,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:39</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran i hyggeskanten.</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4420,7 +4420,7 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
@@ -4435,12 +4435,12 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4862,7 +4862,7 @@
         <v>129135770</v>
       </c>
       <c r="B34" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5274,48 +5274,62 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129135677</v>
+        <v>129128320</v>
       </c>
       <c r="B37" t="n">
-        <v>79041</v>
+        <v>98704</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>520346</v>
+        <v>520352</v>
       </c>
       <c r="R37" t="n">
-        <v>7001536</v>
+        <v>7001397</v>
       </c>
       <c r="S37" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5344,7 +5358,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5354,7 +5368,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Minst 10 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5365,6 +5384,11 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -5381,62 +5405,48 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129128320</v>
+        <v>129135677</v>
       </c>
       <c r="B38" t="n">
-        <v>98678</v>
+        <v>79041</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>520352</v>
+        <v>520346</v>
       </c>
       <c r="R38" t="n">
-        <v>7001397</v>
+        <v>7001536</v>
       </c>
       <c r="S38" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5465,7 +5475,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5475,12 +5485,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:20</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Minst 10 plantor inom ca 0,5 m2 yta.</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5491,11 +5496,6 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -5751,10 +5751,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129193558</v>
+        <v>129193518</v>
       </c>
       <c r="B41" t="n">
-        <v>80146</v>
+        <v>57727</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5762,21 +5762,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5786,10 +5786,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>520415</v>
+        <v>520676</v>
       </c>
       <c r="R41" t="n">
-        <v>7001416</v>
+        <v>7001377</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5822,6 +5822,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5848,10 +5853,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129193518</v>
+        <v>129193558</v>
       </c>
       <c r="B42" t="n">
-        <v>57727</v>
+        <v>80146</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5859,21 +5864,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5883,10 +5888,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>520676</v>
+        <v>520415</v>
       </c>
       <c r="R42" t="n">
-        <v>7001377</v>
+        <v>7001416</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5919,11 +5924,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5950,32 +5950,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129193576</v>
+        <v>129193568</v>
       </c>
       <c r="B43" t="n">
-        <v>98678</v>
+        <v>80146</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5985,10 +5985,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>520675</v>
+        <v>520159</v>
       </c>
       <c r="R43" t="n">
-        <v>7001377</v>
+        <v>7001489</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6050,7 +6050,7 @@
         <v>129193582</v>
       </c>
       <c r="B44" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6166,32 +6166,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129193568</v>
+        <v>129193576</v>
       </c>
       <c r="B45" t="n">
-        <v>80146</v>
+        <v>98704</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>520159</v>
+        <v>520675</v>
       </c>
       <c r="R45" t="n">
-        <v>7001489</v>
+        <v>7001377</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6368,7 +6368,7 @@
         <v>129193583</v>
       </c>
       <c r="B47" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6584,7 +6584,7 @@
         <v>129193591</v>
       </c>
       <c r="B49" t="n">
-        <v>92871</v>
+        <v>92857</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6872,7 +6872,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129193517</v>
+        <v>129193523</v>
       </c>
       <c r="B52" t="n">
         <v>57727</v>
@@ -6907,10 +6907,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>520301</v>
+        <v>520478</v>
       </c>
       <c r="R52" t="n">
-        <v>7001547</v>
+        <v>7001335</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6947,7 +6947,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6974,7 +6974,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129193523</v>
+        <v>129193517</v>
       </c>
       <c r="B53" t="n">
         <v>57727</v>
@@ -7009,10 +7009,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>520478</v>
+        <v>520301</v>
       </c>
       <c r="R53" t="n">
-        <v>7001335</v>
+        <v>7001547</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7079,7 +7079,7 @@
         <v>129193581</v>
       </c>
       <c r="B54" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7583,7 +7583,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129193544</v>
+        <v>129193524</v>
       </c>
       <c r="B59" t="n">
         <v>57727</v>
@@ -7618,10 +7618,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>520270</v>
+        <v>520478</v>
       </c>
       <c r="R59" t="n">
-        <v>7001484</v>
+        <v>7001328</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7658,7 +7658,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7685,7 +7685,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129193524</v>
+        <v>129193544</v>
       </c>
       <c r="B60" t="n">
         <v>57727</v>
@@ -7720,10 +7720,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>520478</v>
+        <v>520270</v>
       </c>
       <c r="R60" t="n">
-        <v>7001328</v>
+        <v>7001484</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7760,7 +7760,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7787,57 +7787,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129193585</v>
+        <v>129193564</v>
       </c>
       <c r="B61" t="n">
-        <v>98678</v>
+        <v>80146</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>520122</v>
+        <v>520225</v>
       </c>
       <c r="R61" t="n">
-        <v>7001476</v>
+        <v>7001483</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7872,18 +7860,12 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Fler än 200</t>
-        </is>
-      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7902,7 +7884,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129193564</v>
+        <v>129193557</v>
       </c>
       <c r="B62" t="n">
         <v>80146</v>
@@ -7937,10 +7919,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>520225</v>
+        <v>520374</v>
       </c>
       <c r="R62" t="n">
-        <v>7001483</v>
+        <v>7001329</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7999,45 +7981,57 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129193557</v>
+        <v>129193585</v>
       </c>
       <c r="B63" t="n">
-        <v>80146</v>
+        <v>98704</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>520374</v>
+        <v>520122</v>
       </c>
       <c r="R63" t="n">
-        <v>7001329</v>
+        <v>7001476</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8072,12 +8066,18 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Fler än 200</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -8293,7 +8293,7 @@
         <v>129193593</v>
       </c>
       <c r="B66" t="n">
-        <v>100866</v>
+        <v>100892</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8387,10 +8387,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129193562</v>
+        <v>129193545</v>
       </c>
       <c r="B67" t="n">
-        <v>80146</v>
+        <v>57727</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8398,21 +8398,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8422,10 +8422,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>520335</v>
+        <v>519958</v>
       </c>
       <c r="R67" t="n">
-        <v>7001429</v>
+        <v>7001547</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8458,6 +8458,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8484,10 +8489,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129193545</v>
+        <v>129193562</v>
       </c>
       <c r="B68" t="n">
-        <v>57727</v>
+        <v>80146</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8495,21 +8500,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8519,10 +8524,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>519958</v>
+        <v>520335</v>
       </c>
       <c r="R68" t="n">
-        <v>7001547</v>
+        <v>7001429</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8555,11 +8560,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8702,7 +8702,7 @@
         <v>129193584</v>
       </c>
       <c r="B70" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8915,32 +8915,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129193559</v>
+        <v>129193548</v>
       </c>
       <c r="B72" t="n">
-        <v>80146</v>
+        <v>92494</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>4769</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8950,10 +8950,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>520330</v>
+        <v>520063</v>
       </c>
       <c r="R72" t="n">
-        <v>7001396</v>
+        <v>7001569</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9012,32 +9012,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129193548</v>
+        <v>129193559</v>
       </c>
       <c r="B73" t="n">
-        <v>92480</v>
+        <v>80146</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4769</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -9047,10 +9047,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>520063</v>
+        <v>520330</v>
       </c>
       <c r="R73" t="n">
-        <v>7001569</v>
+        <v>7001396</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9109,45 +9109,61 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129193549</v>
+        <v>129193575</v>
       </c>
       <c r="B74" t="n">
-        <v>80147</v>
+        <v>98704</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>520345</v>
+        <v>520528</v>
       </c>
       <c r="R74" t="n">
-        <v>7001396</v>
+        <v>7001465</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9182,12 +9198,18 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Minst 50</t>
+        </is>
+      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -9206,10 +9228,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129193546</v>
+        <v>129193549</v>
       </c>
       <c r="B75" t="n">
-        <v>57727</v>
+        <v>80147</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9217,21 +9239,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -9241,10 +9263,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>519958</v>
+        <v>520345</v>
       </c>
       <c r="R75" t="n">
-        <v>7001542</v>
+        <v>7001396</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9277,11 +9299,6 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9308,61 +9325,45 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129193575</v>
+        <v>129193546</v>
       </c>
       <c r="B76" t="n">
-        <v>98678</v>
+        <v>57727</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="N76" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>520528</v>
+        <v>519958</v>
       </c>
       <c r="R76" t="n">
-        <v>7001465</v>
+        <v>7001542</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9399,7 +9400,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Minst 50</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9408,7 +9409,6 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 43533-2025 artfynd.xlsx
+++ b/artfynd/A 43533-2025 artfynd.xlsx
@@ -675,38 +675,47 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129126527</v>
+        <v>129135545</v>
       </c>
       <c r="B2" t="n">
-        <v>80146</v>
+        <v>98705</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -715,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>520189</v>
+        <v>520564</v>
       </c>
       <c r="R2" t="n">
-        <v>7001448</v>
+        <v>7001441</v>
       </c>
       <c r="S2" t="n">
         <v>9</v>
@@ -750,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:12</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,27 +783,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -817,47 +801,38 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129135545</v>
+        <v>129126527</v>
       </c>
       <c r="B3" t="n">
-        <v>98704</v>
+        <v>80146</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -866,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>520564</v>
+        <v>520189</v>
       </c>
       <c r="R3" t="n">
-        <v>7001441</v>
+        <v>7001448</v>
       </c>
       <c r="S3" t="n">
         <v>9</v>
@@ -901,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -911,7 +886,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,7 +905,27 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -946,7 +946,7 @@
         <v>129135852</v>
       </c>
       <c r="B4" t="n">
-        <v>99038</v>
+        <v>99039</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>129126843</v>
       </c>
       <c r="B8" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>129135867</v>
       </c>
       <c r="B10" t="n">
-        <v>100892</v>
+        <v>100894</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1851,10 +1851,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129127736</v>
+        <v>129128175</v>
       </c>
       <c r="B11" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1862,42 +1862,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>520237</v>
+        <v>520329</v>
       </c>
       <c r="R11" t="n">
-        <v>7001416</v>
+        <v>7001400</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1926,7 +1921,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1936,12 +1931,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:01</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1953,11 +1943,6 @@
       <c r="AG11" t="b">
         <v>0</v>
       </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AJ11" t="inlineStr">
         <is>
           <t>gran</t>
@@ -1968,14 +1953,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1993,10 +1973,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129128175</v>
+        <v>129126617</v>
       </c>
       <c r="B12" t="n">
-        <v>79041</v>
+        <v>80146</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2004,37 +1984,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>520329</v>
+        <v>520219</v>
       </c>
       <c r="R12" t="n">
-        <v>7001400</v>
+        <v>7001429</v>
       </c>
       <c r="S12" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2063,7 +2048,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2073,7 +2058,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2087,17 +2072,17 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2115,10 +2100,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129126617</v>
+        <v>129127736</v>
       </c>
       <c r="B13" t="n">
-        <v>80146</v>
+        <v>57727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2126,27 +2111,27 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2155,13 +2140,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>520219</v>
+        <v>520237</v>
       </c>
       <c r="R13" t="n">
-        <v>7001429</v>
+        <v>7001416</v>
       </c>
       <c r="S13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2190,7 +2175,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2200,7 +2185,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2212,19 +2202,29 @@
       <c r="AG13" t="b">
         <v>0</v>
       </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2382,7 +2382,7 @@
         <v>129135822</v>
       </c>
       <c r="B15" t="n">
-        <v>104172</v>
+        <v>104174</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2505,10 +2505,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129128162</v>
+        <v>129128148</v>
       </c>
       <c r="B16" t="n">
-        <v>80146</v>
+        <v>80147</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2516,21 +2516,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2545,13 +2545,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>520355</v>
+        <v>520338</v>
       </c>
       <c r="R16" t="n">
-        <v>7001412</v>
+        <v>7001407</v>
       </c>
       <c r="S16" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2609,22 +2609,22 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark of dead wood # Betula</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2642,10 +2642,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129128148</v>
+        <v>129127604</v>
       </c>
       <c r="B17" t="n">
-        <v>80147</v>
+        <v>80146</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2653,27 +2653,27 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>520338</v>
+        <v>520243</v>
       </c>
       <c r="R17" t="n">
-        <v>7001407</v>
+        <v>7001423</v>
       </c>
       <c r="S17" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2727,7 +2727,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Fertil lunglav på en sälg med doftticka.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2741,27 +2746,27 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Betula</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2779,7 +2784,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129127604</v>
+        <v>129128162</v>
       </c>
       <c r="B18" t="n">
         <v>80146</v>
@@ -2810,7 +2815,7 @@
       <c r="I18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2819,13 +2824,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>520243</v>
+        <v>520355</v>
       </c>
       <c r="R18" t="n">
-        <v>7001423</v>
+        <v>7001412</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2854,7 +2859,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2864,12 +2869,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:59</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Fertil lunglav på en sälg med doftticka.</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2883,7 +2883,7 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -2924,7 +2924,7 @@
         <v>129127509</v>
       </c>
       <c r="B19" t="n">
-        <v>92134</v>
+        <v>92135</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3174,10 +3174,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129125122</v>
+        <v>129126633</v>
       </c>
       <c r="B21" t="n">
-        <v>79041</v>
+        <v>80146</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3185,21 +3185,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3209,13 +3209,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>519973</v>
+        <v>520226</v>
       </c>
       <c r="R21" t="n">
-        <v>7001540</v>
+        <v>7001438</v>
       </c>
       <c r="S21" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3242,11 +3242,26 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På grovbarkad gammal asp.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3255,6 +3270,31 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3271,10 +3311,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129126633</v>
+        <v>129125122</v>
       </c>
       <c r="B22" t="n">
-        <v>80146</v>
+        <v>79041</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3282,21 +3322,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3306,13 +3346,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>520226</v>
+        <v>519973</v>
       </c>
       <c r="R22" t="n">
-        <v>7001438</v>
+        <v>7001540</v>
       </c>
       <c r="S22" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3339,26 +3379,11 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>11:19</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>11:19</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>På grovbarkad gammal asp.</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3367,31 +3392,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3784,10 +3784,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129131479</v>
+        <v>129127211</v>
       </c>
       <c r="B26" t="n">
-        <v>79041</v>
+        <v>80146</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3795,37 +3795,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>520712</v>
+        <v>520158</v>
       </c>
       <c r="R26" t="n">
-        <v>7001363</v>
+        <v>7001448</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3854,7 +3859,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3864,7 +3869,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3878,27 +3883,27 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3916,10 +3921,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129127211</v>
+        <v>129131479</v>
       </c>
       <c r="B27" t="n">
-        <v>80146</v>
+        <v>79041</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3927,42 +3932,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>520158</v>
+        <v>520712</v>
       </c>
       <c r="R27" t="n">
-        <v>7001448</v>
+        <v>7001363</v>
       </c>
       <c r="S27" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3991,7 +3991,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4001,7 +4001,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4015,27 +4015,27 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4053,10 +4053,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129124933</v>
+        <v>129131418</v>
       </c>
       <c r="B28" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4064,42 +4064,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>519886</v>
+        <v>520682</v>
       </c>
       <c r="R28" t="n">
-        <v>7001592</v>
+        <v>7001354</v>
       </c>
       <c r="S28" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4128,7 +4123,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4138,12 +4133,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:39</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran i hyggeskanten.</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4157,7 +4147,7 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
@@ -4172,12 +4162,12 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4198,7 +4188,7 @@
         <v>129127084</v>
       </c>
       <c r="B29" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4326,10 +4316,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129131418</v>
+        <v>129124933</v>
       </c>
       <c r="B30" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4337,37 +4327,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>520682</v>
+        <v>519886</v>
       </c>
       <c r="R30" t="n">
-        <v>7001354</v>
+        <v>7001592</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4396,7 +4391,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4406,7 +4401,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>09:39</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran i hyggeskanten.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4420,7 +4420,7 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
@@ -4435,12 +4435,12 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4862,7 +4862,7 @@
         <v>129135770</v>
       </c>
       <c r="B34" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5274,62 +5274,48 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129128320</v>
+        <v>129135677</v>
       </c>
       <c r="B37" t="n">
-        <v>98704</v>
+        <v>79041</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>520352</v>
+        <v>520346</v>
       </c>
       <c r="R37" t="n">
-        <v>7001397</v>
+        <v>7001536</v>
       </c>
       <c r="S37" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5358,7 +5344,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5368,12 +5354,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:20</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Minst 10 plantor inom ca 0,5 m2 yta.</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5384,11 +5365,6 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -5405,48 +5381,62 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129135677</v>
+        <v>129128320</v>
       </c>
       <c r="B38" t="n">
-        <v>79041</v>
+        <v>98705</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>520346</v>
+        <v>520352</v>
       </c>
       <c r="R38" t="n">
-        <v>7001536</v>
+        <v>7001397</v>
       </c>
       <c r="S38" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5475,7 +5465,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5485,7 +5475,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Minst 10 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5496,6 +5491,11 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -6047,10 +6047,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129193582</v>
+        <v>129193576</v>
       </c>
       <c r="B44" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6075,33 +6075,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>520388</v>
+        <v>520675</v>
       </c>
       <c r="R44" t="n">
-        <v>7001418</v>
+        <v>7001377</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6136,18 +6120,12 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Minst 50</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -6166,10 +6144,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129193576</v>
+        <v>129193582</v>
       </c>
       <c r="B45" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6194,17 +6172,33 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>520675</v>
+        <v>520388</v>
       </c>
       <c r="R45" t="n">
-        <v>7001377</v>
+        <v>7001418</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6239,12 +6233,18 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Minst 50</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -6368,7 +6368,7 @@
         <v>129193583</v>
       </c>
       <c r="B47" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6584,7 +6584,7 @@
         <v>129193591</v>
       </c>
       <c r="B49" t="n">
-        <v>92857</v>
+        <v>92858</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6678,10 +6678,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129193590</v>
+        <v>129193566</v>
       </c>
       <c r="B50" t="n">
-        <v>79041</v>
+        <v>80146</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6689,21 +6689,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6713,10 +6713,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>520187</v>
+        <v>520180</v>
       </c>
       <c r="R50" t="n">
-        <v>7001471</v>
+        <v>7001458</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6775,10 +6775,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129193566</v>
+        <v>129193590</v>
       </c>
       <c r="B51" t="n">
-        <v>80146</v>
+        <v>79041</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6786,21 +6786,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6810,10 +6810,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>520180</v>
+        <v>520187</v>
       </c>
       <c r="R51" t="n">
-        <v>7001458</v>
+        <v>7001471</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -7079,7 +7079,7 @@
         <v>129193581</v>
       </c>
       <c r="B54" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7195,7 +7195,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129193570</v>
+        <v>129193550</v>
       </c>
       <c r="B55" t="n">
         <v>80146</v>
@@ -7230,10 +7230,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>519997</v>
+        <v>520344</v>
       </c>
       <c r="R55" t="n">
-        <v>7001586</v>
+        <v>7001502</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7292,7 +7292,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129193550</v>
+        <v>129193570</v>
       </c>
       <c r="B56" t="n">
         <v>80146</v>
@@ -7327,10 +7327,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>520344</v>
+        <v>519997</v>
       </c>
       <c r="R56" t="n">
-        <v>7001502</v>
+        <v>7001586</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7787,7 +7787,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129193564</v>
+        <v>129193557</v>
       </c>
       <c r="B61" t="n">
         <v>80146</v>
@@ -7822,10 +7822,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>520225</v>
+        <v>520374</v>
       </c>
       <c r="R61" t="n">
-        <v>7001483</v>
+        <v>7001329</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7884,7 +7884,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129193557</v>
+        <v>129193564</v>
       </c>
       <c r="B62" t="n">
         <v>80146</v>
@@ -7919,10 +7919,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>520374</v>
+        <v>520225</v>
       </c>
       <c r="R62" t="n">
-        <v>7001329</v>
+        <v>7001483</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7984,7 +7984,7 @@
         <v>129193585</v>
       </c>
       <c r="B63" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8293,7 +8293,7 @@
         <v>129193593</v>
       </c>
       <c r="B66" t="n">
-        <v>100892</v>
+        <v>100894</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8702,7 +8702,7 @@
         <v>129193584</v>
       </c>
       <c r="B70" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8915,32 +8915,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129193548</v>
+        <v>129193559</v>
       </c>
       <c r="B72" t="n">
-        <v>92494</v>
+        <v>80146</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4769</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8950,10 +8950,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>520063</v>
+        <v>520330</v>
       </c>
       <c r="R72" t="n">
-        <v>7001569</v>
+        <v>7001396</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9012,32 +9012,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129193559</v>
+        <v>129193548</v>
       </c>
       <c r="B73" t="n">
-        <v>80146</v>
+        <v>92495</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>4769</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -9047,10 +9047,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>520330</v>
+        <v>520063</v>
       </c>
       <c r="R73" t="n">
-        <v>7001396</v>
+        <v>7001569</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9109,61 +9109,45 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129193575</v>
+        <v>129193549</v>
       </c>
       <c r="B74" t="n">
-        <v>98704</v>
+        <v>80147</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="N74" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>520528</v>
+        <v>520345</v>
       </c>
       <c r="R74" t="n">
-        <v>7001465</v>
+        <v>7001396</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9198,18 +9182,12 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Minst 50</t>
-        </is>
-      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -9228,10 +9206,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129193549</v>
+        <v>129193546</v>
       </c>
       <c r="B75" t="n">
-        <v>80147</v>
+        <v>57727</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9239,21 +9217,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -9263,10 +9241,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>520345</v>
+        <v>519958</v>
       </c>
       <c r="R75" t="n">
-        <v>7001396</v>
+        <v>7001542</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9299,6 +9277,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9325,45 +9308,61 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129193546</v>
+        <v>129193575</v>
       </c>
       <c r="B76" t="n">
-        <v>57727</v>
+        <v>98705</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>519958</v>
+        <v>520528</v>
       </c>
       <c r="R76" t="n">
-        <v>7001542</v>
+        <v>7001465</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9400,7 +9399,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Minst 50</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9409,6 +9408,7 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 43533-2025 artfynd.xlsx
+++ b/artfynd/A 43533-2025 artfynd.xlsx
@@ -675,47 +675,38 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129135545</v>
+        <v>129126527</v>
       </c>
       <c r="B2" t="n">
-        <v>98705</v>
+        <v>80146</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>520564</v>
+        <v>520189</v>
       </c>
       <c r="R2" t="n">
-        <v>7001441</v>
+        <v>7001448</v>
       </c>
       <c r="S2" t="n">
         <v>9</v>
@@ -759,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -783,7 +779,27 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -801,38 +817,47 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129126527</v>
+        <v>129135545</v>
       </c>
       <c r="B3" t="n">
-        <v>80146</v>
+        <v>98706</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -841,10 +866,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>520189</v>
+        <v>520564</v>
       </c>
       <c r="R3" t="n">
-        <v>7001448</v>
+        <v>7001441</v>
       </c>
       <c r="S3" t="n">
         <v>9</v>
@@ -876,7 +901,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,12 +911,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:12</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,27 +925,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -946,7 +946,7 @@
         <v>129135852</v>
       </c>
       <c r="B4" t="n">
-        <v>99039</v>
+        <v>99040</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>129126843</v>
       </c>
       <c r="B8" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>129135867</v>
       </c>
       <c r="B10" t="n">
-        <v>100894</v>
+        <v>100895</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2382,7 +2382,7 @@
         <v>129135822</v>
       </c>
       <c r="B15" t="n">
-        <v>104174</v>
+        <v>104175</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2505,10 +2505,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129128148</v>
+        <v>129127604</v>
       </c>
       <c r="B16" t="n">
-        <v>80147</v>
+        <v>80146</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2516,27 +2516,27 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2545,13 +2545,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>520338</v>
+        <v>520243</v>
       </c>
       <c r="R16" t="n">
-        <v>7001407</v>
+        <v>7001423</v>
       </c>
       <c r="S16" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2590,7 +2590,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Fertil lunglav på en sälg med doftticka.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2604,27 +2609,27 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Betula</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2642,7 +2647,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129127604</v>
+        <v>129128162</v>
       </c>
       <c r="B17" t="n">
         <v>80146</v>
@@ -2673,7 +2678,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2682,13 +2687,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>520243</v>
+        <v>520355</v>
       </c>
       <c r="R17" t="n">
-        <v>7001423</v>
+        <v>7001412</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2717,7 +2722,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2727,12 +2732,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:59</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Fertil lunglav på en sälg med doftticka.</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -2784,10 +2784,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129128162</v>
+        <v>129128148</v>
       </c>
       <c r="B18" t="n">
-        <v>80146</v>
+        <v>80147</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2795,21 +2795,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2824,13 +2824,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>520355</v>
+        <v>520338</v>
       </c>
       <c r="R18" t="n">
-        <v>7001412</v>
+        <v>7001407</v>
       </c>
       <c r="S18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2888,22 +2888,22 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark of dead wood # Betula</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -3174,10 +3174,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129126633</v>
+        <v>129125122</v>
       </c>
       <c r="B21" t="n">
-        <v>80146</v>
+        <v>79041</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3185,21 +3185,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3209,13 +3209,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>520226</v>
+        <v>519973</v>
       </c>
       <c r="R21" t="n">
-        <v>7001438</v>
+        <v>7001540</v>
       </c>
       <c r="S21" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3242,26 +3242,11 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>11:19</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>11:19</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På grovbarkad gammal asp.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3270,31 +3255,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3311,10 +3271,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129125122</v>
+        <v>129126633</v>
       </c>
       <c r="B22" t="n">
-        <v>79041</v>
+        <v>80146</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3322,21 +3282,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3346,13 +3306,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>519973</v>
+        <v>520226</v>
       </c>
       <c r="R22" t="n">
-        <v>7001540</v>
+        <v>7001438</v>
       </c>
       <c r="S22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3379,11 +3339,26 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På grovbarkad gammal asp.</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3392,6 +3367,31 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -4185,52 +4185,38 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129127084</v>
+        <v>129124933</v>
       </c>
       <c r="B29" t="n">
-        <v>98705</v>
+        <v>57727</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -4239,13 +4225,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>520203</v>
+        <v>519886</v>
       </c>
       <c r="R29" t="n">
-        <v>7001453</v>
+        <v>7001592</v>
       </c>
       <c r="S29" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4274,7 +4260,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4284,7 +4270,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>09:39</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran i hyggeskanten.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4299,6 +4290,26 @@
       <c r="AH29" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4316,38 +4327,52 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129124933</v>
+        <v>129127084</v>
       </c>
       <c r="B30" t="n">
-        <v>57727</v>
+        <v>98706</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4356,13 +4381,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>519886</v>
+        <v>520203</v>
       </c>
       <c r="R30" t="n">
-        <v>7001592</v>
+        <v>7001453</v>
       </c>
       <c r="S30" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4391,7 +4416,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4401,12 +4426,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:39</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran i hyggeskanten.</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4421,26 +4441,6 @@
       <c r="AH30" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4862,7 +4862,7 @@
         <v>129135770</v>
       </c>
       <c r="B34" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5384,7 +5384,7 @@
         <v>129128320</v>
       </c>
       <c r="B38" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5751,10 +5751,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129193518</v>
+        <v>129193558</v>
       </c>
       <c r="B41" t="n">
-        <v>57727</v>
+        <v>80146</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5762,21 +5762,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5786,10 +5786,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>520676</v>
+        <v>520415</v>
       </c>
       <c r="R41" t="n">
-        <v>7001377</v>
+        <v>7001416</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5822,11 +5822,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5853,10 +5848,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129193558</v>
+        <v>129193518</v>
       </c>
       <c r="B42" t="n">
-        <v>80146</v>
+        <v>57727</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5864,21 +5859,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5888,10 +5883,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>520415</v>
+        <v>520676</v>
       </c>
       <c r="R42" t="n">
-        <v>7001416</v>
+        <v>7001377</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5924,6 +5919,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5950,32 +5950,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129193568</v>
+        <v>129193576</v>
       </c>
       <c r="B43" t="n">
-        <v>80146</v>
+        <v>98706</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5985,10 +5985,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>520159</v>
+        <v>520675</v>
       </c>
       <c r="R43" t="n">
-        <v>7001489</v>
+        <v>7001377</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6047,10 +6047,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129193576</v>
+        <v>129193582</v>
       </c>
       <c r="B44" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6075,17 +6075,33 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>520675</v>
+        <v>520388</v>
       </c>
       <c r="R44" t="n">
-        <v>7001377</v>
+        <v>7001418</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6120,12 +6136,18 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Minst 50</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -6144,61 +6166,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129193582</v>
+        <v>129193568</v>
       </c>
       <c r="B45" t="n">
-        <v>98705</v>
+        <v>80146</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>520388</v>
+        <v>520159</v>
       </c>
       <c r="R45" t="n">
-        <v>7001418</v>
+        <v>7001489</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6233,18 +6239,12 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Minst 50</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -6368,7 +6368,7 @@
         <v>129193583</v>
       </c>
       <c r="B47" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6678,45 +6678,61 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129193566</v>
+        <v>129193581</v>
       </c>
       <c r="B50" t="n">
-        <v>80146</v>
+        <v>98706</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>520180</v>
+        <v>520425</v>
       </c>
       <c r="R50" t="n">
-        <v>7001458</v>
+        <v>7001407</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6751,12 +6767,18 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Minst 80</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -6872,10 +6894,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129193523</v>
+        <v>129193566</v>
       </c>
       <c r="B52" t="n">
-        <v>57727</v>
+        <v>80146</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6883,21 +6905,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6907,10 +6929,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>520478</v>
+        <v>520180</v>
       </c>
       <c r="R52" t="n">
-        <v>7001335</v>
+        <v>7001458</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6943,11 +6965,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6974,7 +6991,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129193517</v>
+        <v>129193523</v>
       </c>
       <c r="B53" t="n">
         <v>57727</v>
@@ -7009,10 +7026,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>520301</v>
+        <v>520478</v>
       </c>
       <c r="R53" t="n">
-        <v>7001547</v>
+        <v>7001335</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7049,7 +7066,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7076,61 +7093,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129193581</v>
+        <v>129193517</v>
       </c>
       <c r="B54" t="n">
-        <v>98705</v>
+        <v>57727</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>520425</v>
+        <v>520301</v>
       </c>
       <c r="R54" t="n">
-        <v>7001407</v>
+        <v>7001547</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7167,7 +7168,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Minst 80</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7176,7 +7177,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -7195,7 +7195,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129193550</v>
+        <v>129193570</v>
       </c>
       <c r="B55" t="n">
         <v>80146</v>
@@ -7230,10 +7230,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>520344</v>
+        <v>519997</v>
       </c>
       <c r="R55" t="n">
-        <v>7001502</v>
+        <v>7001586</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7292,7 +7292,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129193570</v>
+        <v>129193550</v>
       </c>
       <c r="B56" t="n">
         <v>80146</v>
@@ -7327,10 +7327,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>519997</v>
+        <v>520344</v>
       </c>
       <c r="R56" t="n">
-        <v>7001586</v>
+        <v>7001502</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7787,7 +7787,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129193557</v>
+        <v>129193564</v>
       </c>
       <c r="B61" t="n">
         <v>80146</v>
@@ -7822,10 +7822,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>520374</v>
+        <v>520225</v>
       </c>
       <c r="R61" t="n">
-        <v>7001329</v>
+        <v>7001483</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7884,7 +7884,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129193564</v>
+        <v>129193557</v>
       </c>
       <c r="B62" t="n">
         <v>80146</v>
@@ -7919,10 +7919,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>520225</v>
+        <v>520374</v>
       </c>
       <c r="R62" t="n">
-        <v>7001483</v>
+        <v>7001329</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7984,7 +7984,7 @@
         <v>129193585</v>
       </c>
       <c r="B63" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8293,7 +8293,7 @@
         <v>129193593</v>
       </c>
       <c r="B66" t="n">
-        <v>100894</v>
+        <v>100895</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8702,7 +8702,7 @@
         <v>129193584</v>
       </c>
       <c r="B70" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9109,45 +9109,61 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129193549</v>
+        <v>129193575</v>
       </c>
       <c r="B74" t="n">
-        <v>80147</v>
+        <v>98706</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>520345</v>
+        <v>520528</v>
       </c>
       <c r="R74" t="n">
-        <v>7001396</v>
+        <v>7001465</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9182,12 +9198,18 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Minst 50</t>
+        </is>
+      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -9206,10 +9228,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129193546</v>
+        <v>129193549</v>
       </c>
       <c r="B75" t="n">
-        <v>57727</v>
+        <v>80147</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9217,21 +9239,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -9241,10 +9263,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>519958</v>
+        <v>520345</v>
       </c>
       <c r="R75" t="n">
-        <v>7001542</v>
+        <v>7001396</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9277,11 +9299,6 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9308,61 +9325,45 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129193575</v>
+        <v>129193546</v>
       </c>
       <c r="B76" t="n">
-        <v>98705</v>
+        <v>57727</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="N76" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>520528</v>
+        <v>519958</v>
       </c>
       <c r="R76" t="n">
-        <v>7001465</v>
+        <v>7001542</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9399,7 +9400,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Minst 50</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9408,7 +9409,6 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 43533-2025 artfynd.xlsx
+++ b/artfynd/A 43533-2025 artfynd.xlsx
@@ -675,38 +675,47 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129126527</v>
+        <v>129135545</v>
       </c>
       <c r="B2" t="n">
-        <v>80146</v>
+        <v>98710</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -715,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>520189</v>
+        <v>520564</v>
       </c>
       <c r="R2" t="n">
-        <v>7001448</v>
+        <v>7001441</v>
       </c>
       <c r="S2" t="n">
         <v>9</v>
@@ -750,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:12</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,27 +783,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -817,47 +801,38 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129135545</v>
+        <v>129135852</v>
       </c>
       <c r="B3" t="n">
-        <v>98706</v>
+        <v>99044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>219880</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>gulnande löv/blad</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -866,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>520564</v>
+        <v>520213</v>
       </c>
       <c r="R3" t="n">
-        <v>7001441</v>
+        <v>7001609</v>
       </c>
       <c r="S3" t="n">
         <v>9</v>
@@ -901,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -911,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -943,38 +918,38 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129135852</v>
+        <v>129126527</v>
       </c>
       <c r="B4" t="n">
-        <v>99040</v>
+        <v>80148</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219880</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>gulnande löv/blad</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -983,10 +958,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>520213</v>
+        <v>520189</v>
       </c>
       <c r="R4" t="n">
-        <v>7001609</v>
+        <v>7001448</v>
       </c>
       <c r="S4" t="n">
         <v>9</v>
@@ -1018,7 +993,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1028,7 +1003,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1042,7 +1022,27 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1063,7 +1063,7 @@
         <v>129131270</v>
       </c>
       <c r="B5" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>129126843</v>
       </c>
       <c r="B8" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1615,7 +1615,7 @@
         <v>129135692</v>
       </c>
       <c r="B9" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>129135867</v>
       </c>
       <c r="B10" t="n">
-        <v>100895</v>
+        <v>100899</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1851,10 +1851,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129128175</v>
+        <v>129126617</v>
       </c>
       <c r="B11" t="n">
-        <v>79041</v>
+        <v>80148</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1862,37 +1862,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>520329</v>
+        <v>520219</v>
       </c>
       <c r="R11" t="n">
-        <v>7001400</v>
+        <v>7001429</v>
       </c>
       <c r="S11" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1921,7 +1926,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1931,7 +1936,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1945,17 +1950,17 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1973,10 +1978,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129126617</v>
+        <v>129127736</v>
       </c>
       <c r="B12" t="n">
-        <v>80146</v>
+        <v>57727</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1984,27 +1989,27 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -2013,13 +2018,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>520219</v>
+        <v>520237</v>
       </c>
       <c r="R12" t="n">
-        <v>7001429</v>
+        <v>7001416</v>
       </c>
       <c r="S12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2048,7 +2053,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2058,7 +2063,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2070,19 +2080,29 @@
       <c r="AG12" t="b">
         <v>0</v>
       </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2100,10 +2120,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129127736</v>
+        <v>129128175</v>
       </c>
       <c r="B13" t="n">
-        <v>57727</v>
+        <v>79043</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2111,42 +2131,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>520237</v>
+        <v>520329</v>
       </c>
       <c r="R13" t="n">
-        <v>7001416</v>
+        <v>7001400</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2175,7 +2190,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2185,12 +2200,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:01</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2202,11 +2212,6 @@
       <c r="AG13" t="b">
         <v>0</v>
       </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AJ13" t="inlineStr">
         <is>
           <t>gran</t>
@@ -2217,14 +2222,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2245,7 +2245,7 @@
         <v>129126547</v>
       </c>
       <c r="B14" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2382,7 +2382,7 @@
         <v>129135822</v>
       </c>
       <c r="B15" t="n">
-        <v>104175</v>
+        <v>104179</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
         <v>129127604</v>
       </c>
       <c r="B16" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2650,7 +2650,7 @@
         <v>129128162</v>
       </c>
       <c r="B17" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2787,7 +2787,7 @@
         <v>129128148</v>
       </c>
       <c r="B18" t="n">
-        <v>80147</v>
+        <v>80149</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2924,7 +2924,7 @@
         <v>129127509</v>
       </c>
       <c r="B19" t="n">
-        <v>92135</v>
+        <v>92138</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3070,7 +3070,7 @@
         <v>129131389</v>
       </c>
       <c r="B20" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         <v>129125122</v>
       </c>
       <c r="B21" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
         <v>129126633</v>
       </c>
       <c r="B22" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3408,10 +3408,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129128128</v>
+        <v>129136001</v>
       </c>
       <c r="B23" t="n">
-        <v>80147</v>
+        <v>79043</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3419,42 +3419,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>520340</v>
+        <v>520012</v>
       </c>
       <c r="R23" t="n">
-        <v>7001392</v>
+        <v>7001652</v>
       </c>
       <c r="S23" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3483,7 +3478,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3493,7 +3488,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3504,31 +3499,6 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3545,10 +3515,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129136001</v>
+        <v>129126703</v>
       </c>
       <c r="B24" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3580,13 +3550,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>520012</v>
+        <v>520253</v>
       </c>
       <c r="R24" t="n">
-        <v>7001652</v>
+        <v>7001454</v>
       </c>
       <c r="S24" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3615,7 +3585,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3625,7 +3595,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3636,6 +3606,31 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3652,10 +3647,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129126703</v>
+        <v>129128128</v>
       </c>
       <c r="B25" t="n">
-        <v>79041</v>
+        <v>80149</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3663,34 +3658,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>520253</v>
+        <v>520340</v>
       </c>
       <c r="R25" t="n">
-        <v>7001454</v>
+        <v>7001392</v>
       </c>
       <c r="S25" t="n">
         <v>9</v>
@@ -3722,7 +3722,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3732,7 +3732,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3746,27 +3746,27 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3784,10 +3784,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129127211</v>
+        <v>129131479</v>
       </c>
       <c r="B26" t="n">
-        <v>80146</v>
+        <v>79043</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3795,42 +3795,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>520158</v>
+        <v>520712</v>
       </c>
       <c r="R26" t="n">
-        <v>7001448</v>
+        <v>7001363</v>
       </c>
       <c r="S26" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3859,7 +3854,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3869,7 +3864,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3883,27 +3878,27 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3921,10 +3916,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129131479</v>
+        <v>129127211</v>
       </c>
       <c r="B27" t="n">
-        <v>79041</v>
+        <v>80148</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3932,37 +3927,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>520712</v>
+        <v>520158</v>
       </c>
       <c r="R27" t="n">
-        <v>7001363</v>
+        <v>7001448</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3991,7 +3991,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4001,7 +4001,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4015,27 +4015,27 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4053,48 +4053,67 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129131418</v>
+        <v>129127084</v>
       </c>
       <c r="B28" t="n">
-        <v>79041</v>
+        <v>98710</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>520682</v>
+        <v>520203</v>
       </c>
       <c r="R28" t="n">
-        <v>7001354</v>
+        <v>7001453</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4123,7 +4142,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4133,7 +4152,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4147,27 +4166,7 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4185,10 +4184,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129124933</v>
+        <v>129131418</v>
       </c>
       <c r="B29" t="n">
-        <v>57727</v>
+        <v>79043</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4196,42 +4195,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>519886</v>
+        <v>520682</v>
       </c>
       <c r="R29" t="n">
-        <v>7001592</v>
+        <v>7001354</v>
       </c>
       <c r="S29" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4260,7 +4254,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4270,12 +4264,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:39</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran i hyggeskanten.</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4289,7 +4278,7 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
@@ -4304,12 +4293,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4327,52 +4316,38 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129127084</v>
+        <v>129124933</v>
       </c>
       <c r="B30" t="n">
-        <v>98706</v>
+        <v>57727</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4381,13 +4356,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>520203</v>
+        <v>519886</v>
       </c>
       <c r="R30" t="n">
-        <v>7001453</v>
+        <v>7001592</v>
       </c>
       <c r="S30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4416,7 +4391,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4426,7 +4401,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>09:39</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran i hyggeskanten.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4441,6 +4421,26 @@
       <c r="AH30" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4461,7 +4461,7 @@
         <v>129135649</v>
       </c>
       <c r="B31" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4598,7 +4598,7 @@
         <v>129125106</v>
       </c>
       <c r="B32" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4722,48 +4722,62 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129128345</v>
+        <v>129135770</v>
       </c>
       <c r="B33" t="n">
-        <v>79041</v>
+        <v>98710</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>520362</v>
+        <v>520226</v>
       </c>
       <c r="R33" t="n">
-        <v>7001381</v>
+        <v>7001601</v>
       </c>
       <c r="S33" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4792,7 +4806,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4802,12 +4816,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Minst 120 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4821,27 +4835,7 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4859,62 +4853,48 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129135770</v>
+        <v>129128345</v>
       </c>
       <c r="B34" t="n">
-        <v>98706</v>
+        <v>79043</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>520226</v>
+        <v>520362</v>
       </c>
       <c r="R34" t="n">
-        <v>7001601</v>
+        <v>7001381</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4943,7 +4923,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4953,12 +4933,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Minst 120 plantor inom ca 1 m2 yta.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4972,7 +4952,27 @@
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4993,7 +4993,7 @@
         <v>129128023</v>
       </c>
       <c r="B35" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5135,7 +5135,7 @@
         <v>129135454</v>
       </c>
       <c r="B36" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5277,7 +5277,7 @@
         <v>129135677</v>
       </c>
       <c r="B37" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5384,7 +5384,7 @@
         <v>129128320</v>
       </c>
       <c r="B38" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5515,7 +5515,7 @@
         <v>129135697</v>
       </c>
       <c r="B39" t="n">
-        <v>80175</v>
+        <v>80177</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5751,10 +5751,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129193558</v>
+        <v>129193518</v>
       </c>
       <c r="B41" t="n">
-        <v>80146</v>
+        <v>57727</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5762,21 +5762,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5786,10 +5786,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>520415</v>
+        <v>520676</v>
       </c>
       <c r="R41" t="n">
-        <v>7001416</v>
+        <v>7001377</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5822,6 +5822,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5848,10 +5853,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129193518</v>
+        <v>129193558</v>
       </c>
       <c r="B42" t="n">
-        <v>57727</v>
+        <v>80148</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5859,21 +5864,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5883,10 +5888,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>520676</v>
+        <v>520415</v>
       </c>
       <c r="R42" t="n">
-        <v>7001377</v>
+        <v>7001416</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5919,11 +5924,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5950,32 +5950,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129193576</v>
+        <v>129193568</v>
       </c>
       <c r="B43" t="n">
-        <v>98706</v>
+        <v>80148</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5985,10 +5985,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>520675</v>
+        <v>520159</v>
       </c>
       <c r="R43" t="n">
-        <v>7001377</v>
+        <v>7001489</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6047,10 +6047,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129193582</v>
+        <v>129193576</v>
       </c>
       <c r="B44" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6075,33 +6075,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>520388</v>
+        <v>520675</v>
       </c>
       <c r="R44" t="n">
-        <v>7001418</v>
+        <v>7001377</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6136,18 +6120,12 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Minst 50</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -6166,45 +6144,61 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129193568</v>
+        <v>129193582</v>
       </c>
       <c r="B45" t="n">
-        <v>80146</v>
+        <v>98710</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>520159</v>
+        <v>520388</v>
       </c>
       <c r="R45" t="n">
-        <v>7001489</v>
+        <v>7001418</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6239,12 +6233,18 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Minst 50</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -6368,7 +6368,7 @@
         <v>129193583</v>
       </c>
       <c r="B47" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6487,7 +6487,7 @@
         <v>129193565</v>
       </c>
       <c r="B48" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6584,7 +6584,7 @@
         <v>129193591</v>
       </c>
       <c r="B49" t="n">
-        <v>92858</v>
+        <v>92861</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6678,61 +6678,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129193581</v>
+        <v>129193590</v>
       </c>
       <c r="B50" t="n">
-        <v>98706</v>
+        <v>79043</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>520425</v>
+        <v>520187</v>
       </c>
       <c r="R50" t="n">
-        <v>7001407</v>
+        <v>7001471</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6767,18 +6751,12 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Minst 80</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -6797,10 +6775,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129193590</v>
+        <v>129193566</v>
       </c>
       <c r="B51" t="n">
-        <v>79041</v>
+        <v>80148</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6808,21 +6786,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6832,10 +6810,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>520187</v>
+        <v>520180</v>
       </c>
       <c r="R51" t="n">
-        <v>7001471</v>
+        <v>7001458</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6894,45 +6872,61 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129193566</v>
+        <v>129193581</v>
       </c>
       <c r="B52" t="n">
-        <v>80146</v>
+        <v>98710</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>520180</v>
+        <v>520425</v>
       </c>
       <c r="R52" t="n">
-        <v>7001458</v>
+        <v>7001407</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6967,12 +6961,18 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Minst 80</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -7198,7 +7198,7 @@
         <v>129193570</v>
       </c>
       <c r="B55" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7295,7 +7295,7 @@
         <v>129193550</v>
       </c>
       <c r="B56" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7392,7 +7392,7 @@
         <v>129193561</v>
       </c>
       <c r="B57" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7489,7 +7489,7 @@
         <v>129193567</v>
       </c>
       <c r="B58" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7790,7 +7790,7 @@
         <v>129193564</v>
       </c>
       <c r="B61" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7887,7 +7887,7 @@
         <v>129193557</v>
       </c>
       <c r="B62" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7984,7 +7984,7 @@
         <v>129193585</v>
       </c>
       <c r="B63" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8099,7 +8099,7 @@
         <v>129193560</v>
       </c>
       <c r="B64" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8196,7 +8196,7 @@
         <v>129193569</v>
       </c>
       <c r="B65" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8293,7 +8293,7 @@
         <v>129193593</v>
       </c>
       <c r="B66" t="n">
-        <v>100895</v>
+        <v>100899</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8387,10 +8387,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129193545</v>
+        <v>129193562</v>
       </c>
       <c r="B67" t="n">
-        <v>57727</v>
+        <v>80148</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8398,21 +8398,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8422,10 +8422,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>519958</v>
+        <v>520335</v>
       </c>
       <c r="R67" t="n">
-        <v>7001547</v>
+        <v>7001429</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8458,11 +8458,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8489,10 +8484,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129193562</v>
+        <v>129193545</v>
       </c>
       <c r="B68" t="n">
-        <v>80146</v>
+        <v>57727</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8500,21 +8495,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8524,10 +8519,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>520335</v>
+        <v>519958</v>
       </c>
       <c r="R68" t="n">
-        <v>7001429</v>
+        <v>7001547</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8560,6 +8555,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8702,7 +8702,7 @@
         <v>129193584</v>
       </c>
       <c r="B70" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8821,7 +8821,7 @@
         <v>129193563</v>
       </c>
       <c r="B71" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8915,32 +8915,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129193559</v>
+        <v>129193548</v>
       </c>
       <c r="B72" t="n">
-        <v>80146</v>
+        <v>92498</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>4769</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8950,10 +8950,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>520330</v>
+        <v>520063</v>
       </c>
       <c r="R72" t="n">
-        <v>7001396</v>
+        <v>7001569</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9012,32 +9012,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129193548</v>
+        <v>129193559</v>
       </c>
       <c r="B73" t="n">
-        <v>92495</v>
+        <v>80148</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4769</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -9047,10 +9047,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>520063</v>
+        <v>520330</v>
       </c>
       <c r="R73" t="n">
-        <v>7001569</v>
+        <v>7001396</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9109,61 +9109,45 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129193575</v>
+        <v>129193546</v>
       </c>
       <c r="B74" t="n">
-        <v>98706</v>
+        <v>57727</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="N74" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>520528</v>
+        <v>519958</v>
       </c>
       <c r="R74" t="n">
-        <v>7001465</v>
+        <v>7001542</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9200,7 +9184,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Minst 50</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9209,7 +9193,6 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -9231,7 +9214,7 @@
         <v>129193549</v>
       </c>
       <c r="B75" t="n">
-        <v>80147</v>
+        <v>80149</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9325,45 +9308,61 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129193546</v>
+        <v>129193575</v>
       </c>
       <c r="B76" t="n">
-        <v>57727</v>
+        <v>98710</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>519958</v>
+        <v>520528</v>
       </c>
       <c r="R76" t="n">
-        <v>7001542</v>
+        <v>7001465</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9400,7 +9399,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Minst 50</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9409,6 +9408,7 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 43533-2025 artfynd.xlsx
+++ b/artfynd/A 43533-2025 artfynd.xlsx
@@ -2505,7 +2505,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129127604</v>
+        <v>129128162</v>
       </c>
       <c r="B16" t="n">
         <v>80148</v>
@@ -2536,7 +2536,7 @@
       <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2545,13 +2545,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>520243</v>
+        <v>520355</v>
       </c>
       <c r="R16" t="n">
-        <v>7001423</v>
+        <v>7001412</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2590,12 +2590,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:59</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Fertil lunglav på en sälg med doftticka.</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2609,7 +2604,7 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -2647,10 +2642,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129128162</v>
+        <v>129128148</v>
       </c>
       <c r="B17" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2658,21 +2653,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2687,13 +2682,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>520355</v>
+        <v>520338</v>
       </c>
       <c r="R17" t="n">
-        <v>7001412</v>
+        <v>7001407</v>
       </c>
       <c r="S17" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2751,22 +2746,22 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark of dead wood # Betula</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2784,10 +2779,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129128148</v>
+        <v>129127604</v>
       </c>
       <c r="B18" t="n">
-        <v>80149</v>
+        <v>80148</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2795,27 +2790,27 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2824,13 +2819,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>520338</v>
+        <v>520243</v>
       </c>
       <c r="R18" t="n">
-        <v>7001407</v>
+        <v>7001423</v>
       </c>
       <c r="S18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2859,7 +2854,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2869,7 +2864,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Fertil lunglav på en sälg med doftticka.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2883,27 +2883,27 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Betula</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2921,62 +2921,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129127509</v>
+        <v>129131389</v>
       </c>
       <c r="B19" t="n">
-        <v>92138</v>
+        <v>79043</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>520242</v>
+        <v>520611</v>
       </c>
       <c r="R19" t="n">
-        <v>7001434</v>
+        <v>7001285</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3005,7 +2991,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3015,7 +3001,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3026,31 +3012,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Salix caprea</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -3067,48 +3028,62 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129131389</v>
+        <v>129127509</v>
       </c>
       <c r="B20" t="n">
-        <v>79043</v>
+        <v>92138</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>520611</v>
+        <v>520242</v>
       </c>
       <c r="R20" t="n">
-        <v>7001285</v>
+        <v>7001434</v>
       </c>
       <c r="S20" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3137,7 +3112,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3147,7 +3122,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3158,6 +3133,31 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Salix caprea</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -3174,10 +3174,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129125122</v>
+        <v>129126633</v>
       </c>
       <c r="B21" t="n">
-        <v>79043</v>
+        <v>80148</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3185,21 +3185,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3209,13 +3209,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>519973</v>
+        <v>520226</v>
       </c>
       <c r="R21" t="n">
-        <v>7001540</v>
+        <v>7001438</v>
       </c>
       <c r="S21" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3242,11 +3242,26 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På grovbarkad gammal asp.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3255,6 +3270,31 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3271,10 +3311,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129126633</v>
+        <v>129125122</v>
       </c>
       <c r="B22" t="n">
-        <v>80148</v>
+        <v>79043</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3282,21 +3322,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3306,13 +3346,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>520226</v>
+        <v>519973</v>
       </c>
       <c r="R22" t="n">
-        <v>7001438</v>
+        <v>7001540</v>
       </c>
       <c r="S22" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3339,26 +3379,11 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>11:19</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>11:19</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>På grovbarkad gammal asp.</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3367,31 +3392,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -5751,10 +5751,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129193518</v>
+        <v>129193558</v>
       </c>
       <c r="B41" t="n">
-        <v>57727</v>
+        <v>80148</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5762,21 +5762,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5786,10 +5786,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>520676</v>
+        <v>520415</v>
       </c>
       <c r="R41" t="n">
-        <v>7001377</v>
+        <v>7001416</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5822,11 +5822,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5853,10 +5848,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129193558</v>
+        <v>129193518</v>
       </c>
       <c r="B42" t="n">
-        <v>80148</v>
+        <v>57727</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5864,21 +5859,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5888,10 +5883,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>520415</v>
+        <v>520676</v>
       </c>
       <c r="R42" t="n">
-        <v>7001416</v>
+        <v>7001377</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5924,6 +5919,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6872,61 +6872,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129193581</v>
+        <v>129193523</v>
       </c>
       <c r="B52" t="n">
-        <v>98710</v>
+        <v>57727</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>520425</v>
+        <v>520478</v>
       </c>
       <c r="R52" t="n">
-        <v>7001407</v>
+        <v>7001335</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6963,7 +6947,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Minst 80</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6972,7 +6956,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6991,7 +6974,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129193523</v>
+        <v>129193517</v>
       </c>
       <c r="B53" t="n">
         <v>57727</v>
@@ -7026,10 +7009,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>520478</v>
+        <v>520301</v>
       </c>
       <c r="R53" t="n">
-        <v>7001335</v>
+        <v>7001547</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7066,7 +7049,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7093,45 +7076,61 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129193517</v>
+        <v>129193581</v>
       </c>
       <c r="B54" t="n">
-        <v>57727</v>
+        <v>98710</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>520301</v>
+        <v>520425</v>
       </c>
       <c r="R54" t="n">
-        <v>7001547</v>
+        <v>7001407</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7168,7 +7167,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Minst 80</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7177,6 +7176,7 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -7389,10 +7389,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129193561</v>
+        <v>129193524</v>
       </c>
       <c r="B57" t="n">
-        <v>80148</v>
+        <v>57727</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7400,21 +7400,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7424,10 +7424,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>520344</v>
+        <v>520478</v>
       </c>
       <c r="R57" t="n">
-        <v>7001402</v>
+        <v>7001328</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7460,6 +7460,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7486,10 +7491,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129193567</v>
+        <v>129193544</v>
       </c>
       <c r="B58" t="n">
-        <v>80148</v>
+        <v>57727</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7497,21 +7502,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7521,10 +7526,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>520184</v>
+        <v>520270</v>
       </c>
       <c r="R58" t="n">
-        <v>7001482</v>
+        <v>7001484</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7557,6 +7562,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7583,10 +7593,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129193524</v>
+        <v>129193561</v>
       </c>
       <c r="B59" t="n">
-        <v>57727</v>
+        <v>80148</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7594,21 +7604,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7618,10 +7628,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>520478</v>
+        <v>520344</v>
       </c>
       <c r="R59" t="n">
-        <v>7001328</v>
+        <v>7001402</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7654,11 +7664,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7685,10 +7690,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129193544</v>
+        <v>129193567</v>
       </c>
       <c r="B60" t="n">
-        <v>57727</v>
+        <v>80148</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7696,21 +7701,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7720,10 +7725,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>520270</v>
+        <v>520184</v>
       </c>
       <c r="R60" t="n">
-        <v>7001484</v>
+        <v>7001482</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7756,11 +7761,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -9109,10 +9109,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129193546</v>
+        <v>129193549</v>
       </c>
       <c r="B74" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9120,21 +9120,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -9144,10 +9144,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>519958</v>
+        <v>520345</v>
       </c>
       <c r="R74" t="n">
-        <v>7001542</v>
+        <v>7001396</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9180,11 +9180,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9211,10 +9206,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129193549</v>
+        <v>129193546</v>
       </c>
       <c r="B75" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9222,21 +9217,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -9246,10 +9241,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>520345</v>
+        <v>519958</v>
       </c>
       <c r="R75" t="n">
-        <v>7001396</v>
+        <v>7001542</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9282,6 +9277,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD75" t="b">

--- a/artfynd/A 43533-2025 artfynd.xlsx
+++ b/artfynd/A 43533-2025 artfynd.xlsx
@@ -675,47 +675,38 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129135545</v>
+        <v>129126527</v>
       </c>
       <c r="B2" t="n">
-        <v>98710</v>
+        <v>80149</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>520564</v>
+        <v>520189</v>
       </c>
       <c r="R2" t="n">
-        <v>7001441</v>
+        <v>7001448</v>
       </c>
       <c r="S2" t="n">
         <v>9</v>
@@ -759,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -783,7 +779,27 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -804,7 +820,7 @@
         <v>129135852</v>
       </c>
       <c r="B3" t="n">
-        <v>99044</v>
+        <v>99046</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,38 +934,47 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129126527</v>
+        <v>129135545</v>
       </c>
       <c r="B4" t="n">
-        <v>80148</v>
+        <v>98712</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -958,10 +983,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>520189</v>
+        <v>520564</v>
       </c>
       <c r="R4" t="n">
-        <v>7001448</v>
+        <v>7001441</v>
       </c>
       <c r="S4" t="n">
         <v>9</v>
@@ -993,7 +1018,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,12 +1028,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:12</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1022,27 +1042,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1063,7 +1063,7 @@
         <v>129131270</v>
       </c>
       <c r="B5" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1182,38 +1182,47 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129127182</v>
+        <v>129126843</v>
       </c>
       <c r="B6" t="n">
-        <v>57727</v>
+        <v>98712</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1227,13 +1236,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>520186</v>
+        <v>520211</v>
       </c>
       <c r="R6" t="n">
-        <v>7001459</v>
+        <v>7001475</v>
       </c>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1262,7 +1271,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1272,12 +1281,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran  intill en gammal sälg.</t>
+          <t>Minst 100 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1292,26 +1301,6 @@
       <c r="AH6" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1329,7 +1318,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129131350</v>
+        <v>129127182</v>
       </c>
       <c r="B7" t="n">
         <v>57727</v>
@@ -1360,7 +1349,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1374,10 +1363,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>520520</v>
+        <v>520186</v>
       </c>
       <c r="R7" t="n">
-        <v>7001311</v>
+        <v>7001459</v>
       </c>
       <c r="S7" t="n">
         <v>8</v>
@@ -1409,7 +1398,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1419,12 +1408,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack, enstaka färska och rikligt med äldre på en tall.</t>
+          <t>Ringhack, äldre, på stambasen av en gran  intill en gammal sälg.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1438,17 +1427,17 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -1458,7 +1447,7 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1476,47 +1465,38 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129126843</v>
+        <v>129131350</v>
       </c>
       <c r="B8" t="n">
-        <v>98710</v>
+        <v>57727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1530,13 +1510,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>520211</v>
+        <v>520520</v>
       </c>
       <c r="R8" t="n">
-        <v>7001475</v>
+        <v>7001311</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1565,7 +1545,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1575,12 +1555,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Minst 100 plantor inom ca 0,5 m2 yta.</t>
+          <t>Ringhack, enstaka färska och rikligt med äldre på en tall.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1594,7 +1574,27 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1615,7 +1615,7 @@
         <v>129135692</v>
       </c>
       <c r="B9" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>129135867</v>
       </c>
       <c r="B10" t="n">
-        <v>100899</v>
+        <v>100901</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1851,10 +1851,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129126617</v>
+        <v>129128175</v>
       </c>
       <c r="B11" t="n">
-        <v>80148</v>
+        <v>79044</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1862,42 +1862,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>520219</v>
+        <v>520329</v>
       </c>
       <c r="R11" t="n">
-        <v>7001429</v>
+        <v>7001400</v>
       </c>
       <c r="S11" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1926,7 +1921,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1936,7 +1931,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1950,17 +1945,17 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2120,10 +2115,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129128175</v>
+        <v>129126617</v>
       </c>
       <c r="B13" t="n">
-        <v>79043</v>
+        <v>80149</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2131,37 +2126,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>520329</v>
+        <v>520219</v>
       </c>
       <c r="R13" t="n">
-        <v>7001400</v>
+        <v>7001429</v>
       </c>
       <c r="S13" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2214,17 +2214,17 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2245,7 +2245,7 @@
         <v>129126547</v>
       </c>
       <c r="B14" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2382,7 +2382,7 @@
         <v>129135822</v>
       </c>
       <c r="B15" t="n">
-        <v>104179</v>
+        <v>104181</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2505,10 +2505,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129128162</v>
+        <v>129128148</v>
       </c>
       <c r="B16" t="n">
-        <v>80148</v>
+        <v>80150</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2516,21 +2516,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2545,13 +2545,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>520355</v>
+        <v>520338</v>
       </c>
       <c r="R16" t="n">
-        <v>7001412</v>
+        <v>7001407</v>
       </c>
       <c r="S16" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2609,22 +2609,22 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark of dead wood # Betula</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2642,7 +2642,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129128148</v>
+        <v>129127604</v>
       </c>
       <c r="B17" t="n">
         <v>80149</v>
@@ -2653,27 +2653,27 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>520338</v>
+        <v>520243</v>
       </c>
       <c r="R17" t="n">
-        <v>7001407</v>
+        <v>7001423</v>
       </c>
       <c r="S17" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2727,7 +2727,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Fertil lunglav på en sälg med doftticka.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2741,27 +2746,27 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Betula</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2779,10 +2784,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129127604</v>
+        <v>129128162</v>
       </c>
       <c r="B18" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2810,7 +2815,7 @@
       <c r="I18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2819,13 +2824,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>520243</v>
+        <v>520355</v>
       </c>
       <c r="R18" t="n">
-        <v>7001423</v>
+        <v>7001412</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2854,7 +2859,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2864,12 +2869,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:59</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Fertil lunglav på en sälg med doftticka.</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2883,7 +2883,7 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -2924,7 +2924,7 @@
         <v>129131389</v>
       </c>
       <c r="B19" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
         <v>129127509</v>
       </c>
       <c r="B20" t="n">
-        <v>92138</v>
+        <v>92140</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3174,10 +3174,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129126633</v>
+        <v>129125122</v>
       </c>
       <c r="B21" t="n">
-        <v>80148</v>
+        <v>79044</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3185,21 +3185,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3209,13 +3209,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>520226</v>
+        <v>519973</v>
       </c>
       <c r="R21" t="n">
-        <v>7001438</v>
+        <v>7001540</v>
       </c>
       <c r="S21" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3242,26 +3242,11 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>11:19</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>11:19</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På grovbarkad gammal asp.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3270,31 +3255,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3311,10 +3271,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129125122</v>
+        <v>129126633</v>
       </c>
       <c r="B22" t="n">
-        <v>79043</v>
+        <v>80149</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3322,21 +3282,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3346,13 +3306,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>519973</v>
+        <v>520226</v>
       </c>
       <c r="R22" t="n">
-        <v>7001540</v>
+        <v>7001438</v>
       </c>
       <c r="S22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3379,11 +3339,26 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På grovbarkad gammal asp.</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3392,6 +3367,31 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3408,10 +3408,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129136001</v>
+        <v>129128128</v>
       </c>
       <c r="B23" t="n">
-        <v>79043</v>
+        <v>80150</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3419,37 +3419,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>520012</v>
+        <v>520340</v>
       </c>
       <c r="R23" t="n">
-        <v>7001652</v>
+        <v>7001392</v>
       </c>
       <c r="S23" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3478,7 +3483,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3488,7 +3493,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3499,6 +3504,31 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3515,10 +3545,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129126703</v>
+        <v>129136001</v>
       </c>
       <c r="B24" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3550,13 +3580,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>520253</v>
+        <v>520012</v>
       </c>
       <c r="R24" t="n">
-        <v>7001454</v>
+        <v>7001652</v>
       </c>
       <c r="S24" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3585,7 +3615,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3595,7 +3625,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3606,31 +3636,6 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3647,10 +3652,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129128128</v>
+        <v>129126703</v>
       </c>
       <c r="B25" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3658,39 +3663,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>520340</v>
+        <v>520253</v>
       </c>
       <c r="R25" t="n">
-        <v>7001392</v>
+        <v>7001454</v>
       </c>
       <c r="S25" t="n">
         <v>9</v>
@@ -3722,7 +3722,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3732,7 +3732,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3746,27 +3746,27 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3787,7 +3787,7 @@
         <v>129131479</v>
       </c>
       <c r="B26" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3919,7 +3919,7 @@
         <v>129127211</v>
       </c>
       <c r="B27" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4053,67 +4053,48 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129127084</v>
+        <v>129131418</v>
       </c>
       <c r="B28" t="n">
-        <v>98710</v>
+        <v>79044</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>520203</v>
+        <v>520682</v>
       </c>
       <c r="R28" t="n">
-        <v>7001453</v>
+        <v>7001354</v>
       </c>
       <c r="S28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4142,7 +4123,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4152,7 +4133,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4166,7 +4147,27 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4184,10 +4185,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129131418</v>
+        <v>129124933</v>
       </c>
       <c r="B29" t="n">
-        <v>79043</v>
+        <v>57727</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4195,37 +4196,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>520682</v>
+        <v>519886</v>
       </c>
       <c r="R29" t="n">
-        <v>7001354</v>
+        <v>7001592</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4254,7 +4260,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4264,7 +4270,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>09:39</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran i hyggeskanten.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4278,7 +4289,7 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
@@ -4293,12 +4304,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4316,38 +4327,52 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129124933</v>
+        <v>129127084</v>
       </c>
       <c r="B30" t="n">
-        <v>57727</v>
+        <v>98712</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4356,13 +4381,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>519886</v>
+        <v>520203</v>
       </c>
       <c r="R30" t="n">
-        <v>7001592</v>
+        <v>7001453</v>
       </c>
       <c r="S30" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4391,7 +4416,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4401,12 +4426,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:39</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran i hyggeskanten.</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4421,26 +4441,6 @@
       <c r="AH30" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4461,7 +4461,7 @@
         <v>129135649</v>
       </c>
       <c r="B31" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4598,7 +4598,7 @@
         <v>129125106</v>
       </c>
       <c r="B32" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4725,7 +4725,7 @@
         <v>129135770</v>
       </c>
       <c r="B33" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4856,7 +4856,7 @@
         <v>129128345</v>
       </c>
       <c r="B34" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4993,7 +4993,7 @@
         <v>129128023</v>
       </c>
       <c r="B35" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5135,7 +5135,7 @@
         <v>129135454</v>
       </c>
       <c r="B36" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5277,7 +5277,7 @@
         <v>129135677</v>
       </c>
       <c r="B37" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5384,7 +5384,7 @@
         <v>129128320</v>
       </c>
       <c r="B38" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5515,7 +5515,7 @@
         <v>129135697</v>
       </c>
       <c r="B39" t="n">
-        <v>80177</v>
+        <v>80178</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5754,7 +5754,7 @@
         <v>129193558</v>
       </c>
       <c r="B41" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5950,32 +5950,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129193568</v>
+        <v>129193576</v>
       </c>
       <c r="B43" t="n">
-        <v>80148</v>
+        <v>98712</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5985,10 +5985,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>520159</v>
+        <v>520675</v>
       </c>
       <c r="R43" t="n">
-        <v>7001489</v>
+        <v>7001377</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6047,10 +6047,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129193576</v>
+        <v>129193582</v>
       </c>
       <c r="B44" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6075,17 +6075,33 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>520675</v>
+        <v>520388</v>
       </c>
       <c r="R44" t="n">
-        <v>7001377</v>
+        <v>7001418</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6120,12 +6136,18 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Minst 50</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -6144,61 +6166,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129193582</v>
+        <v>129193568</v>
       </c>
       <c r="B45" t="n">
-        <v>98710</v>
+        <v>80149</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>520388</v>
+        <v>520159</v>
       </c>
       <c r="R45" t="n">
-        <v>7001418</v>
+        <v>7001489</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6233,18 +6239,12 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Minst 50</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -6368,7 +6368,7 @@
         <v>129193583</v>
       </c>
       <c r="B47" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6487,7 +6487,7 @@
         <v>129193565</v>
       </c>
       <c r="B48" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6584,7 +6584,7 @@
         <v>129193591</v>
       </c>
       <c r="B49" t="n">
-        <v>92861</v>
+        <v>92863</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6681,7 +6681,7 @@
         <v>129193590</v>
       </c>
       <c r="B50" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6778,7 +6778,7 @@
         <v>129193566</v>
       </c>
       <c r="B51" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -7079,7 +7079,7 @@
         <v>129193581</v>
       </c>
       <c r="B54" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7198,7 +7198,7 @@
         <v>129193570</v>
       </c>
       <c r="B55" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7295,7 +7295,7 @@
         <v>129193550</v>
       </c>
       <c r="B56" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7389,10 +7389,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129193524</v>
+        <v>129193561</v>
       </c>
       <c r="B57" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7400,21 +7400,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7424,10 +7424,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>520478</v>
+        <v>520344</v>
       </c>
       <c r="R57" t="n">
-        <v>7001328</v>
+        <v>7001402</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7460,11 +7460,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7491,10 +7486,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129193544</v>
+        <v>129193567</v>
       </c>
       <c r="B58" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7502,21 +7497,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7526,10 +7521,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>520270</v>
+        <v>520184</v>
       </c>
       <c r="R58" t="n">
-        <v>7001484</v>
+        <v>7001482</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7562,11 +7557,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7593,10 +7583,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129193561</v>
+        <v>129193524</v>
       </c>
       <c r="B59" t="n">
-        <v>80148</v>
+        <v>57727</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7604,21 +7594,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7628,10 +7618,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>520344</v>
+        <v>520478</v>
       </c>
       <c r="R59" t="n">
-        <v>7001402</v>
+        <v>7001328</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7664,6 +7654,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7690,10 +7685,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129193567</v>
+        <v>129193544</v>
       </c>
       <c r="B60" t="n">
-        <v>80148</v>
+        <v>57727</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7701,21 +7696,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7725,10 +7720,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>520184</v>
+        <v>520270</v>
       </c>
       <c r="R60" t="n">
-        <v>7001482</v>
+        <v>7001484</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7761,6 +7756,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7787,45 +7787,57 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129193564</v>
+        <v>129193585</v>
       </c>
       <c r="B61" t="n">
-        <v>80148</v>
+        <v>98712</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>520225</v>
+        <v>520122</v>
       </c>
       <c r="R61" t="n">
-        <v>7001483</v>
+        <v>7001476</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7860,12 +7872,18 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Fler än 200</t>
+        </is>
+      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7884,10 +7902,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129193557</v>
+        <v>129193564</v>
       </c>
       <c r="B62" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7919,10 +7937,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>520374</v>
+        <v>520225</v>
       </c>
       <c r="R62" t="n">
-        <v>7001329</v>
+        <v>7001483</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7981,57 +7999,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129193585</v>
+        <v>129193557</v>
       </c>
       <c r="B63" t="n">
-        <v>98710</v>
+        <v>80149</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>520122</v>
+        <v>520374</v>
       </c>
       <c r="R63" t="n">
-        <v>7001476</v>
+        <v>7001329</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8066,18 +8072,12 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Fler än 200</t>
-        </is>
-      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -8096,32 +8096,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129193560</v>
+        <v>129193593</v>
       </c>
       <c r="B64" t="n">
-        <v>80148</v>
+        <v>100901</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>222498</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -8131,10 +8131,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>520346</v>
+        <v>520101</v>
       </c>
       <c r="R64" t="n">
-        <v>7001396</v>
+        <v>7001658</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8193,10 +8193,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129193569</v>
+        <v>129193560</v>
       </c>
       <c r="B65" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8228,10 +8228,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>520094</v>
+        <v>520346</v>
       </c>
       <c r="R65" t="n">
-        <v>7001525</v>
+        <v>7001396</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8290,32 +8290,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129193593</v>
+        <v>129193569</v>
       </c>
       <c r="B66" t="n">
-        <v>100899</v>
+        <v>80149</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>222498</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -8325,10 +8325,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>520101</v>
+        <v>520094</v>
       </c>
       <c r="R66" t="n">
-        <v>7001658</v>
+        <v>7001525</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8390,7 +8390,7 @@
         <v>129193562</v>
       </c>
       <c r="B67" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8702,7 +8702,7 @@
         <v>129193584</v>
       </c>
       <c r="B70" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8821,7 +8821,7 @@
         <v>129193563</v>
       </c>
       <c r="B71" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8915,32 +8915,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129193548</v>
+        <v>129193559</v>
       </c>
       <c r="B72" t="n">
-        <v>92498</v>
+        <v>80149</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4769</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8950,10 +8950,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>520063</v>
+        <v>520330</v>
       </c>
       <c r="R72" t="n">
-        <v>7001569</v>
+        <v>7001396</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9012,32 +9012,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129193559</v>
+        <v>129193548</v>
       </c>
       <c r="B73" t="n">
-        <v>80148</v>
+        <v>92500</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>4769</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -9047,10 +9047,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>520330</v>
+        <v>520063</v>
       </c>
       <c r="R73" t="n">
-        <v>7001396</v>
+        <v>7001569</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9109,10 +9109,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129193549</v>
+        <v>129193546</v>
       </c>
       <c r="B74" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9120,21 +9120,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -9144,10 +9144,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>520345</v>
+        <v>519958</v>
       </c>
       <c r="R74" t="n">
-        <v>7001396</v>
+        <v>7001542</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9180,6 +9180,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9206,10 +9211,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129193546</v>
+        <v>129193549</v>
       </c>
       <c r="B75" t="n">
-        <v>57727</v>
+        <v>80150</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9217,21 +9222,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -9241,10 +9246,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>519958</v>
+        <v>520345</v>
       </c>
       <c r="R75" t="n">
-        <v>7001542</v>
+        <v>7001396</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9277,11 +9282,6 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9311,7 +9311,7 @@
         <v>129193575</v>
       </c>
       <c r="B76" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 43533-2025 artfynd.xlsx
+++ b/artfynd/A 43533-2025 artfynd.xlsx
@@ -820,7 +820,7 @@
         <v>129135852</v>
       </c>
       <c r="B3" t="n">
-        <v>99046</v>
+        <v>99050</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>129135545</v>
       </c>
       <c r="B4" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1185,7 +1185,7 @@
         <v>129126843</v>
       </c>
       <c r="B6" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>129135867</v>
       </c>
       <c r="B10" t="n">
-        <v>100901</v>
+        <v>100905</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1851,10 +1851,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129128175</v>
+        <v>129126617</v>
       </c>
       <c r="B11" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1862,37 +1862,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>520329</v>
+        <v>520219</v>
       </c>
       <c r="R11" t="n">
-        <v>7001400</v>
+        <v>7001429</v>
       </c>
       <c r="S11" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1921,7 +1926,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1931,7 +1936,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1945,17 +1950,17 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2115,10 +2120,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129126617</v>
+        <v>129128175</v>
       </c>
       <c r="B13" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2126,42 +2131,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>520219</v>
+        <v>520329</v>
       </c>
       <c r="R13" t="n">
-        <v>7001429</v>
+        <v>7001400</v>
       </c>
       <c r="S13" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2214,17 +2214,17 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2382,7 +2382,7 @@
         <v>129135822</v>
       </c>
       <c r="B15" t="n">
-        <v>104181</v>
+        <v>104185</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2921,48 +2921,62 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129131389</v>
+        <v>129127509</v>
       </c>
       <c r="B19" t="n">
-        <v>79044</v>
+        <v>92144</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>520611</v>
+        <v>520242</v>
       </c>
       <c r="R19" t="n">
-        <v>7001285</v>
+        <v>7001434</v>
       </c>
       <c r="S19" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2991,7 +3005,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3001,7 +3015,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3012,6 +3026,31 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Salix caprea</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -3028,62 +3067,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129127509</v>
+        <v>129131389</v>
       </c>
       <c r="B20" t="n">
-        <v>92140</v>
+        <v>79044</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>520242</v>
+        <v>520611</v>
       </c>
       <c r="R20" t="n">
-        <v>7001434</v>
+        <v>7001285</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3112,7 +3137,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3122,7 +3147,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3133,31 +3158,6 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Salix caprea</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -4330,7 +4330,7 @@
         <v>129127084</v>
       </c>
       <c r="B30" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4722,62 +4722,48 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129135770</v>
+        <v>129128345</v>
       </c>
       <c r="B33" t="n">
-        <v>98712</v>
+        <v>79044</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>520226</v>
+        <v>520362</v>
       </c>
       <c r="R33" t="n">
-        <v>7001601</v>
+        <v>7001381</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4806,7 +4792,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4816,12 +4802,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Minst 120 plantor inom ca 1 m2 yta.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4835,7 +4821,27 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4853,48 +4859,62 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129128345</v>
+        <v>129135770</v>
       </c>
       <c r="B34" t="n">
-        <v>79044</v>
+        <v>98716</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>520362</v>
+        <v>520226</v>
       </c>
       <c r="R34" t="n">
-        <v>7001381</v>
+        <v>7001601</v>
       </c>
       <c r="S34" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4923,7 +4943,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4933,12 +4953,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Minst 120 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4952,27 +4972,7 @@
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4990,7 +4990,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129128023</v>
+        <v>129135454</v>
       </c>
       <c r="B35" t="n">
         <v>80149</v>
@@ -5030,10 +5030,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>520326</v>
+        <v>520630</v>
       </c>
       <c r="R35" t="n">
-        <v>7001449</v>
+        <v>7001400</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5065,7 +5065,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5075,12 +5075,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Rikligt med bålar på en rakväxt björk.</t>
+          <t>På både gran och sälg.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5094,27 +5094,27 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Betula</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5132,7 +5132,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129135454</v>
+        <v>129128023</v>
       </c>
       <c r="B36" t="n">
         <v>80149</v>
@@ -5172,10 +5172,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>520630</v>
+        <v>520326</v>
       </c>
       <c r="R36" t="n">
-        <v>7001400</v>
+        <v>7001449</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På både gran och sälg.</t>
+          <t>Rikligt med bålar på en rakväxt björk.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5236,27 +5236,27 @@
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Betula</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5274,48 +5274,62 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129135677</v>
+        <v>129128320</v>
       </c>
       <c r="B37" t="n">
-        <v>79044</v>
+        <v>98716</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>520346</v>
+        <v>520352</v>
       </c>
       <c r="R37" t="n">
-        <v>7001536</v>
+        <v>7001397</v>
       </c>
       <c r="S37" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5344,7 +5358,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5354,7 +5368,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Minst 10 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5365,6 +5384,11 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -5381,62 +5405,48 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129128320</v>
+        <v>129135677</v>
       </c>
       <c r="B38" t="n">
-        <v>98712</v>
+        <v>79044</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>520352</v>
+        <v>520346</v>
       </c>
       <c r="R38" t="n">
-        <v>7001397</v>
+        <v>7001536</v>
       </c>
       <c r="S38" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5465,7 +5475,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5475,12 +5485,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:20</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Minst 10 plantor inom ca 0,5 m2 yta.</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5491,11 +5496,6 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -5751,10 +5751,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129193558</v>
+        <v>129193518</v>
       </c>
       <c r="B41" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5762,21 +5762,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5786,10 +5786,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>520415</v>
+        <v>520676</v>
       </c>
       <c r="R41" t="n">
-        <v>7001416</v>
+        <v>7001377</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5822,6 +5822,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5848,10 +5853,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129193518</v>
+        <v>129193558</v>
       </c>
       <c r="B42" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5859,21 +5864,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5883,10 +5888,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>520676</v>
+        <v>520415</v>
       </c>
       <c r="R42" t="n">
-        <v>7001377</v>
+        <v>7001416</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5919,11 +5924,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5950,32 +5950,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129193576</v>
+        <v>129193568</v>
       </c>
       <c r="B43" t="n">
-        <v>98712</v>
+        <v>80149</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5985,10 +5985,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>520675</v>
+        <v>520159</v>
       </c>
       <c r="R43" t="n">
-        <v>7001377</v>
+        <v>7001489</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6047,10 +6047,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129193582</v>
+        <v>129193576</v>
       </c>
       <c r="B44" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6075,33 +6075,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>520388</v>
+        <v>520675</v>
       </c>
       <c r="R44" t="n">
-        <v>7001418</v>
+        <v>7001377</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6136,18 +6120,12 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Minst 50</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -6166,45 +6144,61 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129193568</v>
+        <v>129193582</v>
       </c>
       <c r="B45" t="n">
-        <v>80149</v>
+        <v>98716</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>520159</v>
+        <v>520388</v>
       </c>
       <c r="R45" t="n">
-        <v>7001489</v>
+        <v>7001418</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6239,12 +6233,18 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Minst 50</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -6368,7 +6368,7 @@
         <v>129193583</v>
       </c>
       <c r="B47" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6584,7 +6584,7 @@
         <v>129193591</v>
       </c>
       <c r="B49" t="n">
-        <v>92863</v>
+        <v>92867</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6678,10 +6678,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129193590</v>
+        <v>129193566</v>
       </c>
       <c r="B50" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6689,21 +6689,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6713,10 +6713,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>520187</v>
+        <v>520180</v>
       </c>
       <c r="R50" t="n">
-        <v>7001471</v>
+        <v>7001458</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6775,10 +6775,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129193566</v>
+        <v>129193590</v>
       </c>
       <c r="B51" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6786,21 +6786,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6810,10 +6810,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>520180</v>
+        <v>520187</v>
       </c>
       <c r="R51" t="n">
-        <v>7001458</v>
+        <v>7001471</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -7079,7 +7079,7 @@
         <v>129193581</v>
       </c>
       <c r="B54" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7787,57 +7787,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129193585</v>
+        <v>129193564</v>
       </c>
       <c r="B61" t="n">
-        <v>98712</v>
+        <v>80149</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>520122</v>
+        <v>520225</v>
       </c>
       <c r="R61" t="n">
-        <v>7001476</v>
+        <v>7001483</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7872,18 +7860,12 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Fler än 200</t>
-        </is>
-      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7902,7 +7884,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129193564</v>
+        <v>129193557</v>
       </c>
       <c r="B62" t="n">
         <v>80149</v>
@@ -7937,10 +7919,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>520225</v>
+        <v>520374</v>
       </c>
       <c r="R62" t="n">
-        <v>7001483</v>
+        <v>7001329</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7999,45 +7981,57 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129193557</v>
+        <v>129193585</v>
       </c>
       <c r="B63" t="n">
-        <v>80149</v>
+        <v>98716</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>520374</v>
+        <v>520122</v>
       </c>
       <c r="R63" t="n">
-        <v>7001329</v>
+        <v>7001476</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8072,12 +8066,18 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Fler än 200</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -8096,32 +8096,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129193593</v>
+        <v>129193560</v>
       </c>
       <c r="B64" t="n">
-        <v>100901</v>
+        <v>80149</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>222498</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -8131,10 +8131,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>520101</v>
+        <v>520346</v>
       </c>
       <c r="R64" t="n">
-        <v>7001658</v>
+        <v>7001396</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8193,7 +8193,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129193560</v>
+        <v>129193569</v>
       </c>
       <c r="B65" t="n">
         <v>80149</v>
@@ -8228,10 +8228,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>520346</v>
+        <v>520094</v>
       </c>
       <c r="R65" t="n">
-        <v>7001396</v>
+        <v>7001525</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8290,32 +8290,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129193569</v>
+        <v>129193593</v>
       </c>
       <c r="B66" t="n">
-        <v>80149</v>
+        <v>100905</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>222498</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -8325,10 +8325,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>520094</v>
+        <v>520101</v>
       </c>
       <c r="R66" t="n">
-        <v>7001525</v>
+        <v>7001658</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8586,46 +8586,46 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129193573</v>
+        <v>129193584</v>
       </c>
       <c r="B69" t="n">
-        <v>57831</v>
+        <v>98716</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>103031</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N69" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -8637,10 +8637,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>520153</v>
+        <v>520320</v>
       </c>
       <c r="R69" t="n">
-        <v>7001500</v>
+        <v>7001451</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8675,12 +8675,18 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Minst 100</t>
+        </is>
+      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -8699,46 +8705,46 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129193584</v>
+        <v>129193573</v>
       </c>
       <c r="B70" t="n">
-        <v>98712</v>
+        <v>57831</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>103031</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N70" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -8750,10 +8756,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>520320</v>
+        <v>520153</v>
       </c>
       <c r="R70" t="n">
-        <v>7001451</v>
+        <v>7001500</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8788,18 +8794,12 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Minst 100</t>
-        </is>
-      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -8915,32 +8915,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129193559</v>
+        <v>129193548</v>
       </c>
       <c r="B72" t="n">
-        <v>80149</v>
+        <v>92504</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>4769</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8950,10 +8950,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>520330</v>
+        <v>520063</v>
       </c>
       <c r="R72" t="n">
-        <v>7001396</v>
+        <v>7001569</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9012,32 +9012,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129193548</v>
+        <v>129193559</v>
       </c>
       <c r="B73" t="n">
-        <v>92500</v>
+        <v>80149</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4769</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -9047,10 +9047,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>520063</v>
+        <v>520330</v>
       </c>
       <c r="R73" t="n">
-        <v>7001569</v>
+        <v>7001396</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9109,10 +9109,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129193546</v>
+        <v>129193549</v>
       </c>
       <c r="B74" t="n">
-        <v>57727</v>
+        <v>80150</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9120,21 +9120,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -9144,10 +9144,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>519958</v>
+        <v>520345</v>
       </c>
       <c r="R74" t="n">
-        <v>7001542</v>
+        <v>7001396</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9180,11 +9180,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9211,10 +9206,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129193549</v>
+        <v>129193546</v>
       </c>
       <c r="B75" t="n">
-        <v>80150</v>
+        <v>57727</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9222,21 +9217,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -9246,10 +9241,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>520345</v>
+        <v>519958</v>
       </c>
       <c r="R75" t="n">
-        <v>7001396</v>
+        <v>7001542</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9282,6 +9277,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9311,7 +9311,7 @@
         <v>129193575</v>
       </c>
       <c r="B76" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 43533-2025 artfynd.xlsx
+++ b/artfynd/A 43533-2025 artfynd.xlsx
@@ -675,38 +675,38 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129126527</v>
+        <v>129135852</v>
       </c>
       <c r="B2" t="n">
-        <v>80149</v>
+        <v>99058</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>219880</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>gulnande löv/blad</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>520189</v>
+        <v>520213</v>
       </c>
       <c r="R2" t="n">
-        <v>7001448</v>
+        <v>7001609</v>
       </c>
       <c r="S2" t="n">
         <v>9</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:12</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,27 +774,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -817,38 +792,47 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129135852</v>
+        <v>129135545</v>
       </c>
       <c r="B3" t="n">
-        <v>99050</v>
+        <v>98724</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219880</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>gulnande löv/blad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -857,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>520213</v>
+        <v>520564</v>
       </c>
       <c r="R3" t="n">
-        <v>7001609</v>
+        <v>7001441</v>
       </c>
       <c r="S3" t="n">
         <v>9</v>
@@ -892,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -902,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -934,47 +918,38 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129135545</v>
+        <v>129126527</v>
       </c>
       <c r="B4" t="n">
-        <v>98716</v>
+        <v>80149</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -983,10 +958,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>520564</v>
+        <v>520189</v>
       </c>
       <c r="R4" t="n">
-        <v>7001441</v>
+        <v>7001448</v>
       </c>
       <c r="S4" t="n">
         <v>9</v>
@@ -1018,7 +993,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1028,7 +1003,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1042,7 +1022,27 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1182,47 +1182,38 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129126843</v>
+        <v>129127182</v>
       </c>
       <c r="B6" t="n">
-        <v>98716</v>
+        <v>57727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1236,13 +1227,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>520211</v>
+        <v>520186</v>
       </c>
       <c r="R6" t="n">
-        <v>7001475</v>
+        <v>7001459</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1271,7 +1262,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1281,12 +1272,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Minst 100 plantor inom ca 0,5 m2 yta.</t>
+          <t>Ringhack, äldre, på stambasen av en gran  intill en gammal sälg.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1301,6 +1292,26 @@
       <c r="AH6" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1318,7 +1329,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129127182</v>
+        <v>129131350</v>
       </c>
       <c r="B7" t="n">
         <v>57727</v>
@@ -1349,7 +1360,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1363,10 +1374,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>520186</v>
+        <v>520520</v>
       </c>
       <c r="R7" t="n">
-        <v>7001459</v>
+        <v>7001311</v>
       </c>
       <c r="S7" t="n">
         <v>8</v>
@@ -1398,7 +1409,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1408,12 +1419,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran  intill en gammal sälg.</t>
+          <t>Ringhack, enstaka färska och rikligt med äldre på en tall.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1427,17 +1438,17 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -1447,7 +1458,7 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Stem on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1465,38 +1476,47 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129131350</v>
+        <v>129126843</v>
       </c>
       <c r="B8" t="n">
-        <v>57727</v>
+        <v>98724</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1510,13 +1530,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>520520</v>
+        <v>520211</v>
       </c>
       <c r="R8" t="n">
-        <v>7001311</v>
+        <v>7001475</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1545,7 +1565,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1555,12 +1575,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack, enstaka färska och rikligt med äldre på en tall.</t>
+          <t>Minst 100 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1574,27 +1594,7 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1612,38 +1612,38 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129135692</v>
+        <v>129135867</v>
       </c>
       <c r="B9" t="n">
-        <v>80149</v>
+        <v>100913</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1652,13 +1652,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>520343</v>
+        <v>520192</v>
       </c>
       <c r="R9" t="n">
-        <v>7001533</v>
+        <v>7001635</v>
       </c>
       <c r="S9" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1685,21 +1685,11 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>18:06</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>18:06</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1708,31 +1698,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1749,38 +1714,38 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129135867</v>
+        <v>129135692</v>
       </c>
       <c r="B10" t="n">
-        <v>100905</v>
+        <v>80149</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1789,13 +1754,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>520192</v>
+        <v>520343</v>
       </c>
       <c r="R10" t="n">
-        <v>7001635</v>
+        <v>7001533</v>
       </c>
       <c r="S10" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1822,11 +1787,21 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>18:06</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>18:06</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1835,6 +1810,31 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1851,10 +1851,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129126617</v>
+        <v>129127736</v>
       </c>
       <c r="B11" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1862,27 +1862,27 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1891,13 +1891,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>520219</v>
+        <v>520237</v>
       </c>
       <c r="R11" t="n">
-        <v>7001429</v>
+        <v>7001416</v>
       </c>
       <c r="S11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1936,7 +1936,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1948,19 +1953,29 @@
       <c r="AG11" t="b">
         <v>0</v>
       </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1978,10 +1993,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129127736</v>
+        <v>129128175</v>
       </c>
       <c r="B12" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1989,42 +2004,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>520237</v>
+        <v>520329</v>
       </c>
       <c r="R12" t="n">
-        <v>7001416</v>
+        <v>7001400</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2053,7 +2063,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2063,12 +2073,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:01</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2080,11 +2085,6 @@
       <c r="AG12" t="b">
         <v>0</v>
       </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AJ12" t="inlineStr">
         <is>
           <t>gran</t>
@@ -2095,14 +2095,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2120,10 +2115,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129128175</v>
+        <v>129126617</v>
       </c>
       <c r="B13" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2131,37 +2126,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>520329</v>
+        <v>520219</v>
       </c>
       <c r="R13" t="n">
-        <v>7001400</v>
+        <v>7001429</v>
       </c>
       <c r="S13" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2214,17 +2214,17 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2382,7 +2382,7 @@
         <v>129135822</v>
       </c>
       <c r="B15" t="n">
-        <v>104185</v>
+        <v>104195</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2921,62 +2921,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129127509</v>
+        <v>129131389</v>
       </c>
       <c r="B19" t="n">
-        <v>92144</v>
+        <v>79044</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>520242</v>
+        <v>520611</v>
       </c>
       <c r="R19" t="n">
-        <v>7001434</v>
+        <v>7001285</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3005,7 +2991,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3015,7 +3001,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3026,31 +3012,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Salix caprea</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -3067,48 +3028,62 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129131389</v>
+        <v>129127509</v>
       </c>
       <c r="B20" t="n">
-        <v>79044</v>
+        <v>92145</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>520611</v>
+        <v>520242</v>
       </c>
       <c r="R20" t="n">
-        <v>7001285</v>
+        <v>7001434</v>
       </c>
       <c r="S20" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3137,7 +3112,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3147,7 +3122,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3158,6 +3133,31 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Salix caprea</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -3408,10 +3408,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129128128</v>
+        <v>129136001</v>
       </c>
       <c r="B23" t="n">
-        <v>80150</v>
+        <v>79044</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3419,42 +3419,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>520340</v>
+        <v>520012</v>
       </c>
       <c r="R23" t="n">
-        <v>7001392</v>
+        <v>7001652</v>
       </c>
       <c r="S23" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3483,7 +3478,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3493,7 +3488,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3504,31 +3499,6 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3545,7 +3515,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129136001</v>
+        <v>129126703</v>
       </c>
       <c r="B24" t="n">
         <v>79044</v>
@@ -3580,13 +3550,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>520012</v>
+        <v>520253</v>
       </c>
       <c r="R24" t="n">
-        <v>7001652</v>
+        <v>7001454</v>
       </c>
       <c r="S24" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3615,7 +3585,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3625,7 +3595,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3636,6 +3606,31 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3652,10 +3647,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129126703</v>
+        <v>129128128</v>
       </c>
       <c r="B25" t="n">
-        <v>79044</v>
+        <v>80150</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3663,34 +3658,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>520253</v>
+        <v>520340</v>
       </c>
       <c r="R25" t="n">
-        <v>7001454</v>
+        <v>7001392</v>
       </c>
       <c r="S25" t="n">
         <v>9</v>
@@ -3722,7 +3722,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3732,7 +3732,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3746,27 +3746,27 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -4330,7 +4330,7 @@
         <v>129127084</v>
       </c>
       <c r="B30" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4862,7 +4862,7 @@
         <v>129135770</v>
       </c>
       <c r="B34" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4990,7 +4990,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129135454</v>
+        <v>129128023</v>
       </c>
       <c r="B35" t="n">
         <v>80149</v>
@@ -5030,10 +5030,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>520630</v>
+        <v>520326</v>
       </c>
       <c r="R35" t="n">
-        <v>7001400</v>
+        <v>7001449</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5065,7 +5065,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5075,12 +5075,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På både gran och sälg.</t>
+          <t>Rikligt med bålar på en rakväxt björk.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5094,27 +5094,27 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Betula</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5132,7 +5132,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129128023</v>
+        <v>129135454</v>
       </c>
       <c r="B36" t="n">
         <v>80149</v>
@@ -5172,10 +5172,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>520326</v>
+        <v>520630</v>
       </c>
       <c r="R36" t="n">
-        <v>7001449</v>
+        <v>7001400</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Rikligt med bålar på en rakväxt björk.</t>
+          <t>På både gran och sälg.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5236,27 +5236,27 @@
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Betula</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5274,62 +5274,48 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129128320</v>
+        <v>129135677</v>
       </c>
       <c r="B37" t="n">
-        <v>98716</v>
+        <v>79044</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>520352</v>
+        <v>520346</v>
       </c>
       <c r="R37" t="n">
-        <v>7001397</v>
+        <v>7001536</v>
       </c>
       <c r="S37" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5358,7 +5344,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5368,12 +5354,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:20</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Minst 10 plantor inom ca 0,5 m2 yta.</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5384,11 +5365,6 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -5405,48 +5381,62 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129135677</v>
+        <v>129128320</v>
       </c>
       <c r="B38" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>520346</v>
+        <v>520352</v>
       </c>
       <c r="R38" t="n">
-        <v>7001536</v>
+        <v>7001397</v>
       </c>
       <c r="S38" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5475,7 +5465,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5485,7 +5475,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Minst 10 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5496,6 +5491,11 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -6050,7 +6050,7 @@
         <v>129193576</v>
       </c>
       <c r="B44" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6147,7 +6147,7 @@
         <v>129193582</v>
       </c>
       <c r="B45" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6368,7 +6368,7 @@
         <v>129193583</v>
       </c>
       <c r="B47" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6584,7 +6584,7 @@
         <v>129193591</v>
       </c>
       <c r="B49" t="n">
-        <v>92867</v>
+        <v>92868</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6678,10 +6678,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129193566</v>
+        <v>129193523</v>
       </c>
       <c r="B50" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6689,21 +6689,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6713,10 +6713,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>520180</v>
+        <v>520478</v>
       </c>
       <c r="R50" t="n">
-        <v>7001458</v>
+        <v>7001335</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6749,6 +6749,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6775,10 +6780,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129193590</v>
+        <v>129193517</v>
       </c>
       <c r="B51" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6786,21 +6791,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6810,10 +6815,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>520187</v>
+        <v>520301</v>
       </c>
       <c r="R51" t="n">
-        <v>7001471</v>
+        <v>7001547</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6846,6 +6851,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6872,10 +6882,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129193523</v>
+        <v>129193590</v>
       </c>
       <c r="B52" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6883,21 +6893,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6907,10 +6917,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>520478</v>
+        <v>520187</v>
       </c>
       <c r="R52" t="n">
-        <v>7001335</v>
+        <v>7001471</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6943,11 +6953,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6974,10 +6979,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129193517</v>
+        <v>129193566</v>
       </c>
       <c r="B53" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6985,21 +6990,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -7009,10 +7014,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>520301</v>
+        <v>520180</v>
       </c>
       <c r="R53" t="n">
-        <v>7001547</v>
+        <v>7001458</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7045,11 +7050,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7079,7 +7079,7 @@
         <v>129193581</v>
       </c>
       <c r="B54" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7195,7 +7195,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129193570</v>
+        <v>129193550</v>
       </c>
       <c r="B55" t="n">
         <v>80149</v>
@@ -7230,10 +7230,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>519997</v>
+        <v>520344</v>
       </c>
       <c r="R55" t="n">
-        <v>7001586</v>
+        <v>7001502</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7292,7 +7292,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129193550</v>
+        <v>129193570</v>
       </c>
       <c r="B56" t="n">
         <v>80149</v>
@@ -7327,10 +7327,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>520344</v>
+        <v>519997</v>
       </c>
       <c r="R56" t="n">
-        <v>7001502</v>
+        <v>7001586</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7486,10 +7486,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129193567</v>
+        <v>129193524</v>
       </c>
       <c r="B58" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7497,21 +7497,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7521,10 +7521,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>520184</v>
+        <v>520478</v>
       </c>
       <c r="R58" t="n">
-        <v>7001482</v>
+        <v>7001328</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7557,6 +7557,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7583,7 +7588,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129193524</v>
+        <v>129193544</v>
       </c>
       <c r="B59" t="n">
         <v>57727</v>
@@ -7618,10 +7623,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>520478</v>
+        <v>520270</v>
       </c>
       <c r="R59" t="n">
-        <v>7001328</v>
+        <v>7001484</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7658,7 +7663,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7685,10 +7690,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129193544</v>
+        <v>129193567</v>
       </c>
       <c r="B60" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7696,21 +7701,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7720,10 +7725,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>520270</v>
+        <v>520184</v>
       </c>
       <c r="R60" t="n">
-        <v>7001484</v>
+        <v>7001482</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7756,11 +7761,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7787,45 +7787,57 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129193564</v>
+        <v>129193585</v>
       </c>
       <c r="B61" t="n">
-        <v>80149</v>
+        <v>98724</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>520225</v>
+        <v>520122</v>
       </c>
       <c r="R61" t="n">
-        <v>7001483</v>
+        <v>7001476</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7860,12 +7872,18 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Fler än 200</t>
+        </is>
+      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7884,7 +7902,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129193557</v>
+        <v>129193564</v>
       </c>
       <c r="B62" t="n">
         <v>80149</v>
@@ -7919,10 +7937,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>520374</v>
+        <v>520225</v>
       </c>
       <c r="R62" t="n">
-        <v>7001329</v>
+        <v>7001483</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7981,57 +7999,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129193585</v>
+        <v>129193557</v>
       </c>
       <c r="B63" t="n">
-        <v>98716</v>
+        <v>80149</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>520122</v>
+        <v>520374</v>
       </c>
       <c r="R63" t="n">
-        <v>7001476</v>
+        <v>7001329</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8066,18 +8072,12 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Fler än 200</t>
-        </is>
-      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -8293,7 +8293,7 @@
         <v>129193593</v>
       </c>
       <c r="B66" t="n">
-        <v>100905</v>
+        <v>100913</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8589,7 +8589,7 @@
         <v>129193584</v>
       </c>
       <c r="B69" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8918,7 +8918,7 @@
         <v>129193548</v>
       </c>
       <c r="B72" t="n">
-        <v>92504</v>
+        <v>92505</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9109,10 +9109,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129193549</v>
+        <v>129193546</v>
       </c>
       <c r="B74" t="n">
-        <v>80150</v>
+        <v>57727</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9120,21 +9120,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -9144,10 +9144,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>520345</v>
+        <v>519958</v>
       </c>
       <c r="R74" t="n">
-        <v>7001396</v>
+        <v>7001542</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9180,6 +9180,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9206,10 +9211,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129193546</v>
+        <v>129193549</v>
       </c>
       <c r="B75" t="n">
-        <v>57727</v>
+        <v>80150</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9217,21 +9222,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -9241,10 +9246,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>519958</v>
+        <v>520345</v>
       </c>
       <c r="R75" t="n">
-        <v>7001542</v>
+        <v>7001396</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9277,11 +9282,6 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9311,7 +9311,7 @@
         <v>129193575</v>
       </c>
       <c r="B76" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 43533-2025 artfynd.xlsx
+++ b/artfynd/A 43533-2025 artfynd.xlsx
@@ -675,38 +675,47 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129135852</v>
+        <v>129135545</v>
       </c>
       <c r="B2" t="n">
-        <v>99058</v>
+        <v>98724</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219880</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>gulnande löv/blad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -715,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>520213</v>
+        <v>520564</v>
       </c>
       <c r="R2" t="n">
-        <v>7001609</v>
+        <v>7001441</v>
       </c>
       <c r="S2" t="n">
         <v>9</v>
@@ -750,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,47 +801,38 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129135545</v>
+        <v>129135852</v>
       </c>
       <c r="B3" t="n">
-        <v>98724</v>
+        <v>99058</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>219880</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>gulnande löv/blad</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -841,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>520564</v>
+        <v>520213</v>
       </c>
       <c r="R3" t="n">
-        <v>7001441</v>
+        <v>7001609</v>
       </c>
       <c r="S3" t="n">
         <v>9</v>
@@ -876,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1612,38 +1612,38 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129135867</v>
+        <v>129135692</v>
       </c>
       <c r="B9" t="n">
-        <v>100913</v>
+        <v>80149</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1652,13 +1652,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>520192</v>
+        <v>520343</v>
       </c>
       <c r="R9" t="n">
-        <v>7001635</v>
+        <v>7001533</v>
       </c>
       <c r="S9" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1685,11 +1685,21 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>18:06</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>18:06</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1698,6 +1708,31 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1714,38 +1749,38 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129135692</v>
+        <v>129135867</v>
       </c>
       <c r="B10" t="n">
-        <v>80149</v>
+        <v>100913</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1754,13 +1789,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>520343</v>
+        <v>520192</v>
       </c>
       <c r="R10" t="n">
-        <v>7001533</v>
+        <v>7001635</v>
       </c>
       <c r="S10" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1787,21 +1822,11 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>18:06</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>18:06</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1810,31 +1835,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1851,10 +1851,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129127736</v>
+        <v>129126617</v>
       </c>
       <c r="B11" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1862,27 +1862,27 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1891,13 +1891,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>520237</v>
+        <v>520219</v>
       </c>
       <c r="R11" t="n">
-        <v>7001416</v>
+        <v>7001429</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1936,12 +1936,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:01</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1953,29 +1948,19 @@
       <c r="AG11" t="b">
         <v>0</v>
       </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2115,10 +2100,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129126617</v>
+        <v>129127736</v>
       </c>
       <c r="B13" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2126,27 +2111,27 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2155,13 +2140,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>520219</v>
+        <v>520237</v>
       </c>
       <c r="R13" t="n">
-        <v>7001429</v>
+        <v>7001416</v>
       </c>
       <c r="S13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2190,7 +2175,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2200,7 +2185,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2212,19 +2202,29 @@
       <c r="AG13" t="b">
         <v>0</v>
       </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2505,10 +2505,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129128148</v>
+        <v>129127604</v>
       </c>
       <c r="B16" t="n">
-        <v>80150</v>
+        <v>80149</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2516,27 +2516,27 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2545,13 +2545,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>520338</v>
+        <v>520243</v>
       </c>
       <c r="R16" t="n">
-        <v>7001407</v>
+        <v>7001423</v>
       </c>
       <c r="S16" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2590,7 +2590,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Fertil lunglav på en sälg med doftticka.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2604,27 +2609,27 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Betula</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2642,10 +2647,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129127604</v>
+        <v>129128148</v>
       </c>
       <c r="B17" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2653,27 +2658,27 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2682,13 +2687,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>520243</v>
+        <v>520338</v>
       </c>
       <c r="R17" t="n">
-        <v>7001423</v>
+        <v>7001407</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2717,7 +2722,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2727,12 +2732,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:59</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Fertil lunglav på en sälg med doftticka.</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2746,27 +2746,27 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark of dead wood # Betula</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2921,48 +2921,62 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129131389</v>
+        <v>129127509</v>
       </c>
       <c r="B19" t="n">
-        <v>79044</v>
+        <v>92145</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>520611</v>
+        <v>520242</v>
       </c>
       <c r="R19" t="n">
-        <v>7001285</v>
+        <v>7001434</v>
       </c>
       <c r="S19" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2991,7 +3005,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3001,7 +3015,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3012,6 +3026,31 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Salix caprea</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -3028,62 +3067,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129127509</v>
+        <v>129131389</v>
       </c>
       <c r="B20" t="n">
-        <v>92145</v>
+        <v>79044</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>520242</v>
+        <v>520611</v>
       </c>
       <c r="R20" t="n">
-        <v>7001434</v>
+        <v>7001285</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3112,7 +3137,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3122,7 +3147,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3133,31 +3158,6 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Salix caprea</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -3174,10 +3174,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129125122</v>
+        <v>129126633</v>
       </c>
       <c r="B21" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3185,21 +3185,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3209,13 +3209,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>519973</v>
+        <v>520226</v>
       </c>
       <c r="R21" t="n">
-        <v>7001540</v>
+        <v>7001438</v>
       </c>
       <c r="S21" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3242,11 +3242,26 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På grovbarkad gammal asp.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3255,6 +3270,31 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3271,10 +3311,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129126633</v>
+        <v>129125122</v>
       </c>
       <c r="B22" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3282,21 +3322,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3306,13 +3346,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>520226</v>
+        <v>519973</v>
       </c>
       <c r="R22" t="n">
-        <v>7001438</v>
+        <v>7001540</v>
       </c>
       <c r="S22" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3339,26 +3379,11 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>11:19</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>11:19</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>På grovbarkad gammal asp.</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3367,31 +3392,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3784,10 +3784,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129131479</v>
+        <v>129127211</v>
       </c>
       <c r="B26" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3795,37 +3795,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>520712</v>
+        <v>520158</v>
       </c>
       <c r="R26" t="n">
-        <v>7001363</v>
+        <v>7001448</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3854,7 +3859,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3864,7 +3869,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3878,27 +3883,27 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3916,10 +3921,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129127211</v>
+        <v>129131479</v>
       </c>
       <c r="B27" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3927,42 +3932,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>520158</v>
+        <v>520712</v>
       </c>
       <c r="R27" t="n">
-        <v>7001448</v>
+        <v>7001363</v>
       </c>
       <c r="S27" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3991,7 +3991,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4001,7 +4001,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4015,27 +4015,27 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4053,10 +4053,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129131418</v>
+        <v>129124933</v>
       </c>
       <c r="B28" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4064,37 +4064,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>520682</v>
+        <v>519886</v>
       </c>
       <c r="R28" t="n">
-        <v>7001354</v>
+        <v>7001592</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4123,7 +4128,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4133,7 +4138,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>09:39</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran i hyggeskanten.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4147,7 +4157,7 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
@@ -4162,12 +4172,12 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4185,38 +4195,52 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129124933</v>
+        <v>129127084</v>
       </c>
       <c r="B29" t="n">
-        <v>57727</v>
+        <v>98724</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -4225,13 +4249,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>519886</v>
+        <v>520203</v>
       </c>
       <c r="R29" t="n">
-        <v>7001592</v>
+        <v>7001453</v>
       </c>
       <c r="S29" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4260,7 +4284,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4270,12 +4294,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:39</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran i hyggeskanten.</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4290,26 +4309,6 @@
       <c r="AH29" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4327,67 +4326,48 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129127084</v>
+        <v>129131418</v>
       </c>
       <c r="B30" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>520203</v>
+        <v>520682</v>
       </c>
       <c r="R30" t="n">
-        <v>7001453</v>
+        <v>7001354</v>
       </c>
       <c r="S30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4416,7 +4396,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4426,7 +4406,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4440,7 +4420,27 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -5274,48 +5274,62 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129135677</v>
+        <v>129128320</v>
       </c>
       <c r="B37" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>520346</v>
+        <v>520352</v>
       </c>
       <c r="R37" t="n">
-        <v>7001536</v>
+        <v>7001397</v>
       </c>
       <c r="S37" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5344,7 +5358,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5354,7 +5368,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Minst 10 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5365,6 +5384,11 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -5381,62 +5405,48 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129128320</v>
+        <v>129135677</v>
       </c>
       <c r="B38" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>520352</v>
+        <v>520346</v>
       </c>
       <c r="R38" t="n">
-        <v>7001397</v>
+        <v>7001536</v>
       </c>
       <c r="S38" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5465,7 +5475,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5475,12 +5485,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:20</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Minst 10 plantor inom ca 0,5 m2 yta.</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5491,11 +5496,6 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -5751,10 +5751,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129193518</v>
+        <v>129193558</v>
       </c>
       <c r="B41" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5762,21 +5762,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5786,10 +5786,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>520676</v>
+        <v>520415</v>
       </c>
       <c r="R41" t="n">
-        <v>7001377</v>
+        <v>7001416</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5822,11 +5822,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5853,10 +5848,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129193558</v>
+        <v>129193518</v>
       </c>
       <c r="B42" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5864,21 +5859,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5888,10 +5883,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>520415</v>
+        <v>520676</v>
       </c>
       <c r="R42" t="n">
-        <v>7001416</v>
+        <v>7001377</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5924,6 +5919,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6263,45 +6263,61 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129193542</v>
+        <v>129193583</v>
       </c>
       <c r="B46" t="n">
-        <v>57727</v>
+        <v>98724</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>520422</v>
+        <v>520338</v>
       </c>
       <c r="R46" t="n">
-        <v>7001418</v>
+        <v>7001427</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6338,7 +6354,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Minst 100</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6347,6 +6363,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -6365,61 +6382,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129193583</v>
+        <v>129193542</v>
       </c>
       <c r="B47" t="n">
-        <v>98724</v>
+        <v>57727</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>520338</v>
+        <v>520422</v>
       </c>
       <c r="R47" t="n">
-        <v>7001427</v>
+        <v>7001418</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6456,7 +6457,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Minst 100</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6465,7 +6466,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -6678,10 +6678,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129193523</v>
+        <v>129193590</v>
       </c>
       <c r="B50" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6689,21 +6689,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6713,10 +6713,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>520478</v>
+        <v>520187</v>
       </c>
       <c r="R50" t="n">
-        <v>7001335</v>
+        <v>7001471</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6749,11 +6749,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6780,10 +6775,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129193517</v>
+        <v>129193566</v>
       </c>
       <c r="B51" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6791,21 +6786,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6815,10 +6810,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>520301</v>
+        <v>520180</v>
       </c>
       <c r="R51" t="n">
-        <v>7001547</v>
+        <v>7001458</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6851,11 +6846,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6882,10 +6872,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129193590</v>
+        <v>129193523</v>
       </c>
       <c r="B52" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6893,21 +6883,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6917,10 +6907,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>520187</v>
+        <v>520478</v>
       </c>
       <c r="R52" t="n">
-        <v>7001471</v>
+        <v>7001335</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6953,6 +6943,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6979,10 +6974,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129193566</v>
+        <v>129193517</v>
       </c>
       <c r="B53" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6990,21 +6985,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -7014,10 +7009,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>520180</v>
+        <v>520301</v>
       </c>
       <c r="R53" t="n">
-        <v>7001458</v>
+        <v>7001547</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7050,6 +7045,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7389,10 +7389,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129193561</v>
+        <v>129193524</v>
       </c>
       <c r="B57" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7400,21 +7400,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7424,10 +7424,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>520344</v>
+        <v>520478</v>
       </c>
       <c r="R57" t="n">
-        <v>7001402</v>
+        <v>7001328</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7460,6 +7460,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7486,7 +7491,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129193524</v>
+        <v>129193544</v>
       </c>
       <c r="B58" t="n">
         <v>57727</v>
@@ -7521,10 +7526,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>520478</v>
+        <v>520270</v>
       </c>
       <c r="R58" t="n">
-        <v>7001328</v>
+        <v>7001484</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7561,7 +7566,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7588,10 +7593,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129193544</v>
+        <v>129193561</v>
       </c>
       <c r="B59" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7599,21 +7604,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7623,10 +7628,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>520270</v>
+        <v>520344</v>
       </c>
       <c r="R59" t="n">
-        <v>7001484</v>
+        <v>7001402</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7659,11 +7664,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7787,57 +7787,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129193585</v>
+        <v>129193564</v>
       </c>
       <c r="B61" t="n">
-        <v>98724</v>
+        <v>80149</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>520122</v>
+        <v>520225</v>
       </c>
       <c r="R61" t="n">
-        <v>7001476</v>
+        <v>7001483</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7872,18 +7860,12 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Fler än 200</t>
-        </is>
-      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7902,7 +7884,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129193564</v>
+        <v>129193557</v>
       </c>
       <c r="B62" t="n">
         <v>80149</v>
@@ -7937,10 +7919,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>520225</v>
+        <v>520374</v>
       </c>
       <c r="R62" t="n">
-        <v>7001483</v>
+        <v>7001329</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7999,45 +7981,57 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129193557</v>
+        <v>129193585</v>
       </c>
       <c r="B63" t="n">
-        <v>80149</v>
+        <v>98724</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>520374</v>
+        <v>520122</v>
       </c>
       <c r="R63" t="n">
-        <v>7001329</v>
+        <v>7001476</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8072,12 +8066,18 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Fler än 200</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -8096,32 +8096,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129193560</v>
+        <v>129193593</v>
       </c>
       <c r="B64" t="n">
-        <v>80149</v>
+        <v>100913</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>222498</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -8131,10 +8131,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>520346</v>
+        <v>520101</v>
       </c>
       <c r="R64" t="n">
-        <v>7001396</v>
+        <v>7001658</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8193,7 +8193,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129193569</v>
+        <v>129193560</v>
       </c>
       <c r="B65" t="n">
         <v>80149</v>
@@ -8228,10 +8228,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>520094</v>
+        <v>520346</v>
       </c>
       <c r="R65" t="n">
-        <v>7001525</v>
+        <v>7001396</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8290,32 +8290,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129193593</v>
+        <v>129193569</v>
       </c>
       <c r="B66" t="n">
-        <v>100913</v>
+        <v>80149</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>222498</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -8325,10 +8325,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>520101</v>
+        <v>520094</v>
       </c>
       <c r="R66" t="n">
-        <v>7001658</v>
+        <v>7001525</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8586,46 +8586,46 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129193584</v>
+        <v>129193573</v>
       </c>
       <c r="B69" t="n">
-        <v>98724</v>
+        <v>57831</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>103031</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N69" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -8637,10 +8637,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>520320</v>
+        <v>520153</v>
       </c>
       <c r="R69" t="n">
-        <v>7001451</v>
+        <v>7001500</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8675,18 +8675,12 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Minst 100</t>
-        </is>
-      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -8705,46 +8699,46 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129193573</v>
+        <v>129193584</v>
       </c>
       <c r="B70" t="n">
-        <v>57831</v>
+        <v>98724</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>103031</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N70" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -8756,10 +8750,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>520153</v>
+        <v>520320</v>
       </c>
       <c r="R70" t="n">
-        <v>7001500</v>
+        <v>7001451</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8794,12 +8788,18 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Minst 100</t>
+        </is>
+      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -9109,10 +9109,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129193546</v>
+        <v>129193549</v>
       </c>
       <c r="B74" t="n">
-        <v>57727</v>
+        <v>80150</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9120,21 +9120,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -9144,10 +9144,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>519958</v>
+        <v>520345</v>
       </c>
       <c r="R74" t="n">
-        <v>7001542</v>
+        <v>7001396</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9180,11 +9180,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9211,10 +9206,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129193549</v>
+        <v>129193546</v>
       </c>
       <c r="B75" t="n">
-        <v>80150</v>
+        <v>57727</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9222,21 +9217,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -9246,10 +9241,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>520345</v>
+        <v>519958</v>
       </c>
       <c r="R75" t="n">
-        <v>7001396</v>
+        <v>7001542</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9282,6 +9277,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD75" t="b">

--- a/artfynd/A 43533-2025 artfynd.xlsx
+++ b/artfynd/A 43533-2025 artfynd.xlsx
@@ -675,47 +675,38 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129135545</v>
+        <v>129126527</v>
       </c>
       <c r="B2" t="n">
-        <v>98724</v>
+        <v>80149</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>520564</v>
+        <v>520189</v>
       </c>
       <c r="R2" t="n">
-        <v>7001441</v>
+        <v>7001448</v>
       </c>
       <c r="S2" t="n">
         <v>9</v>
@@ -759,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -783,7 +779,27 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -918,38 +934,47 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129126527</v>
+        <v>129135545</v>
       </c>
       <c r="B4" t="n">
-        <v>80149</v>
+        <v>98724</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -958,10 +983,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>520189</v>
+        <v>520564</v>
       </c>
       <c r="R4" t="n">
-        <v>7001448</v>
+        <v>7001441</v>
       </c>
       <c r="S4" t="n">
         <v>9</v>
@@ -993,7 +1018,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,12 +1028,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:12</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1022,27 +1042,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1978,10 +1978,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129128175</v>
+        <v>129127736</v>
       </c>
       <c r="B12" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1989,37 +1989,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>520329</v>
+        <v>520237</v>
       </c>
       <c r="R12" t="n">
-        <v>7001400</v>
+        <v>7001416</v>
       </c>
       <c r="S12" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2048,7 +2053,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2058,7 +2063,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2070,6 +2080,11 @@
       <c r="AG12" t="b">
         <v>0</v>
       </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AJ12" t="inlineStr">
         <is>
           <t>gran</t>
@@ -2080,9 +2095,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2100,10 +2120,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129127736</v>
+        <v>129128175</v>
       </c>
       <c r="B13" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2111,42 +2131,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>520237</v>
+        <v>520329</v>
       </c>
       <c r="R13" t="n">
-        <v>7001416</v>
+        <v>7001400</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2175,7 +2190,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2185,12 +2200,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:01</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2202,11 +2212,6 @@
       <c r="AG13" t="b">
         <v>0</v>
       </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AJ13" t="inlineStr">
         <is>
           <t>gran</t>
@@ -2217,14 +2222,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2505,7 +2505,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129127604</v>
+        <v>129128162</v>
       </c>
       <c r="B16" t="n">
         <v>80149</v>
@@ -2536,7 +2536,7 @@
       <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2545,13 +2545,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>520243</v>
+        <v>520355</v>
       </c>
       <c r="R16" t="n">
-        <v>7001423</v>
+        <v>7001412</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2590,12 +2590,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:59</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Fertil lunglav på en sälg med doftticka.</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2609,7 +2604,7 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -2784,7 +2779,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129128162</v>
+        <v>129127604</v>
       </c>
       <c r="B18" t="n">
         <v>80149</v>
@@ -2815,7 +2810,7 @@
       <c r="I18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2824,13 +2819,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>520355</v>
+        <v>520243</v>
       </c>
       <c r="R18" t="n">
-        <v>7001412</v>
+        <v>7001423</v>
       </c>
       <c r="S18" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2859,7 +2854,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2869,7 +2864,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Fertil lunglav på en sälg med doftticka.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2883,7 +2883,7 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -4053,10 +4053,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129124933</v>
+        <v>129131418</v>
       </c>
       <c r="B28" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4064,42 +4064,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>519886</v>
+        <v>520682</v>
       </c>
       <c r="R28" t="n">
-        <v>7001592</v>
+        <v>7001354</v>
       </c>
       <c r="S28" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4128,7 +4123,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4138,12 +4133,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:39</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran i hyggeskanten.</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4157,7 +4147,7 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
@@ -4172,12 +4162,12 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4326,10 +4316,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129131418</v>
+        <v>129124933</v>
       </c>
       <c r="B30" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4337,37 +4327,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>520682</v>
+        <v>519886</v>
       </c>
       <c r="R30" t="n">
-        <v>7001354</v>
+        <v>7001592</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4396,7 +4391,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4406,7 +4401,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>09:39</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran i hyggeskanten.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4420,7 +4420,7 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
@@ -4435,12 +4435,12 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4722,48 +4722,62 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129128345</v>
+        <v>129135770</v>
       </c>
       <c r="B33" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>520362</v>
+        <v>520226</v>
       </c>
       <c r="R33" t="n">
-        <v>7001381</v>
+        <v>7001601</v>
       </c>
       <c r="S33" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4792,7 +4806,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4802,12 +4816,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Minst 120 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4821,27 +4835,7 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4859,62 +4853,48 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129135770</v>
+        <v>129128345</v>
       </c>
       <c r="B34" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>520226</v>
+        <v>520362</v>
       </c>
       <c r="R34" t="n">
-        <v>7001601</v>
+        <v>7001381</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4943,7 +4923,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4953,12 +4933,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Minst 120 plantor inom ca 1 m2 yta.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4972,7 +4952,27 @@
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -6263,61 +6263,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129193583</v>
+        <v>129193542</v>
       </c>
       <c r="B46" t="n">
-        <v>98724</v>
+        <v>57727</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>520338</v>
+        <v>520422</v>
       </c>
       <c r="R46" t="n">
-        <v>7001427</v>
+        <v>7001418</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6354,7 +6338,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Minst 100</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6363,7 +6347,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -6382,45 +6365,61 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129193542</v>
+        <v>129193583</v>
       </c>
       <c r="B47" t="n">
-        <v>57727</v>
+        <v>98724</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>520422</v>
+        <v>520338</v>
       </c>
       <c r="R47" t="n">
-        <v>7001418</v>
+        <v>7001427</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6457,7 +6456,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Minst 100</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6466,6 +6465,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -7389,10 +7389,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129193524</v>
+        <v>129193561</v>
       </c>
       <c r="B57" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7400,21 +7400,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7424,10 +7424,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>520478</v>
+        <v>520344</v>
       </c>
       <c r="R57" t="n">
-        <v>7001328</v>
+        <v>7001402</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7460,11 +7460,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7491,10 +7486,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129193544</v>
+        <v>129193567</v>
       </c>
       <c r="B58" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7502,21 +7497,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7526,10 +7521,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>520270</v>
+        <v>520184</v>
       </c>
       <c r="R58" t="n">
-        <v>7001484</v>
+        <v>7001482</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7562,11 +7557,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7593,10 +7583,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129193561</v>
+        <v>129193524</v>
       </c>
       <c r="B59" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7604,21 +7594,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7628,10 +7618,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>520344</v>
+        <v>520478</v>
       </c>
       <c r="R59" t="n">
-        <v>7001402</v>
+        <v>7001328</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7664,6 +7654,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7690,10 +7685,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129193567</v>
+        <v>129193544</v>
       </c>
       <c r="B60" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7701,21 +7696,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7725,10 +7720,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>520184</v>
+        <v>520270</v>
       </c>
       <c r="R60" t="n">
-        <v>7001482</v>
+        <v>7001484</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7761,6 +7756,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8096,32 +8096,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129193593</v>
+        <v>129193560</v>
       </c>
       <c r="B64" t="n">
-        <v>100913</v>
+        <v>80149</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>222498</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -8131,10 +8131,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>520101</v>
+        <v>520346</v>
       </c>
       <c r="R64" t="n">
-        <v>7001658</v>
+        <v>7001396</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8193,7 +8193,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129193560</v>
+        <v>129193569</v>
       </c>
       <c r="B65" t="n">
         <v>80149</v>
@@ -8228,10 +8228,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>520346</v>
+        <v>520094</v>
       </c>
       <c r="R65" t="n">
-        <v>7001396</v>
+        <v>7001525</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8290,32 +8290,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129193569</v>
+        <v>129193593</v>
       </c>
       <c r="B66" t="n">
-        <v>80149</v>
+        <v>100913</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>222498</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -8325,10 +8325,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>520094</v>
+        <v>520101</v>
       </c>
       <c r="R66" t="n">
-        <v>7001525</v>
+        <v>7001658</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8387,10 +8387,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129193562</v>
+        <v>129193545</v>
       </c>
       <c r="B67" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8398,21 +8398,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8422,10 +8422,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>520335</v>
+        <v>519958</v>
       </c>
       <c r="R67" t="n">
-        <v>7001429</v>
+        <v>7001547</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8458,6 +8458,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8484,10 +8489,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129193545</v>
+        <v>129193562</v>
       </c>
       <c r="B68" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8495,21 +8500,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8519,10 +8524,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>519958</v>
+        <v>520335</v>
       </c>
       <c r="R68" t="n">
-        <v>7001547</v>
+        <v>7001429</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8555,11 +8560,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD68" t="b">

--- a/artfynd/A 43533-2025 artfynd.xlsx
+++ b/artfynd/A 43533-2025 artfynd.xlsx
@@ -820,7 +820,7 @@
         <v>129135852</v>
       </c>
       <c r="B3" t="n">
-        <v>99058</v>
+        <v>99061</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>129135545</v>
       </c>
       <c r="B4" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>129126843</v>
       </c>
       <c r="B8" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1612,38 +1612,38 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129135692</v>
+        <v>129135867</v>
       </c>
       <c r="B9" t="n">
-        <v>80149</v>
+        <v>100916</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1652,13 +1652,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>520343</v>
+        <v>520192</v>
       </c>
       <c r="R9" t="n">
-        <v>7001533</v>
+        <v>7001635</v>
       </c>
       <c r="S9" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1685,21 +1685,11 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>18:06</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>18:06</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1708,31 +1698,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1749,38 +1714,38 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129135867</v>
+        <v>129135692</v>
       </c>
       <c r="B10" t="n">
-        <v>100913</v>
+        <v>80149</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1789,13 +1754,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>520192</v>
+        <v>520343</v>
       </c>
       <c r="R10" t="n">
-        <v>7001635</v>
+        <v>7001533</v>
       </c>
       <c r="S10" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1822,11 +1787,21 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>18:06</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>18:06</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1835,6 +1810,31 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1851,10 +1851,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129126617</v>
+        <v>129128175</v>
       </c>
       <c r="B11" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1862,42 +1862,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>520219</v>
+        <v>520329</v>
       </c>
       <c r="R11" t="n">
-        <v>7001429</v>
+        <v>7001400</v>
       </c>
       <c r="S11" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1926,7 +1921,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1936,7 +1931,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1950,17 +1945,17 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1978,10 +1973,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129127736</v>
+        <v>129126617</v>
       </c>
       <c r="B12" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1989,27 +1984,27 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -2018,13 +2013,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>520237</v>
+        <v>520219</v>
       </c>
       <c r="R12" t="n">
-        <v>7001416</v>
+        <v>7001429</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2053,7 +2048,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2063,12 +2058,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:01</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2080,29 +2070,19 @@
       <c r="AG12" t="b">
         <v>0</v>
       </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2120,10 +2100,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129128175</v>
+        <v>129127736</v>
       </c>
       <c r="B13" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2131,37 +2111,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>520329</v>
+        <v>520237</v>
       </c>
       <c r="R13" t="n">
-        <v>7001400</v>
+        <v>7001416</v>
       </c>
       <c r="S13" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2190,7 +2175,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2200,7 +2185,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2212,6 +2202,11 @@
       <c r="AG13" t="b">
         <v>0</v>
       </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AJ13" t="inlineStr">
         <is>
           <t>gran</t>
@@ -2222,9 +2217,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2382,7 +2382,7 @@
         <v>129135822</v>
       </c>
       <c r="B15" t="n">
-        <v>104195</v>
+        <v>104198</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2505,10 +2505,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129128162</v>
+        <v>129128148</v>
       </c>
       <c r="B16" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2516,21 +2516,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2545,13 +2545,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>520355</v>
+        <v>520338</v>
       </c>
       <c r="R16" t="n">
-        <v>7001412</v>
+        <v>7001407</v>
       </c>
       <c r="S16" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2609,22 +2609,22 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark of dead wood # Betula</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2642,10 +2642,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129128148</v>
+        <v>129127604</v>
       </c>
       <c r="B17" t="n">
-        <v>80150</v>
+        <v>80149</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2653,27 +2653,27 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>520338</v>
+        <v>520243</v>
       </c>
       <c r="R17" t="n">
-        <v>7001407</v>
+        <v>7001423</v>
       </c>
       <c r="S17" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2727,7 +2727,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Fertil lunglav på en sälg med doftticka.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2741,27 +2746,27 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Betula</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2779,7 +2784,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129127604</v>
+        <v>129128162</v>
       </c>
       <c r="B18" t="n">
         <v>80149</v>
@@ -2810,7 +2815,7 @@
       <c r="I18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2819,13 +2824,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>520243</v>
+        <v>520355</v>
       </c>
       <c r="R18" t="n">
-        <v>7001423</v>
+        <v>7001412</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2854,7 +2859,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2864,12 +2869,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:59</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Fertil lunglav på en sälg med doftticka.</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2883,7 +2883,7 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -2924,7 +2924,7 @@
         <v>129127509</v>
       </c>
       <c r="B19" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3174,10 +3174,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129126633</v>
+        <v>129125122</v>
       </c>
       <c r="B21" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3185,21 +3185,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3209,13 +3209,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>520226</v>
+        <v>519973</v>
       </c>
       <c r="R21" t="n">
-        <v>7001438</v>
+        <v>7001540</v>
       </c>
       <c r="S21" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3242,26 +3242,11 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>11:19</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>11:19</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På grovbarkad gammal asp.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3270,31 +3255,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3311,10 +3271,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129125122</v>
+        <v>129126633</v>
       </c>
       <c r="B22" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3322,21 +3282,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3346,13 +3306,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>519973</v>
+        <v>520226</v>
       </c>
       <c r="R22" t="n">
-        <v>7001540</v>
+        <v>7001438</v>
       </c>
       <c r="S22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3379,11 +3339,26 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På grovbarkad gammal asp.</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3392,6 +3367,31 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3408,10 +3408,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129136001</v>
+        <v>129128128</v>
       </c>
       <c r="B23" t="n">
-        <v>79044</v>
+        <v>80150</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3419,37 +3419,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>520012</v>
+        <v>520340</v>
       </c>
       <c r="R23" t="n">
-        <v>7001652</v>
+        <v>7001392</v>
       </c>
       <c r="S23" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3478,7 +3483,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3488,7 +3493,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3499,6 +3504,31 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3515,7 +3545,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129126703</v>
+        <v>129136001</v>
       </c>
       <c r="B24" t="n">
         <v>79044</v>
@@ -3550,13 +3580,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>520253</v>
+        <v>520012</v>
       </c>
       <c r="R24" t="n">
-        <v>7001454</v>
+        <v>7001652</v>
       </c>
       <c r="S24" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3585,7 +3615,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3595,7 +3625,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3606,31 +3636,6 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3647,10 +3652,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129128128</v>
+        <v>129126703</v>
       </c>
       <c r="B25" t="n">
-        <v>80150</v>
+        <v>79044</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3658,39 +3663,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>520340</v>
+        <v>520253</v>
       </c>
       <c r="R25" t="n">
-        <v>7001392</v>
+        <v>7001454</v>
       </c>
       <c r="S25" t="n">
         <v>9</v>
@@ -3722,7 +3722,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3732,7 +3732,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3746,27 +3746,27 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3784,10 +3784,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129127211</v>
+        <v>129131479</v>
       </c>
       <c r="B26" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3795,42 +3795,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>520158</v>
+        <v>520712</v>
       </c>
       <c r="R26" t="n">
-        <v>7001448</v>
+        <v>7001363</v>
       </c>
       <c r="S26" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3859,7 +3854,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3869,7 +3864,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3883,27 +3878,27 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3921,10 +3916,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129131479</v>
+        <v>129127211</v>
       </c>
       <c r="B27" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3932,37 +3927,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>520712</v>
+        <v>520158</v>
       </c>
       <c r="R27" t="n">
-        <v>7001363</v>
+        <v>7001448</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3991,7 +3991,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4001,7 +4001,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4015,27 +4015,27 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4188,7 +4188,7 @@
         <v>129127084</v>
       </c>
       <c r="B29" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4725,7 +4725,7 @@
         <v>129135770</v>
       </c>
       <c r="B33" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -5274,62 +5274,48 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129128320</v>
+        <v>129135677</v>
       </c>
       <c r="B37" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>520352</v>
+        <v>520346</v>
       </c>
       <c r="R37" t="n">
-        <v>7001397</v>
+        <v>7001536</v>
       </c>
       <c r="S37" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5358,7 +5344,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5368,12 +5354,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:20</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Minst 10 plantor inom ca 0,5 m2 yta.</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5384,11 +5365,6 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -5405,48 +5381,62 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129135677</v>
+        <v>129128320</v>
       </c>
       <c r="B38" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>520346</v>
+        <v>520352</v>
       </c>
       <c r="R38" t="n">
-        <v>7001536</v>
+        <v>7001397</v>
       </c>
       <c r="S38" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5475,7 +5465,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5485,7 +5475,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Minst 10 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5496,6 +5491,11 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -6050,7 +6050,7 @@
         <v>129193576</v>
       </c>
       <c r="B44" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6147,7 +6147,7 @@
         <v>129193582</v>
       </c>
       <c r="B45" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6368,7 +6368,7 @@
         <v>129193583</v>
       </c>
       <c r="B47" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6584,7 +6584,7 @@
         <v>129193591</v>
       </c>
       <c r="B49" t="n">
-        <v>92868</v>
+        <v>92871</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6872,7 +6872,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129193523</v>
+        <v>129193517</v>
       </c>
       <c r="B52" t="n">
         <v>57727</v>
@@ -6907,10 +6907,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>520478</v>
+        <v>520301</v>
       </c>
       <c r="R52" t="n">
-        <v>7001335</v>
+        <v>7001547</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6947,7 +6947,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6974,7 +6974,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129193517</v>
+        <v>129193523</v>
       </c>
       <c r="B53" t="n">
         <v>57727</v>
@@ -7009,10 +7009,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>520301</v>
+        <v>520478</v>
       </c>
       <c r="R53" t="n">
-        <v>7001547</v>
+        <v>7001335</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7079,7 +7079,7 @@
         <v>129193581</v>
       </c>
       <c r="B54" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7195,7 +7195,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129193550</v>
+        <v>129193570</v>
       </c>
       <c r="B55" t="n">
         <v>80149</v>
@@ -7230,10 +7230,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>520344</v>
+        <v>519997</v>
       </c>
       <c r="R55" t="n">
-        <v>7001502</v>
+        <v>7001586</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7292,7 +7292,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129193570</v>
+        <v>129193550</v>
       </c>
       <c r="B56" t="n">
         <v>80149</v>
@@ -7327,10 +7327,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>519997</v>
+        <v>520344</v>
       </c>
       <c r="R56" t="n">
-        <v>7001586</v>
+        <v>7001502</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7389,10 +7389,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129193561</v>
+        <v>129193524</v>
       </c>
       <c r="B57" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7400,21 +7400,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7424,10 +7424,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>520344</v>
+        <v>520478</v>
       </c>
       <c r="R57" t="n">
-        <v>7001402</v>
+        <v>7001328</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7460,6 +7460,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7486,10 +7491,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129193567</v>
+        <v>129193544</v>
       </c>
       <c r="B58" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7497,21 +7502,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7521,10 +7526,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>520184</v>
+        <v>520270</v>
       </c>
       <c r="R58" t="n">
-        <v>7001482</v>
+        <v>7001484</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7557,6 +7562,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7583,10 +7593,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129193524</v>
+        <v>129193561</v>
       </c>
       <c r="B59" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7594,21 +7604,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7618,10 +7628,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>520478</v>
+        <v>520344</v>
       </c>
       <c r="R59" t="n">
-        <v>7001328</v>
+        <v>7001402</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7654,11 +7664,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7685,10 +7690,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129193544</v>
+        <v>129193567</v>
       </c>
       <c r="B60" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7696,21 +7701,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7720,10 +7725,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>520270</v>
+        <v>520184</v>
       </c>
       <c r="R60" t="n">
-        <v>7001484</v>
+        <v>7001482</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7756,11 +7761,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7984,7 +7984,7 @@
         <v>129193585</v>
       </c>
       <c r="B63" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8293,7 +8293,7 @@
         <v>129193593</v>
       </c>
       <c r="B66" t="n">
-        <v>100913</v>
+        <v>100916</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8387,10 +8387,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129193545</v>
+        <v>129193562</v>
       </c>
       <c r="B67" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8398,21 +8398,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8422,10 +8422,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>519958</v>
+        <v>520335</v>
       </c>
       <c r="R67" t="n">
-        <v>7001547</v>
+        <v>7001429</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8458,11 +8458,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8489,10 +8484,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129193562</v>
+        <v>129193545</v>
       </c>
       <c r="B68" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8500,21 +8495,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8524,10 +8519,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>520335</v>
+        <v>519958</v>
       </c>
       <c r="R68" t="n">
-        <v>7001429</v>
+        <v>7001547</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8560,6 +8555,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8702,7 +8702,7 @@
         <v>129193584</v>
       </c>
       <c r="B70" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8918,7 +8918,7 @@
         <v>129193548</v>
       </c>
       <c r="B72" t="n">
-        <v>92505</v>
+        <v>92508</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9109,45 +9109,61 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129193549</v>
+        <v>129193575</v>
       </c>
       <c r="B74" t="n">
-        <v>80150</v>
+        <v>98727</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>520345</v>
+        <v>520528</v>
       </c>
       <c r="R74" t="n">
-        <v>7001396</v>
+        <v>7001465</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9182,12 +9198,18 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Minst 50</t>
+        </is>
+      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -9308,61 +9330,45 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129193575</v>
+        <v>129193549</v>
       </c>
       <c r="B76" t="n">
-        <v>98724</v>
+        <v>80150</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="N76" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>520528</v>
+        <v>520345</v>
       </c>
       <c r="R76" t="n">
-        <v>7001465</v>
+        <v>7001396</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9397,18 +9403,12 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Minst 50</t>
-        </is>
-      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 43533-2025 artfynd.xlsx
+++ b/artfynd/A 43533-2025 artfynd.xlsx
@@ -1182,38 +1182,47 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129127182</v>
+        <v>129126843</v>
       </c>
       <c r="B6" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1227,13 +1236,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>520186</v>
+        <v>520211</v>
       </c>
       <c r="R6" t="n">
-        <v>7001459</v>
+        <v>7001475</v>
       </c>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1262,7 +1271,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1272,12 +1281,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran  intill en gammal sälg.</t>
+          <t>Minst 100 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1292,26 +1301,6 @@
       <c r="AH6" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1329,7 +1318,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129131350</v>
+        <v>129127182</v>
       </c>
       <c r="B7" t="n">
         <v>57727</v>
@@ -1360,7 +1349,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1374,10 +1363,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>520520</v>
+        <v>520186</v>
       </c>
       <c r="R7" t="n">
-        <v>7001311</v>
+        <v>7001459</v>
       </c>
       <c r="S7" t="n">
         <v>8</v>
@@ -1409,7 +1398,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1419,12 +1408,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack, enstaka färska och rikligt med äldre på en tall.</t>
+          <t>Ringhack, äldre, på stambasen av en gran  intill en gammal sälg.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1438,17 +1427,17 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -1458,7 +1447,7 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1476,47 +1465,38 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129126843</v>
+        <v>129131350</v>
       </c>
       <c r="B8" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1530,13 +1510,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>520211</v>
+        <v>520520</v>
       </c>
       <c r="R8" t="n">
-        <v>7001475</v>
+        <v>7001311</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1565,7 +1545,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1575,12 +1555,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Minst 100 plantor inom ca 0,5 m2 yta.</t>
+          <t>Ringhack, enstaka färska och rikligt med äldre på en tall.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1594,7 +1574,27 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -3545,7 +3545,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129136001</v>
+        <v>129126703</v>
       </c>
       <c r="B24" t="n">
         <v>79044</v>
@@ -3580,13 +3580,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>520012</v>
+        <v>520253</v>
       </c>
       <c r="R24" t="n">
-        <v>7001652</v>
+        <v>7001454</v>
       </c>
       <c r="S24" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3625,7 +3625,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3636,6 +3636,31 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3652,7 +3677,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129126703</v>
+        <v>129136001</v>
       </c>
       <c r="B25" t="n">
         <v>79044</v>
@@ -3687,13 +3712,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>520253</v>
+        <v>520012</v>
       </c>
       <c r="R25" t="n">
-        <v>7001454</v>
+        <v>7001652</v>
       </c>
       <c r="S25" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3722,7 +3747,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3732,7 +3757,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3743,31 +3768,6 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -4053,10 +4053,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129131418</v>
+        <v>129124933</v>
       </c>
       <c r="B28" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4064,37 +4064,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>520682</v>
+        <v>519886</v>
       </c>
       <c r="R28" t="n">
-        <v>7001354</v>
+        <v>7001592</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4123,7 +4128,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4133,7 +4138,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>09:39</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran i hyggeskanten.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4147,7 +4157,7 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
@@ -4162,12 +4172,12 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4185,67 +4195,48 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129127084</v>
+        <v>129131418</v>
       </c>
       <c r="B29" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>520203</v>
+        <v>520682</v>
       </c>
       <c r="R29" t="n">
-        <v>7001453</v>
+        <v>7001354</v>
       </c>
       <c r="S29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4274,7 +4265,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4284,7 +4275,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4298,7 +4289,27 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4316,38 +4327,52 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129124933</v>
+        <v>129127084</v>
       </c>
       <c r="B30" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4356,13 +4381,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>519886</v>
+        <v>520203</v>
       </c>
       <c r="R30" t="n">
-        <v>7001592</v>
+        <v>7001453</v>
       </c>
       <c r="S30" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4391,7 +4416,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4401,12 +4426,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:39</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran i hyggeskanten.</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4421,26 +4441,6 @@
       <c r="AH30" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4722,62 +4722,48 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129135770</v>
+        <v>129128345</v>
       </c>
       <c r="B33" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>520226</v>
+        <v>520362</v>
       </c>
       <c r="R33" t="n">
-        <v>7001601</v>
+        <v>7001381</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4806,7 +4792,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4816,12 +4802,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Minst 120 plantor inom ca 1 m2 yta.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4835,7 +4821,27 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4853,48 +4859,62 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129128345</v>
+        <v>129135770</v>
       </c>
       <c r="B34" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>520362</v>
+        <v>520226</v>
       </c>
       <c r="R34" t="n">
-        <v>7001381</v>
+        <v>7001601</v>
       </c>
       <c r="S34" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4923,7 +4943,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4933,12 +4953,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Minst 120 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4952,27 +4972,7 @@
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5950,32 +5950,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129193568</v>
+        <v>129193576</v>
       </c>
       <c r="B43" t="n">
-        <v>80149</v>
+        <v>98727</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5985,10 +5985,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>520159</v>
+        <v>520675</v>
       </c>
       <c r="R43" t="n">
-        <v>7001489</v>
+        <v>7001377</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6047,7 +6047,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129193576</v>
+        <v>129193582</v>
       </c>
       <c r="B44" t="n">
         <v>98727</v>
@@ -6075,17 +6075,33 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>520675</v>
+        <v>520388</v>
       </c>
       <c r="R44" t="n">
-        <v>7001377</v>
+        <v>7001418</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6120,12 +6136,18 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Minst 50</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -6144,61 +6166,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129193582</v>
+        <v>129193568</v>
       </c>
       <c r="B45" t="n">
-        <v>98727</v>
+        <v>80149</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>520388</v>
+        <v>520159</v>
       </c>
       <c r="R45" t="n">
-        <v>7001418</v>
+        <v>7001489</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6233,18 +6239,12 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Minst 50</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -6263,45 +6263,61 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129193542</v>
+        <v>129193583</v>
       </c>
       <c r="B46" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>520422</v>
+        <v>520338</v>
       </c>
       <c r="R46" t="n">
-        <v>7001418</v>
+        <v>7001427</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6338,7 +6354,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Minst 100</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6347,6 +6363,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -6365,61 +6382,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129193583</v>
+        <v>129193542</v>
       </c>
       <c r="B47" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>520338</v>
+        <v>520422</v>
       </c>
       <c r="R47" t="n">
-        <v>7001427</v>
+        <v>7001418</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6456,7 +6457,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Minst 100</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6465,7 +6466,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -6678,10 +6678,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129193590</v>
+        <v>129193523</v>
       </c>
       <c r="B50" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6689,21 +6689,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6713,10 +6713,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>520187</v>
+        <v>520478</v>
       </c>
       <c r="R50" t="n">
-        <v>7001471</v>
+        <v>7001335</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6749,6 +6749,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6775,10 +6780,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129193566</v>
+        <v>129193517</v>
       </c>
       <c r="B51" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6786,21 +6791,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6810,10 +6815,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>520180</v>
+        <v>520301</v>
       </c>
       <c r="R51" t="n">
-        <v>7001458</v>
+        <v>7001547</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6846,6 +6851,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6872,10 +6882,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129193517</v>
+        <v>129193590</v>
       </c>
       <c r="B52" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6883,21 +6893,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6907,10 +6917,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>520301</v>
+        <v>520187</v>
       </c>
       <c r="R52" t="n">
-        <v>7001547</v>
+        <v>7001471</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6943,11 +6953,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6974,10 +6979,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129193523</v>
+        <v>129193566</v>
       </c>
       <c r="B53" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6985,21 +6990,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -7009,10 +7014,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>520478</v>
+        <v>520180</v>
       </c>
       <c r="R53" t="n">
-        <v>7001335</v>
+        <v>7001458</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7045,11 +7050,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7787,45 +7787,57 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129193564</v>
+        <v>129193585</v>
       </c>
       <c r="B61" t="n">
-        <v>80149</v>
+        <v>98727</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>520225</v>
+        <v>520122</v>
       </c>
       <c r="R61" t="n">
-        <v>7001483</v>
+        <v>7001476</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7860,12 +7872,18 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Fler än 200</t>
+        </is>
+      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7884,7 +7902,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129193557</v>
+        <v>129193564</v>
       </c>
       <c r="B62" t="n">
         <v>80149</v>
@@ -7919,10 +7937,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>520374</v>
+        <v>520225</v>
       </c>
       <c r="R62" t="n">
-        <v>7001329</v>
+        <v>7001483</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7981,57 +7999,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129193585</v>
+        <v>129193557</v>
       </c>
       <c r="B63" t="n">
-        <v>98727</v>
+        <v>80149</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>520122</v>
+        <v>520374</v>
       </c>
       <c r="R63" t="n">
-        <v>7001476</v>
+        <v>7001329</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8066,18 +8072,12 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Fler än 200</t>
-        </is>
-      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -9109,61 +9109,45 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129193575</v>
+        <v>129193549</v>
       </c>
       <c r="B74" t="n">
-        <v>98727</v>
+        <v>80150</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="N74" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>520528</v>
+        <v>520345</v>
       </c>
       <c r="R74" t="n">
-        <v>7001465</v>
+        <v>7001396</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9198,18 +9182,12 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Minst 50</t>
-        </is>
-      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -9228,45 +9206,61 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129193546</v>
+        <v>129193575</v>
       </c>
       <c r="B75" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>519958</v>
+        <v>520528</v>
       </c>
       <c r="R75" t="n">
-        <v>7001542</v>
+        <v>7001465</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9303,7 +9297,7 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Minst 50</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9312,6 +9306,7 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -9330,10 +9325,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129193549</v>
+        <v>129193546</v>
       </c>
       <c r="B76" t="n">
-        <v>80150</v>
+        <v>57727</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9341,21 +9336,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9365,10 +9360,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>520345</v>
+        <v>519958</v>
       </c>
       <c r="R76" t="n">
-        <v>7001396</v>
+        <v>7001542</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9401,6 +9396,11 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD76" t="b">

--- a/artfynd/A 43533-2025 artfynd.xlsx
+++ b/artfynd/A 43533-2025 artfynd.xlsx
@@ -817,38 +817,47 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129135852</v>
+        <v>129135545</v>
       </c>
       <c r="B3" t="n">
-        <v>99061</v>
+        <v>98727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219880</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>gulnande löv/blad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -857,10 +866,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>520213</v>
+        <v>520564</v>
       </c>
       <c r="R3" t="n">
-        <v>7001609</v>
+        <v>7001441</v>
       </c>
       <c r="S3" t="n">
         <v>9</v>
@@ -892,7 +901,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -902,7 +911,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -934,47 +943,38 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129135545</v>
+        <v>129135852</v>
       </c>
       <c r="B4" t="n">
-        <v>98727</v>
+        <v>99061</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>219880</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>gulnande löv/blad</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -983,10 +983,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>520564</v>
+        <v>520213</v>
       </c>
       <c r="R4" t="n">
-        <v>7001441</v>
+        <v>7001609</v>
       </c>
       <c r="S4" t="n">
         <v>9</v>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1182,47 +1182,38 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129126843</v>
+        <v>129127182</v>
       </c>
       <c r="B6" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1236,13 +1227,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>520211</v>
+        <v>520186</v>
       </c>
       <c r="R6" t="n">
-        <v>7001475</v>
+        <v>7001459</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1271,7 +1262,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1281,12 +1272,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Minst 100 plantor inom ca 0,5 m2 yta.</t>
+          <t>Ringhack, äldre, på stambasen av en gran  intill en gammal sälg.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1301,6 +1292,26 @@
       <c r="AH6" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1318,7 +1329,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129127182</v>
+        <v>129131350</v>
       </c>
       <c r="B7" t="n">
         <v>57727</v>
@@ -1349,7 +1360,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1363,10 +1374,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>520186</v>
+        <v>520520</v>
       </c>
       <c r="R7" t="n">
-        <v>7001459</v>
+        <v>7001311</v>
       </c>
       <c r="S7" t="n">
         <v>8</v>
@@ -1398,7 +1409,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1408,12 +1419,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran  intill en gammal sälg.</t>
+          <t>Ringhack, enstaka färska och rikligt med äldre på en tall.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1427,17 +1438,17 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -1447,7 +1458,7 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Stem on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1465,38 +1476,47 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129131350</v>
+        <v>129126843</v>
       </c>
       <c r="B8" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1510,13 +1530,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>520520</v>
+        <v>520211</v>
       </c>
       <c r="R8" t="n">
-        <v>7001311</v>
+        <v>7001475</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1545,7 +1565,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1555,12 +1575,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack, enstaka färska och rikligt med äldre på en tall.</t>
+          <t>Minst 100 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1574,27 +1594,7 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1612,38 +1612,38 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129135867</v>
+        <v>129135692</v>
       </c>
       <c r="B9" t="n">
-        <v>100916</v>
+        <v>80149</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1652,13 +1652,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>520192</v>
+        <v>520343</v>
       </c>
       <c r="R9" t="n">
-        <v>7001635</v>
+        <v>7001533</v>
       </c>
       <c r="S9" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1685,11 +1685,21 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>18:06</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>18:06</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1698,6 +1708,31 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1714,38 +1749,38 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129135692</v>
+        <v>129135867</v>
       </c>
       <c r="B10" t="n">
-        <v>80149</v>
+        <v>100916</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1754,13 +1789,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>520343</v>
+        <v>520192</v>
       </c>
       <c r="R10" t="n">
-        <v>7001533</v>
+        <v>7001635</v>
       </c>
       <c r="S10" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1787,21 +1822,11 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>18:06</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>18:06</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1810,31 +1835,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -2505,10 +2505,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129128148</v>
+        <v>129127604</v>
       </c>
       <c r="B16" t="n">
-        <v>80150</v>
+        <v>80149</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2516,27 +2516,27 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2545,13 +2545,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>520338</v>
+        <v>520243</v>
       </c>
       <c r="R16" t="n">
-        <v>7001407</v>
+        <v>7001423</v>
       </c>
       <c r="S16" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2590,7 +2590,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Fertil lunglav på en sälg med doftticka.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2604,27 +2609,27 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Betula</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2642,7 +2647,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129127604</v>
+        <v>129128162</v>
       </c>
       <c r="B17" t="n">
         <v>80149</v>
@@ -2673,7 +2678,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2682,13 +2687,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>520243</v>
+        <v>520355</v>
       </c>
       <c r="R17" t="n">
-        <v>7001423</v>
+        <v>7001412</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2717,7 +2722,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2727,12 +2732,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:59</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Fertil lunglav på en sälg med doftticka.</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -2784,10 +2784,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129128162</v>
+        <v>129128148</v>
       </c>
       <c r="B18" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2795,21 +2795,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2824,13 +2824,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>520355</v>
+        <v>520338</v>
       </c>
       <c r="R18" t="n">
-        <v>7001412</v>
+        <v>7001407</v>
       </c>
       <c r="S18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2888,22 +2888,22 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark of dead wood # Betula</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -3545,7 +3545,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129126703</v>
+        <v>129136001</v>
       </c>
       <c r="B24" t="n">
         <v>79044</v>
@@ -3580,13 +3580,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>520253</v>
+        <v>520012</v>
       </c>
       <c r="R24" t="n">
-        <v>7001454</v>
+        <v>7001652</v>
       </c>
       <c r="S24" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3625,7 +3625,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3636,31 +3636,6 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3677,7 +3652,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129136001</v>
+        <v>129126703</v>
       </c>
       <c r="B25" t="n">
         <v>79044</v>
@@ -3712,13 +3687,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>520012</v>
+        <v>520253</v>
       </c>
       <c r="R25" t="n">
-        <v>7001652</v>
+        <v>7001454</v>
       </c>
       <c r="S25" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3747,7 +3722,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3757,7 +3732,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3768,6 +3743,31 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3784,10 +3784,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129131479</v>
+        <v>129127211</v>
       </c>
       <c r="B26" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3795,37 +3795,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>520712</v>
+        <v>520158</v>
       </c>
       <c r="R26" t="n">
-        <v>7001363</v>
+        <v>7001448</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3854,7 +3859,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3864,7 +3869,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3878,27 +3883,27 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3916,10 +3921,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129127211</v>
+        <v>129131479</v>
       </c>
       <c r="B27" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3927,42 +3932,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>520158</v>
+        <v>520712</v>
       </c>
       <c r="R27" t="n">
-        <v>7001448</v>
+        <v>7001363</v>
       </c>
       <c r="S27" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3991,7 +3991,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4001,7 +4001,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4015,27 +4015,27 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4053,38 +4053,52 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129124933</v>
+        <v>129127084</v>
       </c>
       <c r="B28" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -4093,13 +4107,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>519886</v>
+        <v>520203</v>
       </c>
       <c r="R28" t="n">
-        <v>7001592</v>
+        <v>7001453</v>
       </c>
       <c r="S28" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4128,7 +4142,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4138,12 +4152,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:39</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran i hyggeskanten.</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4158,26 +4167,6 @@
       <c r="AH28" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4327,52 +4316,38 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129127084</v>
+        <v>129124933</v>
       </c>
       <c r="B30" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4381,13 +4356,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>520203</v>
+        <v>519886</v>
       </c>
       <c r="R30" t="n">
-        <v>7001453</v>
+        <v>7001592</v>
       </c>
       <c r="S30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4416,7 +4391,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4426,7 +4401,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>09:39</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran i hyggeskanten.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4441,6 +4421,26 @@
       <c r="AH30" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -5274,48 +5274,62 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129135677</v>
+        <v>129128320</v>
       </c>
       <c r="B37" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>520346</v>
+        <v>520352</v>
       </c>
       <c r="R37" t="n">
-        <v>7001536</v>
+        <v>7001397</v>
       </c>
       <c r="S37" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5344,7 +5358,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5354,7 +5368,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Minst 10 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5365,6 +5384,11 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -5381,62 +5405,48 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129128320</v>
+        <v>129135677</v>
       </c>
       <c r="B38" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>520352</v>
+        <v>520346</v>
       </c>
       <c r="R38" t="n">
-        <v>7001397</v>
+        <v>7001536</v>
       </c>
       <c r="S38" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5465,7 +5475,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5475,12 +5485,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:20</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Minst 10 plantor inom ca 0,5 m2 yta.</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5491,11 +5496,6 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -5950,32 +5950,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129193576</v>
+        <v>129193568</v>
       </c>
       <c r="B43" t="n">
-        <v>98727</v>
+        <v>80149</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5985,10 +5985,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>520675</v>
+        <v>520159</v>
       </c>
       <c r="R43" t="n">
-        <v>7001377</v>
+        <v>7001489</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6047,7 +6047,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129193582</v>
+        <v>129193576</v>
       </c>
       <c r="B44" t="n">
         <v>98727</v>
@@ -6075,33 +6075,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>520388</v>
+        <v>520675</v>
       </c>
       <c r="R44" t="n">
-        <v>7001418</v>
+        <v>7001377</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6136,18 +6120,12 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Minst 50</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -6166,45 +6144,61 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129193568</v>
+        <v>129193582</v>
       </c>
       <c r="B45" t="n">
-        <v>80149</v>
+        <v>98727</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>520159</v>
+        <v>520388</v>
       </c>
       <c r="R45" t="n">
-        <v>7001489</v>
+        <v>7001418</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6239,12 +6233,18 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Minst 50</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -6263,61 +6263,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129193583</v>
+        <v>129193542</v>
       </c>
       <c r="B46" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>520338</v>
+        <v>520422</v>
       </c>
       <c r="R46" t="n">
-        <v>7001427</v>
+        <v>7001418</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6354,7 +6338,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Minst 100</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6363,7 +6347,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -6382,45 +6365,61 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129193542</v>
+        <v>129193583</v>
       </c>
       <c r="B47" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>520422</v>
+        <v>520338</v>
       </c>
       <c r="R47" t="n">
-        <v>7001418</v>
+        <v>7001427</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6457,7 +6456,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Minst 100</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6466,6 +6465,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -6678,10 +6678,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129193523</v>
+        <v>129193566</v>
       </c>
       <c r="B50" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6689,21 +6689,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6713,10 +6713,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>520478</v>
+        <v>520180</v>
       </c>
       <c r="R50" t="n">
-        <v>7001335</v>
+        <v>7001458</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6749,11 +6749,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6780,10 +6775,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129193517</v>
+        <v>129193590</v>
       </c>
       <c r="B51" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6791,21 +6786,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6815,10 +6810,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>520301</v>
+        <v>520187</v>
       </c>
       <c r="R51" t="n">
-        <v>7001547</v>
+        <v>7001471</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6851,11 +6846,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6882,10 +6872,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129193590</v>
+        <v>129193523</v>
       </c>
       <c r="B52" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6893,21 +6883,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6917,10 +6907,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>520187</v>
+        <v>520478</v>
       </c>
       <c r="R52" t="n">
-        <v>7001471</v>
+        <v>7001335</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6953,6 +6943,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6979,10 +6974,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129193566</v>
+        <v>129193517</v>
       </c>
       <c r="B53" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6990,21 +6985,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -7014,10 +7009,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>520180</v>
+        <v>520301</v>
       </c>
       <c r="R53" t="n">
-        <v>7001458</v>
+        <v>7001547</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7050,6 +7045,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7389,10 +7389,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129193524</v>
+        <v>129193561</v>
       </c>
       <c r="B57" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7400,21 +7400,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7424,10 +7424,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>520478</v>
+        <v>520344</v>
       </c>
       <c r="R57" t="n">
-        <v>7001328</v>
+        <v>7001402</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7460,11 +7460,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7491,10 +7486,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129193544</v>
+        <v>129193567</v>
       </c>
       <c r="B58" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7502,21 +7497,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7526,10 +7521,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>520270</v>
+        <v>520184</v>
       </c>
       <c r="R58" t="n">
-        <v>7001484</v>
+        <v>7001482</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7562,11 +7557,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7593,10 +7583,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129193561</v>
+        <v>129193524</v>
       </c>
       <c r="B59" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7604,21 +7594,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7628,10 +7618,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>520344</v>
+        <v>520478</v>
       </c>
       <c r="R59" t="n">
-        <v>7001402</v>
+        <v>7001328</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7664,6 +7654,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7690,10 +7685,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129193567</v>
+        <v>129193544</v>
       </c>
       <c r="B60" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7701,21 +7696,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7725,10 +7720,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>520184</v>
+        <v>520270</v>
       </c>
       <c r="R60" t="n">
-        <v>7001482</v>
+        <v>7001484</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7761,6 +7756,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7787,57 +7787,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129193585</v>
+        <v>129193564</v>
       </c>
       <c r="B61" t="n">
-        <v>98727</v>
+        <v>80149</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>520122</v>
+        <v>520225</v>
       </c>
       <c r="R61" t="n">
-        <v>7001476</v>
+        <v>7001483</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7872,18 +7860,12 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Fler än 200</t>
-        </is>
-      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7902,7 +7884,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129193564</v>
+        <v>129193557</v>
       </c>
       <c r="B62" t="n">
         <v>80149</v>
@@ -7937,10 +7919,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>520225</v>
+        <v>520374</v>
       </c>
       <c r="R62" t="n">
-        <v>7001483</v>
+        <v>7001329</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7999,45 +7981,57 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129193557</v>
+        <v>129193585</v>
       </c>
       <c r="B63" t="n">
-        <v>80149</v>
+        <v>98727</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>520374</v>
+        <v>520122</v>
       </c>
       <c r="R63" t="n">
-        <v>7001329</v>
+        <v>7001476</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8072,12 +8066,18 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Fler än 200</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -8096,32 +8096,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129193560</v>
+        <v>129193593</v>
       </c>
       <c r="B64" t="n">
-        <v>80149</v>
+        <v>100916</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>222498</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -8131,10 +8131,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>520346</v>
+        <v>520101</v>
       </c>
       <c r="R64" t="n">
-        <v>7001396</v>
+        <v>7001658</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8193,7 +8193,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129193569</v>
+        <v>129193560</v>
       </c>
       <c r="B65" t="n">
         <v>80149</v>
@@ -8228,10 +8228,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>520094</v>
+        <v>520346</v>
       </c>
       <c r="R65" t="n">
-        <v>7001525</v>
+        <v>7001396</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8290,32 +8290,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129193593</v>
+        <v>129193569</v>
       </c>
       <c r="B66" t="n">
-        <v>100916</v>
+        <v>80149</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>222498</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -8325,10 +8325,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>520101</v>
+        <v>520094</v>
       </c>
       <c r="R66" t="n">
-        <v>7001658</v>
+        <v>7001525</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8387,10 +8387,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129193562</v>
+        <v>129193545</v>
       </c>
       <c r="B67" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8398,21 +8398,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8422,10 +8422,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>520335</v>
+        <v>519958</v>
       </c>
       <c r="R67" t="n">
-        <v>7001429</v>
+        <v>7001547</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8458,6 +8458,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8484,10 +8489,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129193545</v>
+        <v>129193562</v>
       </c>
       <c r="B68" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8495,21 +8500,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8519,10 +8524,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>519958</v>
+        <v>520335</v>
       </c>
       <c r="R68" t="n">
-        <v>7001547</v>
+        <v>7001429</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8555,11 +8560,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8915,32 +8915,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129193548</v>
+        <v>129193559</v>
       </c>
       <c r="B72" t="n">
-        <v>92508</v>
+        <v>80149</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4769</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8950,10 +8950,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>520063</v>
+        <v>520330</v>
       </c>
       <c r="R72" t="n">
-        <v>7001569</v>
+        <v>7001396</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9012,32 +9012,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129193559</v>
+        <v>129193548</v>
       </c>
       <c r="B73" t="n">
-        <v>80149</v>
+        <v>92508</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>4769</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -9047,10 +9047,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>520330</v>
+        <v>520063</v>
       </c>
       <c r="R73" t="n">
-        <v>7001396</v>
+        <v>7001569</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9109,10 +9109,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129193549</v>
+        <v>129193546</v>
       </c>
       <c r="B74" t="n">
-        <v>80150</v>
+        <v>57727</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9120,21 +9120,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -9144,10 +9144,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>520345</v>
+        <v>519958</v>
       </c>
       <c r="R74" t="n">
-        <v>7001396</v>
+        <v>7001542</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9180,6 +9180,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9206,61 +9211,45 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129193575</v>
+        <v>129193549</v>
       </c>
       <c r="B75" t="n">
-        <v>98727</v>
+        <v>80150</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="N75" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>520528</v>
+        <v>520345</v>
       </c>
       <c r="R75" t="n">
-        <v>7001465</v>
+        <v>7001396</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9295,18 +9284,12 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Minst 50</t>
-        </is>
-      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -9325,45 +9308,61 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129193546</v>
+        <v>129193575</v>
       </c>
       <c r="B76" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>519958</v>
+        <v>520528</v>
       </c>
       <c r="R76" t="n">
-        <v>7001542</v>
+        <v>7001465</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9400,7 +9399,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Minst 50</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9409,6 +9408,7 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 43533-2025 artfynd.xlsx
+++ b/artfynd/A 43533-2025 artfynd.xlsx
@@ -817,47 +817,38 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129135545</v>
+        <v>129135852</v>
       </c>
       <c r="B3" t="n">
-        <v>98727</v>
+        <v>99061</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>219880</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>gulnande löv/blad</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -866,10 +857,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>520564</v>
+        <v>520213</v>
       </c>
       <c r="R3" t="n">
-        <v>7001441</v>
+        <v>7001609</v>
       </c>
       <c r="S3" t="n">
         <v>9</v>
@@ -901,7 +892,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -911,7 +902,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -943,38 +934,47 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129135852</v>
+        <v>129135545</v>
       </c>
       <c r="B4" t="n">
-        <v>99061</v>
+        <v>98727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219880</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>gulnande löv/blad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -983,10 +983,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>520213</v>
+        <v>520564</v>
       </c>
       <c r="R4" t="n">
-        <v>7001609</v>
+        <v>7001441</v>
       </c>
       <c r="S4" t="n">
         <v>9</v>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1182,38 +1182,47 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129127182</v>
+        <v>129126843</v>
       </c>
       <c r="B6" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1227,13 +1236,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>520186</v>
+        <v>520211</v>
       </c>
       <c r="R6" t="n">
-        <v>7001459</v>
+        <v>7001475</v>
       </c>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1262,7 +1271,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1272,12 +1281,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran  intill en gammal sälg.</t>
+          <t>Minst 100 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1292,26 +1301,6 @@
       <c r="AH6" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1329,7 +1318,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129131350</v>
+        <v>129127182</v>
       </c>
       <c r="B7" t="n">
         <v>57727</v>
@@ -1360,7 +1349,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1374,10 +1363,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>520520</v>
+        <v>520186</v>
       </c>
       <c r="R7" t="n">
-        <v>7001311</v>
+        <v>7001459</v>
       </c>
       <c r="S7" t="n">
         <v>8</v>
@@ -1409,7 +1398,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1419,12 +1408,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack, enstaka färska och rikligt med äldre på en tall.</t>
+          <t>Ringhack, äldre, på stambasen av en gran  intill en gammal sälg.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1438,17 +1427,17 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -1458,7 +1447,7 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1476,47 +1465,38 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129126843</v>
+        <v>129131350</v>
       </c>
       <c r="B8" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1530,13 +1510,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>520211</v>
+        <v>520520</v>
       </c>
       <c r="R8" t="n">
-        <v>7001475</v>
+        <v>7001311</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1565,7 +1545,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1575,12 +1555,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Minst 100 plantor inom ca 0,5 m2 yta.</t>
+          <t>Ringhack, enstaka färska och rikligt med äldre på en tall.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1594,7 +1574,27 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1973,10 +1973,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129126617</v>
+        <v>129127736</v>
       </c>
       <c r="B12" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1984,27 +1984,27 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -2013,13 +2013,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>520219</v>
+        <v>520237</v>
       </c>
       <c r="R12" t="n">
-        <v>7001429</v>
+        <v>7001416</v>
       </c>
       <c r="S12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2048,7 +2048,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2058,7 +2058,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2070,19 +2075,29 @@
       <c r="AG12" t="b">
         <v>0</v>
       </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2100,10 +2115,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129127736</v>
+        <v>129126617</v>
       </c>
       <c r="B13" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2111,27 +2126,27 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2140,13 +2155,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>520237</v>
+        <v>520219</v>
       </c>
       <c r="R13" t="n">
-        <v>7001416</v>
+        <v>7001429</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2175,7 +2190,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2185,12 +2200,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:01</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2202,29 +2212,19 @@
       <c r="AG13" t="b">
         <v>0</v>
       </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2505,10 +2505,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129127604</v>
+        <v>129128148</v>
       </c>
       <c r="B16" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2516,27 +2516,27 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2545,13 +2545,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>520243</v>
+        <v>520338</v>
       </c>
       <c r="R16" t="n">
-        <v>7001423</v>
+        <v>7001407</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2590,12 +2590,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:59</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Fertil lunglav på en sälg med doftticka.</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2609,27 +2604,27 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark of dead wood # Betula</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2647,7 +2642,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129128162</v>
+        <v>129127604</v>
       </c>
       <c r="B17" t="n">
         <v>80149</v>
@@ -2678,7 +2673,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2687,13 +2682,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>520355</v>
+        <v>520243</v>
       </c>
       <c r="R17" t="n">
-        <v>7001412</v>
+        <v>7001423</v>
       </c>
       <c r="S17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2722,7 +2717,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2732,7 +2727,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Fertil lunglav på en sälg med doftticka.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -2784,10 +2784,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129128148</v>
+        <v>129128162</v>
       </c>
       <c r="B18" t="n">
-        <v>80150</v>
+        <v>80149</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2795,21 +2795,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2824,13 +2824,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>520338</v>
+        <v>520355</v>
       </c>
       <c r="R18" t="n">
-        <v>7001407</v>
+        <v>7001412</v>
       </c>
       <c r="S18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2888,22 +2888,22 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Betula</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2921,62 +2921,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129127509</v>
+        <v>129131389</v>
       </c>
       <c r="B19" t="n">
-        <v>92148</v>
+        <v>79044</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>520242</v>
+        <v>520611</v>
       </c>
       <c r="R19" t="n">
-        <v>7001434</v>
+        <v>7001285</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3005,7 +2991,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3015,7 +3001,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3026,31 +3012,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Salix caprea</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -3067,48 +3028,62 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129131389</v>
+        <v>129127509</v>
       </c>
       <c r="B20" t="n">
-        <v>79044</v>
+        <v>92148</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>520611</v>
+        <v>520242</v>
       </c>
       <c r="R20" t="n">
-        <v>7001285</v>
+        <v>7001434</v>
       </c>
       <c r="S20" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3137,7 +3112,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3147,7 +3122,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3158,6 +3133,31 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Salix caprea</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -3408,10 +3408,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129128128</v>
+        <v>129136001</v>
       </c>
       <c r="B23" t="n">
-        <v>80150</v>
+        <v>79044</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3419,42 +3419,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>520340</v>
+        <v>520012</v>
       </c>
       <c r="R23" t="n">
-        <v>7001392</v>
+        <v>7001652</v>
       </c>
       <c r="S23" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3483,7 +3478,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3493,7 +3488,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3504,31 +3499,6 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3545,7 +3515,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129136001</v>
+        <v>129126703</v>
       </c>
       <c r="B24" t="n">
         <v>79044</v>
@@ -3580,13 +3550,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>520012</v>
+        <v>520253</v>
       </c>
       <c r="R24" t="n">
-        <v>7001652</v>
+        <v>7001454</v>
       </c>
       <c r="S24" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3615,7 +3585,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3625,7 +3595,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3636,6 +3606,31 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3652,10 +3647,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129126703</v>
+        <v>129128128</v>
       </c>
       <c r="B25" t="n">
-        <v>79044</v>
+        <v>80150</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3663,34 +3658,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>520253</v>
+        <v>520340</v>
       </c>
       <c r="R25" t="n">
-        <v>7001454</v>
+        <v>7001392</v>
       </c>
       <c r="S25" t="n">
         <v>9</v>
@@ -3722,7 +3722,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3732,7 +3732,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3746,27 +3746,27 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3784,10 +3784,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129127211</v>
+        <v>129131479</v>
       </c>
       <c r="B26" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3795,42 +3795,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>520158</v>
+        <v>520712</v>
       </c>
       <c r="R26" t="n">
-        <v>7001448</v>
+        <v>7001363</v>
       </c>
       <c r="S26" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3859,7 +3854,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3869,7 +3864,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3883,27 +3878,27 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3921,10 +3916,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129131479</v>
+        <v>129127211</v>
       </c>
       <c r="B27" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3932,37 +3927,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>520712</v>
+        <v>520158</v>
       </c>
       <c r="R27" t="n">
-        <v>7001363</v>
+        <v>7001448</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3991,7 +3991,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4001,7 +4001,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4015,27 +4015,27 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4053,67 +4053,48 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129127084</v>
+        <v>129131418</v>
       </c>
       <c r="B28" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>520203</v>
+        <v>520682</v>
       </c>
       <c r="R28" t="n">
-        <v>7001453</v>
+        <v>7001354</v>
       </c>
       <c r="S28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4142,7 +4123,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4152,7 +4133,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4166,7 +4147,27 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4184,10 +4185,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129131418</v>
+        <v>129124933</v>
       </c>
       <c r="B29" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4195,37 +4196,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>520682</v>
+        <v>519886</v>
       </c>
       <c r="R29" t="n">
-        <v>7001354</v>
+        <v>7001592</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4254,7 +4260,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4264,7 +4270,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>09:39</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran i hyggeskanten.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4278,7 +4289,7 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
@@ -4293,12 +4304,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4316,38 +4327,52 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129124933</v>
+        <v>129127084</v>
       </c>
       <c r="B30" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4356,13 +4381,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>519886</v>
+        <v>520203</v>
       </c>
       <c r="R30" t="n">
-        <v>7001592</v>
+        <v>7001453</v>
       </c>
       <c r="S30" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4391,7 +4416,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4401,12 +4426,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:39</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran i hyggeskanten.</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4421,26 +4441,6 @@
       <c r="AH30" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -5274,62 +5274,48 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129128320</v>
+        <v>129135677</v>
       </c>
       <c r="B37" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>520352</v>
+        <v>520346</v>
       </c>
       <c r="R37" t="n">
-        <v>7001397</v>
+        <v>7001536</v>
       </c>
       <c r="S37" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5358,7 +5344,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5368,12 +5354,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:20</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Minst 10 plantor inom ca 0,5 m2 yta.</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5384,11 +5365,6 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -5405,48 +5381,62 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129135677</v>
+        <v>129128320</v>
       </c>
       <c r="B38" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>520346</v>
+        <v>520352</v>
       </c>
       <c r="R38" t="n">
-        <v>7001536</v>
+        <v>7001397</v>
       </c>
       <c r="S38" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5475,7 +5465,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5485,7 +5475,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Minst 10 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5496,6 +5491,11 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -5751,10 +5751,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129193558</v>
+        <v>129193518</v>
       </c>
       <c r="B41" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5762,21 +5762,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5786,10 +5786,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>520415</v>
+        <v>520676</v>
       </c>
       <c r="R41" t="n">
-        <v>7001416</v>
+        <v>7001377</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5822,6 +5822,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5848,10 +5853,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129193518</v>
+        <v>129193558</v>
       </c>
       <c r="B42" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5859,21 +5864,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5883,10 +5888,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>520676</v>
+        <v>520415</v>
       </c>
       <c r="R42" t="n">
-        <v>7001377</v>
+        <v>7001416</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5919,11 +5924,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6678,10 +6678,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129193566</v>
+        <v>129193523</v>
       </c>
       <c r="B50" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6689,21 +6689,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6713,10 +6713,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>520180</v>
+        <v>520478</v>
       </c>
       <c r="R50" t="n">
-        <v>7001458</v>
+        <v>7001335</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6749,6 +6749,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6775,10 +6780,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129193590</v>
+        <v>129193517</v>
       </c>
       <c r="B51" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6786,21 +6791,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6810,10 +6815,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>520187</v>
+        <v>520301</v>
       </c>
       <c r="R51" t="n">
-        <v>7001471</v>
+        <v>7001547</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6846,6 +6851,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6872,45 +6882,61 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129193523</v>
+        <v>129193581</v>
       </c>
       <c r="B52" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>520478</v>
+        <v>520425</v>
       </c>
       <c r="R52" t="n">
-        <v>7001335</v>
+        <v>7001407</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6947,7 +6973,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Minst 80</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6956,6 +6982,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6974,10 +7001,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129193517</v>
+        <v>129193590</v>
       </c>
       <c r="B53" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6985,21 +7012,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -7009,10 +7036,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>520301</v>
+        <v>520187</v>
       </c>
       <c r="R53" t="n">
-        <v>7001547</v>
+        <v>7001471</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7045,11 +7072,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7076,61 +7098,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129193581</v>
+        <v>129193566</v>
       </c>
       <c r="B54" t="n">
-        <v>98727</v>
+        <v>80149</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>520425</v>
+        <v>520180</v>
       </c>
       <c r="R54" t="n">
-        <v>7001407</v>
+        <v>7001458</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7165,18 +7171,12 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Minst 80</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -8096,32 +8096,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129193593</v>
+        <v>129193560</v>
       </c>
       <c r="B64" t="n">
-        <v>100916</v>
+        <v>80149</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>222498</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -8131,10 +8131,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>520101</v>
+        <v>520346</v>
       </c>
       <c r="R64" t="n">
-        <v>7001658</v>
+        <v>7001396</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8193,7 +8193,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129193560</v>
+        <v>129193569</v>
       </c>
       <c r="B65" t="n">
         <v>80149</v>
@@ -8228,10 +8228,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>520346</v>
+        <v>520094</v>
       </c>
       <c r="R65" t="n">
-        <v>7001396</v>
+        <v>7001525</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8290,32 +8290,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129193569</v>
+        <v>129193593</v>
       </c>
       <c r="B66" t="n">
-        <v>80149</v>
+        <v>100916</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>222498</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -8325,10 +8325,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>520094</v>
+        <v>520101</v>
       </c>
       <c r="R66" t="n">
-        <v>7001525</v>
+        <v>7001658</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8915,32 +8915,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129193559</v>
+        <v>129193548</v>
       </c>
       <c r="B72" t="n">
-        <v>80149</v>
+        <v>92508</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>4769</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8950,10 +8950,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>520330</v>
+        <v>520063</v>
       </c>
       <c r="R72" t="n">
-        <v>7001396</v>
+        <v>7001569</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9012,32 +9012,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129193548</v>
+        <v>129193559</v>
       </c>
       <c r="B73" t="n">
-        <v>92508</v>
+        <v>80149</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4769</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -9047,10 +9047,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>520063</v>
+        <v>520330</v>
       </c>
       <c r="R73" t="n">
-        <v>7001569</v>
+        <v>7001396</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>

--- a/artfynd/A 43533-2025 artfynd.xlsx
+++ b/artfynd/A 43533-2025 artfynd.xlsx
@@ -1182,47 +1182,38 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129126843</v>
+        <v>129127182</v>
       </c>
       <c r="B6" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1236,13 +1227,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>520211</v>
+        <v>520186</v>
       </c>
       <c r="R6" t="n">
-        <v>7001475</v>
+        <v>7001459</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1271,7 +1262,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1281,12 +1272,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Minst 100 plantor inom ca 0,5 m2 yta.</t>
+          <t>Ringhack, äldre, på stambasen av en gran  intill en gammal sälg.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1301,6 +1292,26 @@
       <c r="AH6" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1318,7 +1329,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129127182</v>
+        <v>129131350</v>
       </c>
       <c r="B7" t="n">
         <v>57727</v>
@@ -1349,7 +1360,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1363,10 +1374,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>520186</v>
+        <v>520520</v>
       </c>
       <c r="R7" t="n">
-        <v>7001459</v>
+        <v>7001311</v>
       </c>
       <c r="S7" t="n">
         <v>8</v>
@@ -1398,7 +1409,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1408,12 +1419,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran  intill en gammal sälg.</t>
+          <t>Ringhack, enstaka färska och rikligt med äldre på en tall.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1427,17 +1438,17 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -1447,7 +1458,7 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Stem on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1465,38 +1476,47 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129131350</v>
+        <v>129126843</v>
       </c>
       <c r="B8" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1510,13 +1530,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>520520</v>
+        <v>520211</v>
       </c>
       <c r="R8" t="n">
-        <v>7001311</v>
+        <v>7001475</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1545,7 +1565,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1555,12 +1575,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack, enstaka färska och rikligt med äldre på en tall.</t>
+          <t>Minst 100 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1574,27 +1594,7 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1973,10 +1973,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129127736</v>
+        <v>129126617</v>
       </c>
       <c r="B12" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1984,27 +1984,27 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -2013,13 +2013,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>520237</v>
+        <v>520219</v>
       </c>
       <c r="R12" t="n">
-        <v>7001416</v>
+        <v>7001429</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2048,7 +2048,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2058,12 +2058,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:01</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2075,29 +2070,19 @@
       <c r="AG12" t="b">
         <v>0</v>
       </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2115,10 +2100,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129126617</v>
+        <v>129127736</v>
       </c>
       <c r="B13" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2126,27 +2111,27 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2155,13 +2140,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>520219</v>
+        <v>520237</v>
       </c>
       <c r="R13" t="n">
-        <v>7001429</v>
+        <v>7001416</v>
       </c>
       <c r="S13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2190,7 +2175,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2200,7 +2185,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2212,19 +2202,29 @@
       <c r="AG13" t="b">
         <v>0</v>
       </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2921,48 +2921,62 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129131389</v>
+        <v>129127509</v>
       </c>
       <c r="B19" t="n">
-        <v>79044</v>
+        <v>92148</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>520611</v>
+        <v>520242</v>
       </c>
       <c r="R19" t="n">
-        <v>7001285</v>
+        <v>7001434</v>
       </c>
       <c r="S19" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2991,7 +3005,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3001,7 +3015,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3012,6 +3026,31 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Salix caprea</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -3028,62 +3067,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129127509</v>
+        <v>129131389</v>
       </c>
       <c r="B20" t="n">
-        <v>92148</v>
+        <v>79044</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>520242</v>
+        <v>520611</v>
       </c>
       <c r="R20" t="n">
-        <v>7001434</v>
+        <v>7001285</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3112,7 +3137,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3122,7 +3147,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3133,31 +3158,6 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Salix caprea</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -3784,10 +3784,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129131479</v>
+        <v>129127211</v>
       </c>
       <c r="B26" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3795,37 +3795,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>520712</v>
+        <v>520158</v>
       </c>
       <c r="R26" t="n">
-        <v>7001363</v>
+        <v>7001448</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3854,7 +3859,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3864,7 +3869,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3878,27 +3883,27 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3916,10 +3921,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129127211</v>
+        <v>129131479</v>
       </c>
       <c r="B27" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3927,42 +3932,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>520158</v>
+        <v>520712</v>
       </c>
       <c r="R27" t="n">
-        <v>7001448</v>
+        <v>7001363</v>
       </c>
       <c r="S27" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3991,7 +3991,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4001,7 +4001,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4015,27 +4015,27 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4053,48 +4053,67 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129131418</v>
+        <v>129127084</v>
       </c>
       <c r="B28" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>520682</v>
+        <v>520203</v>
       </c>
       <c r="R28" t="n">
-        <v>7001354</v>
+        <v>7001453</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4123,7 +4142,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4133,7 +4152,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4147,27 +4166,7 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4185,10 +4184,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129124933</v>
+        <v>129131418</v>
       </c>
       <c r="B29" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4196,42 +4195,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>519886</v>
+        <v>520682</v>
       </c>
       <c r="R29" t="n">
-        <v>7001592</v>
+        <v>7001354</v>
       </c>
       <c r="S29" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4260,7 +4254,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4270,12 +4264,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:39</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran i hyggeskanten.</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4289,7 +4278,7 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
@@ -4304,12 +4293,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4327,52 +4316,38 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129127084</v>
+        <v>129124933</v>
       </c>
       <c r="B30" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4381,13 +4356,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>520203</v>
+        <v>519886</v>
       </c>
       <c r="R30" t="n">
-        <v>7001453</v>
+        <v>7001592</v>
       </c>
       <c r="S30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4416,7 +4391,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4426,7 +4401,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>09:39</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran i hyggeskanten.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4441,6 +4421,26 @@
       <c r="AH30" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -5950,32 +5950,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129193568</v>
+        <v>129193576</v>
       </c>
       <c r="B43" t="n">
-        <v>80149</v>
+        <v>98727</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5985,10 +5985,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>520159</v>
+        <v>520675</v>
       </c>
       <c r="R43" t="n">
-        <v>7001489</v>
+        <v>7001377</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6047,7 +6047,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129193576</v>
+        <v>129193582</v>
       </c>
       <c r="B44" t="n">
         <v>98727</v>
@@ -6075,17 +6075,33 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>520675</v>
+        <v>520388</v>
       </c>
       <c r="R44" t="n">
-        <v>7001377</v>
+        <v>7001418</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6120,12 +6136,18 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Minst 50</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -6144,61 +6166,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129193582</v>
+        <v>129193568</v>
       </c>
       <c r="B45" t="n">
-        <v>98727</v>
+        <v>80149</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>520388</v>
+        <v>520159</v>
       </c>
       <c r="R45" t="n">
-        <v>7001418</v>
+        <v>7001489</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6233,18 +6239,12 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Minst 50</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -6678,45 +6678,61 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129193523</v>
+        <v>129193581</v>
       </c>
       <c r="B50" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>520478</v>
+        <v>520425</v>
       </c>
       <c r="R50" t="n">
-        <v>7001335</v>
+        <v>7001407</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6753,7 +6769,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Minst 80</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6762,6 +6778,7 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -6780,10 +6797,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129193517</v>
+        <v>129193590</v>
       </c>
       <c r="B51" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6791,21 +6808,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6815,10 +6832,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>520301</v>
+        <v>520187</v>
       </c>
       <c r="R51" t="n">
-        <v>7001547</v>
+        <v>7001471</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6851,11 +6868,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6882,61 +6894,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129193581</v>
+        <v>129193566</v>
       </c>
       <c r="B52" t="n">
-        <v>98727</v>
+        <v>80149</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>520425</v>
+        <v>520180</v>
       </c>
       <c r="R52" t="n">
-        <v>7001407</v>
+        <v>7001458</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6971,18 +6967,12 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Minst 80</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -7001,10 +6991,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129193590</v>
+        <v>129193523</v>
       </c>
       <c r="B53" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7012,21 +7002,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -7036,10 +7026,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>520187</v>
+        <v>520478</v>
       </c>
       <c r="R53" t="n">
-        <v>7001471</v>
+        <v>7001335</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7072,6 +7062,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7098,10 +7093,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129193566</v>
+        <v>129193517</v>
       </c>
       <c r="B54" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7109,21 +7104,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -7133,10 +7128,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>520180</v>
+        <v>520301</v>
       </c>
       <c r="R54" t="n">
-        <v>7001458</v>
+        <v>7001547</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7169,6 +7164,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7787,45 +7787,57 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129193564</v>
+        <v>129193585</v>
       </c>
       <c r="B61" t="n">
-        <v>80149</v>
+        <v>98727</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>520225</v>
+        <v>520122</v>
       </c>
       <c r="R61" t="n">
-        <v>7001483</v>
+        <v>7001476</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7860,12 +7872,18 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Fler än 200</t>
+        </is>
+      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7884,7 +7902,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129193557</v>
+        <v>129193564</v>
       </c>
       <c r="B62" t="n">
         <v>80149</v>
@@ -7919,10 +7937,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>520374</v>
+        <v>520225</v>
       </c>
       <c r="R62" t="n">
-        <v>7001329</v>
+        <v>7001483</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7981,57 +7999,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129193585</v>
+        <v>129193557</v>
       </c>
       <c r="B63" t="n">
-        <v>98727</v>
+        <v>80149</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>520122</v>
+        <v>520374</v>
       </c>
       <c r="R63" t="n">
-        <v>7001476</v>
+        <v>7001329</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8066,18 +8072,12 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Fler än 200</t>
-        </is>
-      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -8915,32 +8915,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129193548</v>
+        <v>129193559</v>
       </c>
       <c r="B72" t="n">
-        <v>92508</v>
+        <v>80149</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4769</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8950,10 +8950,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>520063</v>
+        <v>520330</v>
       </c>
       <c r="R72" t="n">
-        <v>7001569</v>
+        <v>7001396</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9012,32 +9012,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129193559</v>
+        <v>129193548</v>
       </c>
       <c r="B73" t="n">
-        <v>80149</v>
+        <v>92508</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>4769</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -9047,10 +9047,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>520330</v>
+        <v>520063</v>
       </c>
       <c r="R73" t="n">
-        <v>7001396</v>
+        <v>7001569</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9109,10 +9109,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129193546</v>
+        <v>129193549</v>
       </c>
       <c r="B74" t="n">
-        <v>57727</v>
+        <v>80150</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9120,21 +9120,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -9144,10 +9144,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>519958</v>
+        <v>520345</v>
       </c>
       <c r="R74" t="n">
-        <v>7001542</v>
+        <v>7001396</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9180,11 +9180,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9211,10 +9206,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129193549</v>
+        <v>129193546</v>
       </c>
       <c r="B75" t="n">
-        <v>80150</v>
+        <v>57727</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9222,21 +9217,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -9246,10 +9241,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>520345</v>
+        <v>519958</v>
       </c>
       <c r="R75" t="n">
-        <v>7001396</v>
+        <v>7001542</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9282,6 +9277,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD75" t="b">

--- a/artfynd/A 43533-2025 artfynd.xlsx
+++ b/artfynd/A 43533-2025 artfynd.xlsx
@@ -675,38 +675,38 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129126527</v>
+        <v>129135852</v>
       </c>
       <c r="B2" t="n">
-        <v>80149</v>
+        <v>99061</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>219880</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>gulnande löv/blad</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>520189</v>
+        <v>520213</v>
       </c>
       <c r="R2" t="n">
-        <v>7001448</v>
+        <v>7001609</v>
       </c>
       <c r="S2" t="n">
         <v>9</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:12</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,27 +774,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -817,38 +792,38 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129135852</v>
+        <v>129126527</v>
       </c>
       <c r="B3" t="n">
-        <v>99061</v>
+        <v>80149</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219880</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>gulnande löv/blad</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -857,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>520213</v>
+        <v>520189</v>
       </c>
       <c r="R3" t="n">
-        <v>7001609</v>
+        <v>7001448</v>
       </c>
       <c r="S3" t="n">
         <v>9</v>
@@ -892,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -902,7 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -916,7 +896,27 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -1851,10 +1851,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129128175</v>
+        <v>129127736</v>
       </c>
       <c r="B11" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1862,37 +1862,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>520329</v>
+        <v>520237</v>
       </c>
       <c r="R11" t="n">
-        <v>7001400</v>
+        <v>7001416</v>
       </c>
       <c r="S11" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1921,7 +1926,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1931,7 +1936,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1943,6 +1953,11 @@
       <c r="AG11" t="b">
         <v>0</v>
       </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AJ11" t="inlineStr">
         <is>
           <t>gran</t>
@@ -1953,9 +1968,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1973,10 +1993,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129126617</v>
+        <v>129128175</v>
       </c>
       <c r="B12" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1984,42 +2004,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>520219</v>
+        <v>520329</v>
       </c>
       <c r="R12" t="n">
-        <v>7001429</v>
+        <v>7001400</v>
       </c>
       <c r="S12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2048,7 +2063,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2058,7 +2073,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2072,17 +2087,17 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2100,10 +2115,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129127736</v>
+        <v>129126617</v>
       </c>
       <c r="B13" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2111,27 +2126,27 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2140,13 +2155,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>520237</v>
+        <v>520219</v>
       </c>
       <c r="R13" t="n">
-        <v>7001416</v>
+        <v>7001429</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2175,7 +2190,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2185,12 +2200,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:01</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2202,29 +2212,19 @@
       <c r="AG13" t="b">
         <v>0</v>
       </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -3784,10 +3784,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129127211</v>
+        <v>129131479</v>
       </c>
       <c r="B26" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3795,42 +3795,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>520158</v>
+        <v>520712</v>
       </c>
       <c r="R26" t="n">
-        <v>7001448</v>
+        <v>7001363</v>
       </c>
       <c r="S26" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3859,7 +3854,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3869,7 +3864,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3883,27 +3878,27 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3921,10 +3916,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129131479</v>
+        <v>129127211</v>
       </c>
       <c r="B27" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3932,37 +3927,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>520712</v>
+        <v>520158</v>
       </c>
       <c r="R27" t="n">
-        <v>7001363</v>
+        <v>7001448</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3991,7 +3991,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4001,7 +4001,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4015,27 +4015,27 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4053,67 +4053,48 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129127084</v>
+        <v>129131418</v>
       </c>
       <c r="B28" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>520203</v>
+        <v>520682</v>
       </c>
       <c r="R28" t="n">
-        <v>7001453</v>
+        <v>7001354</v>
       </c>
       <c r="S28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4142,7 +4123,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4152,7 +4133,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4166,7 +4147,27 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4184,10 +4185,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129131418</v>
+        <v>129124933</v>
       </c>
       <c r="B29" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4195,37 +4196,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>520682</v>
+        <v>519886</v>
       </c>
       <c r="R29" t="n">
-        <v>7001354</v>
+        <v>7001592</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4254,7 +4260,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4264,7 +4270,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>09:39</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran i hyggeskanten.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4278,7 +4289,7 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
@@ -4293,12 +4304,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4316,38 +4327,52 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129124933</v>
+        <v>129127084</v>
       </c>
       <c r="B30" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4356,13 +4381,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>519886</v>
+        <v>520203</v>
       </c>
       <c r="R30" t="n">
-        <v>7001592</v>
+        <v>7001453</v>
       </c>
       <c r="S30" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4391,7 +4416,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4401,12 +4426,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:39</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran i hyggeskanten.</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4421,26 +4441,6 @@
       <c r="AH30" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -5950,32 +5950,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129193576</v>
+        <v>129193568</v>
       </c>
       <c r="B43" t="n">
-        <v>98727</v>
+        <v>80149</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5985,10 +5985,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>520675</v>
+        <v>520159</v>
       </c>
       <c r="R43" t="n">
-        <v>7001377</v>
+        <v>7001489</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6047,7 +6047,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129193582</v>
+        <v>129193576</v>
       </c>
       <c r="B44" t="n">
         <v>98727</v>
@@ -6075,33 +6075,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>520388</v>
+        <v>520675</v>
       </c>
       <c r="R44" t="n">
-        <v>7001418</v>
+        <v>7001377</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6136,18 +6120,12 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Minst 50</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -6166,45 +6144,61 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129193568</v>
+        <v>129193582</v>
       </c>
       <c r="B45" t="n">
-        <v>80149</v>
+        <v>98727</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>520159</v>
+        <v>520388</v>
       </c>
       <c r="R45" t="n">
-        <v>7001489</v>
+        <v>7001418</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6239,12 +6233,18 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Minst 50</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -6263,45 +6263,61 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129193542</v>
+        <v>129193583</v>
       </c>
       <c r="B46" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>520422</v>
+        <v>520338</v>
       </c>
       <c r="R46" t="n">
-        <v>7001418</v>
+        <v>7001427</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6338,7 +6354,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Minst 100</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6347,6 +6363,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -6365,61 +6382,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129193583</v>
+        <v>129193542</v>
       </c>
       <c r="B47" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>520338</v>
+        <v>520422</v>
       </c>
       <c r="R47" t="n">
-        <v>7001427</v>
+        <v>7001418</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6456,7 +6457,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Minst 100</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6465,7 +6466,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -6678,61 +6678,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129193581</v>
+        <v>129193566</v>
       </c>
       <c r="B50" t="n">
-        <v>98727</v>
+        <v>80149</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>520425</v>
+        <v>520180</v>
       </c>
       <c r="R50" t="n">
-        <v>7001407</v>
+        <v>7001458</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6767,18 +6751,12 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Minst 80</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -6797,10 +6775,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129193590</v>
+        <v>129193523</v>
       </c>
       <c r="B51" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6808,21 +6786,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6832,10 +6810,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>520187</v>
+        <v>520478</v>
       </c>
       <c r="R51" t="n">
-        <v>7001471</v>
+        <v>7001335</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6868,6 +6846,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6894,10 +6877,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129193566</v>
+        <v>129193517</v>
       </c>
       <c r="B52" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6905,21 +6888,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6929,10 +6912,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>520180</v>
+        <v>520301</v>
       </c>
       <c r="R52" t="n">
-        <v>7001458</v>
+        <v>7001547</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6965,6 +6948,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6991,10 +6979,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129193523</v>
+        <v>129193590</v>
       </c>
       <c r="B53" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7002,21 +6990,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -7026,10 +7014,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>520478</v>
+        <v>520187</v>
       </c>
       <c r="R53" t="n">
-        <v>7001335</v>
+        <v>7001471</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7062,11 +7050,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7093,45 +7076,61 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129193517</v>
+        <v>129193581</v>
       </c>
       <c r="B54" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>520301</v>
+        <v>520425</v>
       </c>
       <c r="R54" t="n">
-        <v>7001547</v>
+        <v>7001407</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7168,7 +7167,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Minst 80</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7177,6 +7176,7 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -7389,10 +7389,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129193561</v>
+        <v>129193544</v>
       </c>
       <c r="B57" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7400,21 +7400,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7424,10 +7424,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>520344</v>
+        <v>520270</v>
       </c>
       <c r="R57" t="n">
-        <v>7001402</v>
+        <v>7001484</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7460,6 +7460,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7486,10 +7491,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129193567</v>
+        <v>129193524</v>
       </c>
       <c r="B58" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7497,21 +7502,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7521,10 +7526,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>520184</v>
+        <v>520478</v>
       </c>
       <c r="R58" t="n">
-        <v>7001482</v>
+        <v>7001328</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7557,6 +7562,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7583,10 +7593,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129193524</v>
+        <v>129193561</v>
       </c>
       <c r="B59" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7594,21 +7604,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7618,10 +7628,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>520478</v>
+        <v>520344</v>
       </c>
       <c r="R59" t="n">
-        <v>7001328</v>
+        <v>7001402</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7654,11 +7664,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7685,10 +7690,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129193544</v>
+        <v>129193567</v>
       </c>
       <c r="B60" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7696,21 +7701,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7720,10 +7725,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>520270</v>
+        <v>520184</v>
       </c>
       <c r="R60" t="n">
-        <v>7001484</v>
+        <v>7001482</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7756,11 +7761,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7787,57 +7787,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129193585</v>
+        <v>129193564</v>
       </c>
       <c r="B61" t="n">
-        <v>98727</v>
+        <v>80149</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>520122</v>
+        <v>520225</v>
       </c>
       <c r="R61" t="n">
-        <v>7001476</v>
+        <v>7001483</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7872,18 +7860,12 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Fler än 200</t>
-        </is>
-      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7902,7 +7884,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129193564</v>
+        <v>129193557</v>
       </c>
       <c r="B62" t="n">
         <v>80149</v>
@@ -7937,10 +7919,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>520225</v>
+        <v>520374</v>
       </c>
       <c r="R62" t="n">
-        <v>7001483</v>
+        <v>7001329</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7999,45 +7981,57 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129193557</v>
+        <v>129193585</v>
       </c>
       <c r="B63" t="n">
-        <v>80149</v>
+        <v>98727</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>520374</v>
+        <v>520122</v>
       </c>
       <c r="R63" t="n">
-        <v>7001329</v>
+        <v>7001476</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8072,12 +8066,18 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Fler än 200</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -8915,32 +8915,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129193559</v>
+        <v>129193548</v>
       </c>
       <c r="B72" t="n">
-        <v>80149</v>
+        <v>92508</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>4769</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8950,10 +8950,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>520330</v>
+        <v>520063</v>
       </c>
       <c r="R72" t="n">
-        <v>7001396</v>
+        <v>7001569</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9012,32 +9012,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129193548</v>
+        <v>129193559</v>
       </c>
       <c r="B73" t="n">
-        <v>92508</v>
+        <v>80149</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4769</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -9047,10 +9047,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>520063</v>
+        <v>520330</v>
       </c>
       <c r="R73" t="n">
-        <v>7001569</v>
+        <v>7001396</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9109,45 +9109,61 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129193549</v>
+        <v>129193575</v>
       </c>
       <c r="B74" t="n">
-        <v>80150</v>
+        <v>98727</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>520345</v>
+        <v>520528</v>
       </c>
       <c r="R74" t="n">
-        <v>7001396</v>
+        <v>7001465</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9182,12 +9198,18 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Minst 50</t>
+        </is>
+      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -9308,61 +9330,45 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129193575</v>
+        <v>129193549</v>
       </c>
       <c r="B76" t="n">
-        <v>98727</v>
+        <v>80150</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="N76" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>520528</v>
+        <v>520345</v>
       </c>
       <c r="R76" t="n">
-        <v>7001465</v>
+        <v>7001396</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9397,18 +9403,12 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Minst 50</t>
-        </is>
-      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 43533-2025 artfynd.xlsx
+++ b/artfynd/A 43533-2025 artfynd.xlsx
@@ -675,38 +675,47 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129135852</v>
+        <v>129135545</v>
       </c>
       <c r="B2" t="n">
-        <v>99061</v>
+        <v>98756</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219880</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>gulnande löv/blad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -715,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>520213</v>
+        <v>520564</v>
       </c>
       <c r="R2" t="n">
-        <v>7001609</v>
+        <v>7001441</v>
       </c>
       <c r="S2" t="n">
         <v>9</v>
@@ -750,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,38 +801,38 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129126527</v>
+        <v>129135852</v>
       </c>
       <c r="B3" t="n">
-        <v>80149</v>
+        <v>99090</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>219880</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>gulnande löv/blad</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -832,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>520189</v>
+        <v>520213</v>
       </c>
       <c r="R3" t="n">
-        <v>7001448</v>
+        <v>7001609</v>
       </c>
       <c r="S3" t="n">
         <v>9</v>
@@ -867,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:12</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,27 +900,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -934,47 +918,38 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129135545</v>
+        <v>129126527</v>
       </c>
       <c r="B4" t="n">
-        <v>98727</v>
+        <v>80175</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -983,10 +958,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>520564</v>
+        <v>520189</v>
       </c>
       <c r="R4" t="n">
-        <v>7001441</v>
+        <v>7001448</v>
       </c>
       <c r="S4" t="n">
         <v>9</v>
@@ -1018,7 +993,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1028,7 +1003,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1042,7 +1022,27 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1063,7 +1063,7 @@
         <v>129131270</v>
       </c>
       <c r="B5" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1185,7 +1185,7 @@
         <v>129127182</v>
       </c>
       <c r="B6" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>129131350</v>
       </c>
       <c r="B7" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>129126843</v>
       </c>
       <c r="B8" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1615,7 +1615,7 @@
         <v>129135692</v>
       </c>
       <c r="B9" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>129135867</v>
       </c>
       <c r="B10" t="n">
-        <v>100916</v>
+        <v>100945</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1851,10 +1851,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129127736</v>
+        <v>129128175</v>
       </c>
       <c r="B11" t="n">
-        <v>57727</v>
+        <v>79070</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1862,42 +1862,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>520237</v>
+        <v>520329</v>
       </c>
       <c r="R11" t="n">
-        <v>7001416</v>
+        <v>7001400</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1926,7 +1921,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1936,12 +1931,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:01</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1953,11 +1943,6 @@
       <c r="AG11" t="b">
         <v>0</v>
       </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AJ11" t="inlineStr">
         <is>
           <t>gran</t>
@@ -1968,14 +1953,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1993,10 +1973,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129128175</v>
+        <v>129127736</v>
       </c>
       <c r="B12" t="n">
-        <v>79044</v>
+        <v>57730</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2004,37 +1984,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>520329</v>
+        <v>520237</v>
       </c>
       <c r="R12" t="n">
-        <v>7001400</v>
+        <v>7001416</v>
       </c>
       <c r="S12" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2063,7 +2048,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2073,7 +2058,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2085,6 +2075,11 @@
       <c r="AG12" t="b">
         <v>0</v>
       </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AJ12" t="inlineStr">
         <is>
           <t>gran</t>
@@ -2095,9 +2090,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2118,7 +2118,7 @@
         <v>129126617</v>
       </c>
       <c r="B13" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         <v>129126547</v>
       </c>
       <c r="B14" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2382,7 +2382,7 @@
         <v>129135822</v>
       </c>
       <c r="B15" t="n">
-        <v>104198</v>
+        <v>104227</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
         <v>129128148</v>
       </c>
       <c r="B16" t="n">
-        <v>80150</v>
+        <v>80176</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2645,7 +2645,7 @@
         <v>129127604</v>
       </c>
       <c r="B17" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2787,7 +2787,7 @@
         <v>129128162</v>
       </c>
       <c r="B18" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2921,62 +2921,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129127509</v>
+        <v>129131389</v>
       </c>
       <c r="B19" t="n">
-        <v>92148</v>
+        <v>79070</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>520242</v>
+        <v>520611</v>
       </c>
       <c r="R19" t="n">
-        <v>7001434</v>
+        <v>7001285</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3005,7 +2991,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3015,7 +3001,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3026,31 +3012,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Salix caprea</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -3067,48 +3028,62 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129131389</v>
+        <v>129127509</v>
       </c>
       <c r="B20" t="n">
-        <v>79044</v>
+        <v>92176</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>520611</v>
+        <v>520242</v>
       </c>
       <c r="R20" t="n">
-        <v>7001285</v>
+        <v>7001434</v>
       </c>
       <c r="S20" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3137,7 +3112,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3147,7 +3122,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3158,6 +3133,31 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Salix caprea</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -3177,7 +3177,7 @@
         <v>129125122</v>
       </c>
       <c r="B21" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
         <v>129126633</v>
       </c>
       <c r="B22" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3408,10 +3408,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129136001</v>
+        <v>129128128</v>
       </c>
       <c r="B23" t="n">
-        <v>79044</v>
+        <v>80176</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3419,37 +3419,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>520012</v>
+        <v>520340</v>
       </c>
       <c r="R23" t="n">
-        <v>7001652</v>
+        <v>7001392</v>
       </c>
       <c r="S23" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3478,7 +3483,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3488,7 +3493,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3499,6 +3504,31 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3515,10 +3545,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129126703</v>
+        <v>129136001</v>
       </c>
       <c r="B24" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3550,13 +3580,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>520253</v>
+        <v>520012</v>
       </c>
       <c r="R24" t="n">
-        <v>7001454</v>
+        <v>7001652</v>
       </c>
       <c r="S24" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3585,7 +3615,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3595,7 +3625,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3606,31 +3636,6 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3647,10 +3652,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129128128</v>
+        <v>129126703</v>
       </c>
       <c r="B25" t="n">
-        <v>80150</v>
+        <v>79070</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3658,39 +3663,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>520340</v>
+        <v>520253</v>
       </c>
       <c r="R25" t="n">
-        <v>7001392</v>
+        <v>7001454</v>
       </c>
       <c r="S25" t="n">
         <v>9</v>
@@ -3722,7 +3722,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3732,7 +3732,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3746,27 +3746,27 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3787,7 +3787,7 @@
         <v>129131479</v>
       </c>
       <c r="B26" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3919,7 +3919,7 @@
         <v>129127211</v>
       </c>
       <c r="B27" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4056,7 +4056,7 @@
         <v>129131418</v>
       </c>
       <c r="B28" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
         <v>129124933</v>
       </c>
       <c r="B29" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4330,7 +4330,7 @@
         <v>129127084</v>
       </c>
       <c r="B30" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         <v>129135649</v>
       </c>
       <c r="B31" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4598,7 +4598,7 @@
         <v>129125106</v>
       </c>
       <c r="B32" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4725,7 +4725,7 @@
         <v>129128345</v>
       </c>
       <c r="B33" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4862,7 +4862,7 @@
         <v>129135770</v>
       </c>
       <c r="B34" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4993,7 +4993,7 @@
         <v>129128023</v>
       </c>
       <c r="B35" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5135,7 +5135,7 @@
         <v>129135454</v>
       </c>
       <c r="B36" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5277,7 +5277,7 @@
         <v>129135677</v>
       </c>
       <c r="B37" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5384,7 +5384,7 @@
         <v>129128320</v>
       </c>
       <c r="B38" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5515,7 +5515,7 @@
         <v>129135697</v>
       </c>
       <c r="B39" t="n">
-        <v>80178</v>
+        <v>80204</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5652,7 +5652,7 @@
         <v>129193543</v>
       </c>
       <c r="B40" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5754,7 +5754,7 @@
         <v>129193518</v>
       </c>
       <c r="B41" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5856,7 +5856,7 @@
         <v>129193558</v>
       </c>
       <c r="B42" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5953,7 +5953,7 @@
         <v>129193568</v>
       </c>
       <c r="B43" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6050,7 +6050,7 @@
         <v>129193576</v>
       </c>
       <c r="B44" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6147,7 +6147,7 @@
         <v>129193582</v>
       </c>
       <c r="B45" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6263,61 +6263,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129193583</v>
+        <v>129193542</v>
       </c>
       <c r="B46" t="n">
-        <v>98727</v>
+        <v>57730</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>520338</v>
+        <v>520422</v>
       </c>
       <c r="R46" t="n">
-        <v>7001427</v>
+        <v>7001418</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6354,7 +6338,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Minst 100</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6363,7 +6347,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -6382,45 +6365,61 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129193542</v>
+        <v>129193583</v>
       </c>
       <c r="B47" t="n">
-        <v>57727</v>
+        <v>98756</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>520422</v>
+        <v>520338</v>
       </c>
       <c r="R47" t="n">
-        <v>7001418</v>
+        <v>7001427</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6457,7 +6456,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Minst 100</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6466,6 +6465,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -6487,7 +6487,7 @@
         <v>129193565</v>
       </c>
       <c r="B48" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6584,7 +6584,7 @@
         <v>129193591</v>
       </c>
       <c r="B49" t="n">
-        <v>92871</v>
+        <v>92899</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6681,7 +6681,7 @@
         <v>129193566</v>
       </c>
       <c r="B50" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6775,10 +6775,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129193523</v>
+        <v>129193590</v>
       </c>
       <c r="B51" t="n">
-        <v>57727</v>
+        <v>79070</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6786,21 +6786,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6810,10 +6810,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>520478</v>
+        <v>520187</v>
       </c>
       <c r="R51" t="n">
-        <v>7001335</v>
+        <v>7001471</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6846,11 +6846,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6877,10 +6872,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129193517</v>
+        <v>129193523</v>
       </c>
       <c r="B52" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6912,10 +6907,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>520301</v>
+        <v>520478</v>
       </c>
       <c r="R52" t="n">
-        <v>7001547</v>
+        <v>7001335</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6952,7 +6947,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6979,10 +6974,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129193590</v>
+        <v>129193517</v>
       </c>
       <c r="B53" t="n">
-        <v>79044</v>
+        <v>57730</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6990,21 +6985,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -7014,10 +7009,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>520187</v>
+        <v>520301</v>
       </c>
       <c r="R53" t="n">
-        <v>7001471</v>
+        <v>7001547</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7050,6 +7045,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7079,7 +7079,7 @@
         <v>129193581</v>
       </c>
       <c r="B54" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7198,7 +7198,7 @@
         <v>129193570</v>
       </c>
       <c r="B55" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7295,7 +7295,7 @@
         <v>129193550</v>
       </c>
       <c r="B56" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7389,10 +7389,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129193544</v>
+        <v>129193524</v>
       </c>
       <c r="B57" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7424,10 +7424,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>520270</v>
+        <v>520478</v>
       </c>
       <c r="R57" t="n">
-        <v>7001484</v>
+        <v>7001328</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7464,7 +7464,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7491,10 +7491,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129193524</v>
+        <v>129193544</v>
       </c>
       <c r="B58" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7526,10 +7526,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>520478</v>
+        <v>520270</v>
       </c>
       <c r="R58" t="n">
-        <v>7001328</v>
+        <v>7001484</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7566,7 +7566,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7596,7 +7596,7 @@
         <v>129193561</v>
       </c>
       <c r="B59" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7693,7 +7693,7 @@
         <v>129193567</v>
       </c>
       <c r="B60" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7790,7 +7790,7 @@
         <v>129193564</v>
       </c>
       <c r="B61" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7887,7 +7887,7 @@
         <v>129193557</v>
       </c>
       <c r="B62" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7984,7 +7984,7 @@
         <v>129193585</v>
       </c>
       <c r="B63" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8096,32 +8096,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129193560</v>
+        <v>129193593</v>
       </c>
       <c r="B64" t="n">
-        <v>80149</v>
+        <v>100945</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>222498</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -8131,10 +8131,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>520346</v>
+        <v>520101</v>
       </c>
       <c r="R64" t="n">
-        <v>7001396</v>
+        <v>7001658</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8193,10 +8193,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129193569</v>
+        <v>129193560</v>
       </c>
       <c r="B65" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8228,10 +8228,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>520094</v>
+        <v>520346</v>
       </c>
       <c r="R65" t="n">
-        <v>7001525</v>
+        <v>7001396</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8290,32 +8290,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129193593</v>
+        <v>129193569</v>
       </c>
       <c r="B66" t="n">
-        <v>100916</v>
+        <v>80175</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>222498</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -8325,10 +8325,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>520101</v>
+        <v>520094</v>
       </c>
       <c r="R66" t="n">
-        <v>7001658</v>
+        <v>7001525</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8387,10 +8387,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129193545</v>
+        <v>129193562</v>
       </c>
       <c r="B67" t="n">
-        <v>57727</v>
+        <v>80175</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8398,21 +8398,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8422,10 +8422,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>519958</v>
+        <v>520335</v>
       </c>
       <c r="R67" t="n">
-        <v>7001547</v>
+        <v>7001429</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8458,11 +8458,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8489,10 +8484,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129193562</v>
+        <v>129193545</v>
       </c>
       <c r="B68" t="n">
-        <v>80149</v>
+        <v>57730</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8500,21 +8495,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8524,10 +8519,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>520335</v>
+        <v>519958</v>
       </c>
       <c r="R68" t="n">
-        <v>7001429</v>
+        <v>7001547</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8560,6 +8555,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8586,46 +8586,46 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129193573</v>
+        <v>129193584</v>
       </c>
       <c r="B69" t="n">
-        <v>57831</v>
+        <v>98756</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>103031</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N69" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -8637,10 +8637,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>520153</v>
+        <v>520320</v>
       </c>
       <c r="R69" t="n">
-        <v>7001500</v>
+        <v>7001451</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8675,12 +8675,18 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Minst 100</t>
+        </is>
+      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -8699,46 +8705,46 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129193584</v>
+        <v>129193573</v>
       </c>
       <c r="B70" t="n">
-        <v>98727</v>
+        <v>57834</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>103031</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N70" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -8750,10 +8756,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>520320</v>
+        <v>520153</v>
       </c>
       <c r="R70" t="n">
-        <v>7001451</v>
+        <v>7001500</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8788,18 +8794,12 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Minst 100</t>
-        </is>
-      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -8821,7 +8821,7 @@
         <v>129193563</v>
       </c>
       <c r="B71" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8918,7 +8918,7 @@
         <v>129193548</v>
       </c>
       <c r="B72" t="n">
-        <v>92508</v>
+        <v>92536</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9015,7 +9015,7 @@
         <v>129193559</v>
       </c>
       <c r="B73" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9112,7 +9112,7 @@
         <v>129193575</v>
       </c>
       <c r="B74" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9228,10 +9228,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129193546</v>
+        <v>129193549</v>
       </c>
       <c r="B75" t="n">
-        <v>57727</v>
+        <v>80176</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9239,21 +9239,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -9263,10 +9263,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>519958</v>
+        <v>520345</v>
       </c>
       <c r="R75" t="n">
-        <v>7001542</v>
+        <v>7001396</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9299,11 +9299,6 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9330,10 +9325,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129193549</v>
+        <v>129193546</v>
       </c>
       <c r="B76" t="n">
-        <v>80150</v>
+        <v>57730</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9341,21 +9336,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9365,10 +9360,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>520345</v>
+        <v>519958</v>
       </c>
       <c r="R76" t="n">
-        <v>7001396</v>
+        <v>7001542</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9401,6 +9396,11 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD76" t="b">

--- a/artfynd/A 43533-2025 artfynd.xlsx
+++ b/artfynd/A 43533-2025 artfynd.xlsx
@@ -5751,10 +5751,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129193518</v>
+        <v>129193558</v>
       </c>
       <c r="B41" t="n">
-        <v>57730</v>
+        <v>80175</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5762,21 +5762,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5786,10 +5786,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>520676</v>
+        <v>520415</v>
       </c>
       <c r="R41" t="n">
-        <v>7001377</v>
+        <v>7001416</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5822,11 +5822,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5853,10 +5848,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129193558</v>
+        <v>129193518</v>
       </c>
       <c r="B42" t="n">
-        <v>80175</v>
+        <v>57730</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5864,21 +5859,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5888,10 +5883,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>520415</v>
+        <v>520676</v>
       </c>
       <c r="R42" t="n">
-        <v>7001416</v>
+        <v>7001377</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5924,6 +5919,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -8096,32 +8096,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129193593</v>
+        <v>129193560</v>
       </c>
       <c r="B64" t="n">
-        <v>100945</v>
+        <v>80175</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>222498</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -8131,10 +8131,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>520101</v>
+        <v>520346</v>
       </c>
       <c r="R64" t="n">
-        <v>7001658</v>
+        <v>7001396</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8193,7 +8193,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129193560</v>
+        <v>129193569</v>
       </c>
       <c r="B65" t="n">
         <v>80175</v>
@@ -8228,10 +8228,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>520346</v>
+        <v>520094</v>
       </c>
       <c r="R65" t="n">
-        <v>7001396</v>
+        <v>7001525</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8290,32 +8290,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129193569</v>
+        <v>129193593</v>
       </c>
       <c r="B66" t="n">
-        <v>80175</v>
+        <v>100945</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>222498</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -8325,10 +8325,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>520094</v>
+        <v>520101</v>
       </c>
       <c r="R66" t="n">
-        <v>7001525</v>
+        <v>7001658</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8586,46 +8586,46 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129193584</v>
+        <v>129193573</v>
       </c>
       <c r="B69" t="n">
-        <v>98756</v>
+        <v>57834</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>103031</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N69" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -8637,10 +8637,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>520320</v>
+        <v>520153</v>
       </c>
       <c r="R69" t="n">
-        <v>7001451</v>
+        <v>7001500</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8675,18 +8675,12 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Minst 100</t>
-        </is>
-      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -8705,46 +8699,46 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129193573</v>
+        <v>129193584</v>
       </c>
       <c r="B70" t="n">
-        <v>57834</v>
+        <v>98756</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>103031</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N70" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -8756,10 +8750,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>520153</v>
+        <v>520320</v>
       </c>
       <c r="R70" t="n">
-        <v>7001500</v>
+        <v>7001451</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8794,12 +8788,18 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Minst 100</t>
+        </is>
+      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 43533-2025 artfynd.xlsx
+++ b/artfynd/A 43533-2025 artfynd.xlsx
@@ -1185,7 +1185,7 @@
         <v>129127182</v>
       </c>
       <c r="B6" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>129131350</v>
       </c>
       <c r="B7" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         <v>129127736</v>
       </c>
       <c r="B12" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
         <v>129124933</v>
       </c>
       <c r="B29" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -5652,7 +5652,7 @@
         <v>129193543</v>
       </c>
       <c r="B40" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5851,7 +5851,7 @@
         <v>129193518</v>
       </c>
       <c r="B42" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6266,7 +6266,7 @@
         <v>129193542</v>
       </c>
       <c r="B46" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6875,7 +6875,7 @@
         <v>129193523</v>
       </c>
       <c r="B52" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         <v>129193517</v>
       </c>
       <c r="B53" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7392,7 +7392,7 @@
         <v>129193524</v>
       </c>
       <c r="B57" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7494,7 +7494,7 @@
         <v>129193544</v>
       </c>
       <c r="B58" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -8487,7 +8487,7 @@
         <v>129193545</v>
       </c>
       <c r="B68" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -9328,7 +9328,7 @@
         <v>129193546</v>
       </c>
       <c r="B76" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 43533-2025 artfynd.xlsx
+++ b/artfynd/A 43533-2025 artfynd.xlsx
@@ -1185,7 +1185,7 @@
         <v>129127182</v>
       </c>
       <c r="B6" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>129131350</v>
       </c>
       <c r="B7" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         <v>129127736</v>
       </c>
       <c r="B12" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
         <v>129124933</v>
       </c>
       <c r="B29" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -5652,7 +5652,7 @@
         <v>129193543</v>
       </c>
       <c r="B40" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5851,7 +5851,7 @@
         <v>129193518</v>
       </c>
       <c r="B42" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6266,7 +6266,7 @@
         <v>129193542</v>
       </c>
       <c r="B46" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6875,7 +6875,7 @@
         <v>129193523</v>
       </c>
       <c r="B52" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         <v>129193517</v>
       </c>
       <c r="B53" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7392,7 +7392,7 @@
         <v>129193524</v>
       </c>
       <c r="B57" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7494,7 +7494,7 @@
         <v>129193544</v>
       </c>
       <c r="B58" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -8487,7 +8487,7 @@
         <v>129193545</v>
       </c>
       <c r="B68" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -9328,7 +9328,7 @@
         <v>129193546</v>
       </c>
       <c r="B76" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 43533-2025 artfynd.xlsx
+++ b/artfynd/A 43533-2025 artfynd.xlsx
@@ -1185,7 +1185,7 @@
         <v>129127182</v>
       </c>
       <c r="B6" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>129131350</v>
       </c>
       <c r="B7" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         <v>129127736</v>
       </c>
       <c r="B12" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
         <v>129124933</v>
       </c>
       <c r="B29" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -5652,7 +5652,7 @@
         <v>129193543</v>
       </c>
       <c r="B40" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5851,7 +5851,7 @@
         <v>129193518</v>
       </c>
       <c r="B42" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6266,7 +6266,7 @@
         <v>129193542</v>
       </c>
       <c r="B46" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6875,7 +6875,7 @@
         <v>129193523</v>
       </c>
       <c r="B52" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         <v>129193517</v>
       </c>
       <c r="B53" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7392,7 +7392,7 @@
         <v>129193524</v>
       </c>
       <c r="B57" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7494,7 +7494,7 @@
         <v>129193544</v>
       </c>
       <c r="B58" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -8487,7 +8487,7 @@
         <v>129193545</v>
       </c>
       <c r="B68" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -9328,7 +9328,7 @@
         <v>129193546</v>
       </c>
       <c r="B76" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 43533-2025 artfynd.xlsx
+++ b/artfynd/A 43533-2025 artfynd.xlsx
@@ -1185,7 +1185,7 @@
         <v>129127182</v>
       </c>
       <c r="B6" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>129131350</v>
       </c>
       <c r="B7" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         <v>129127736</v>
       </c>
       <c r="B12" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
         <v>129124933</v>
       </c>
       <c r="B29" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -5652,7 +5652,7 @@
         <v>129193543</v>
       </c>
       <c r="B40" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5851,7 +5851,7 @@
         <v>129193518</v>
       </c>
       <c r="B42" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6266,7 +6266,7 @@
         <v>129193542</v>
       </c>
       <c r="B46" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6875,7 +6875,7 @@
         <v>129193523</v>
       </c>
       <c r="B52" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         <v>129193517</v>
       </c>
       <c r="B53" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7392,7 +7392,7 @@
         <v>129193524</v>
       </c>
       <c r="B57" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7494,7 +7494,7 @@
         <v>129193544</v>
       </c>
       <c r="B58" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -8487,7 +8487,7 @@
         <v>129193545</v>
       </c>
       <c r="B68" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -9328,7 +9328,7 @@
         <v>129193546</v>
       </c>
       <c r="B76" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 43533-2025 artfynd.xlsx
+++ b/artfynd/A 43533-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY76"/>
+  <dimension ref="A1:AY77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129135545</v>
+        <v>129127509</v>
       </c>
       <c r="B2" t="n">
-        <v>98756</v>
+        <v>92509</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,36 +686,36 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>760</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>520564</v>
+        <v>520242</v>
       </c>
       <c r="R2" t="n">
-        <v>7001441</v>
+        <v>7001434</v>
       </c>
       <c r="S2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -783,7 +783,27 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Salix caprea</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -801,38 +821,38 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129135852</v>
+        <v>129128128</v>
       </c>
       <c r="B3" t="n">
-        <v>99090</v>
+        <v>80433</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219880</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>gulnande löv/blad</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -841,10 +861,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>520213</v>
+        <v>520340</v>
       </c>
       <c r="R3" t="n">
-        <v>7001609</v>
+        <v>7001392</v>
       </c>
       <c r="S3" t="n">
         <v>9</v>
@@ -876,7 +896,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +906,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,6 +921,26 @@
       <c r="AH3" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -918,10 +958,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129126527</v>
+        <v>129128148</v>
       </c>
       <c r="B4" t="n">
-        <v>80175</v>
+        <v>80433</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -929,21 +969,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -958,13 +998,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>520189</v>
+        <v>520338</v>
       </c>
       <c r="R4" t="n">
-        <v>7001448</v>
+        <v>7001407</v>
       </c>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -993,7 +1033,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,12 +1043,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:12</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1022,27 +1057,27 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark of dead wood # Betula</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1060,10 +1095,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129131270</v>
+        <v>129193549</v>
       </c>
       <c r="B5" t="n">
-        <v>79070</v>
+        <v>80433</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,37 +1106,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kajsadalen, Kajsadalen, Jmt</t>
+          <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>520497</v>
+        <v>520345</v>
       </c>
       <c r="R5" t="n">
-        <v>7001281</v>
+        <v>7001396</v>
       </c>
       <c r="S5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1128,21 +1163,11 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>14:41</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>14:41</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1151,89 +1176,64 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129127182</v>
+        <v>129193548</v>
       </c>
       <c r="B6" t="n">
-        <v>57740</v>
+        <v>92869</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>4769</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kajsadalen, Kajsadalen, Jmt</t>
+          <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>520186</v>
+        <v>520063</v>
       </c>
       <c r="R6" t="n">
-        <v>7001459</v>
+        <v>7001569</v>
       </c>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1260,26 +1260,11 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>11:39</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>11:39</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen av en gran  intill en gammal sälg.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1288,51 +1273,26 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129131350</v>
+        <v>129193591</v>
       </c>
       <c r="B7" t="n">
-        <v>57740</v>
+        <v>93233</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1340,47 +1300,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5964</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kajsadalen, Kajsadalen, Jmt</t>
+          <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>520520</v>
+        <v>520063</v>
       </c>
       <c r="R7" t="n">
-        <v>7001311</v>
+        <v>7001567</v>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1407,26 +1357,11 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>14:49</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>14:49</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack, enstaka färska och rikligt med äldre på en tall.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1435,51 +1370,26 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129126843</v>
+        <v>129125122</v>
       </c>
       <c r="B8" t="n">
-        <v>98756</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1487,56 +1397,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>520211</v>
+        <v>519973</v>
       </c>
       <c r="R8" t="n">
-        <v>7001475</v>
+        <v>7001540</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1563,26 +1454,11 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>11:27</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>11:27</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Minst 100 plantor inom ca 0,5 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1591,11 +1467,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1612,53 +1483,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129135692</v>
+        <v>129126187</v>
       </c>
       <c r="B9" t="n">
-        <v>80175</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>520343</v>
+        <v>520022</v>
       </c>
       <c r="R9" t="n">
-        <v>7001533</v>
+        <v>7001485</v>
       </c>
       <c r="S9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1687,7 +1553,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1697,7 +1563,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1716,22 +1582,22 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1749,53 +1615,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129135867</v>
+        <v>129126703</v>
       </c>
       <c r="B10" t="n">
-        <v>100945</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>520192</v>
+        <v>520253</v>
       </c>
       <c r="R10" t="n">
-        <v>7001635</v>
+        <v>7001454</v>
       </c>
       <c r="S10" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1822,11 +1683,21 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1835,6 +1706,31 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1854,11 +1750,11 @@
         <v>129128175</v>
       </c>
       <c r="B11" t="n">
-        <v>79070</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1973,53 +1869,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129127736</v>
+        <v>129128345</v>
       </c>
       <c r="B12" t="n">
-        <v>57740</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>520237</v>
+        <v>520362</v>
       </c>
       <c r="R12" t="n">
-        <v>7001416</v>
+        <v>7001381</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2048,7 +1939,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2058,12 +1949,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2077,7 +1968,7 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -2092,12 +1983,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2115,53 +2006,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129126617</v>
+        <v>129131270</v>
       </c>
       <c r="B13" t="n">
-        <v>80175</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>520219</v>
+        <v>520497</v>
       </c>
       <c r="R13" t="n">
-        <v>7001429</v>
+        <v>7001281</v>
       </c>
       <c r="S13" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2190,7 +2076,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2200,7 +2086,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2214,17 +2100,17 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2242,53 +2128,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129126547</v>
+        <v>129131389</v>
       </c>
       <c r="B14" t="n">
-        <v>80175</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>520206</v>
+        <v>520611</v>
       </c>
       <c r="R14" t="n">
-        <v>7001461</v>
+        <v>7001285</v>
       </c>
       <c r="S14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2317,7 +2198,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2327,7 +2208,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2338,31 +2219,6 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2379,59 +2235,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129135822</v>
+        <v>129131418</v>
       </c>
       <c r="B15" t="n">
-        <v>104227</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222412</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>bladfällning, vissnar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>520219</v>
+        <v>520682</v>
       </c>
       <c r="R15" t="n">
-        <v>7001610</v>
+        <v>7001354</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2463,7 +2305,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2473,7 +2315,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2488,6 +2330,26 @@
       <c r="AH15" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2505,53 +2367,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129128148</v>
+        <v>129131479</v>
       </c>
       <c r="B16" t="n">
-        <v>80176</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>520338</v>
+        <v>520712</v>
       </c>
       <c r="R16" t="n">
-        <v>7001407</v>
+        <v>7001363</v>
       </c>
       <c r="S16" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2580,7 +2437,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2590,7 +2447,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2609,22 +2466,22 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Betula</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2642,53 +2499,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129127604</v>
+        <v>129135677</v>
       </c>
       <c r="B17" t="n">
-        <v>80175</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>520243</v>
+        <v>520346</v>
       </c>
       <c r="R17" t="n">
-        <v>7001423</v>
+        <v>7001536</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2717,7 +2569,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2727,12 +2579,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:59</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Fertil lunglav på en sälg med doftticka.</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2743,31 +2590,6 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2784,53 +2606,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129128162</v>
+        <v>129136001</v>
       </c>
       <c r="B18" t="n">
-        <v>80175</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>520355</v>
+        <v>520012</v>
       </c>
       <c r="R18" t="n">
-        <v>7001412</v>
+        <v>7001652</v>
       </c>
       <c r="S18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2859,7 +2676,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2869,7 +2686,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2880,31 +2697,6 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2921,14 +2713,14 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129131389</v>
+        <v>129193590</v>
       </c>
       <c r="B19" t="n">
-        <v>79070</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2952,17 +2744,17 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kajsadalen, Kajsadalen, Jmt</t>
+          <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>520611</v>
+        <v>520187</v>
       </c>
       <c r="R19" t="n">
-        <v>7001285</v>
+        <v>7001471</v>
       </c>
       <c r="S19" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2989,19 +2781,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>14:53</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>14:53</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3016,59 +2798,50 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129127509</v>
+        <v>129125106</v>
       </c>
       <c r="B20" t="n">
-        <v>92176</v>
+        <v>80432</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -3077,13 +2850,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>520242</v>
+        <v>519989</v>
       </c>
       <c r="R20" t="n">
-        <v>7001434</v>
+        <v>7001538</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3112,7 +2885,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3122,7 +2895,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3134,11 +2907,6 @@
       <c r="AG20" t="b">
         <v>0</v>
       </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AJ20" t="inlineStr">
         <is>
           <t>sälg</t>
@@ -3149,14 +2917,9 @@
           <t>Salix caprea</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Stem on living tree # Salix caprea</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3174,10 +2937,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129125122</v>
+        <v>129126527</v>
       </c>
       <c r="B21" t="n">
-        <v>79070</v>
+        <v>80432</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3185,37 +2948,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>519973</v>
+        <v>520189</v>
       </c>
       <c r="R21" t="n">
-        <v>7001540</v>
+        <v>7001448</v>
       </c>
       <c r="S21" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3242,11 +3010,26 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3255,6 +3038,31 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3271,10 +3079,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129126633</v>
+        <v>129126547</v>
       </c>
       <c r="B22" t="n">
-        <v>80175</v>
+        <v>80432</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3300,19 +3108,24 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>520226</v>
+        <v>520206</v>
       </c>
       <c r="R22" t="n">
-        <v>7001438</v>
+        <v>7001461</v>
       </c>
       <c r="S22" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3341,7 +3154,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3351,12 +3164,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:19</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>På grovbarkad gammal asp.</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3408,10 +3216,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129128128</v>
+        <v>129126617</v>
       </c>
       <c r="B23" t="n">
-        <v>80176</v>
+        <v>80432</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3419,21 +3227,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3448,13 +3256,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>520340</v>
+        <v>520219</v>
       </c>
       <c r="R23" t="n">
-        <v>7001392</v>
+        <v>7001429</v>
       </c>
       <c r="S23" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3483,7 +3291,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3493,7 +3301,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3505,11 +3313,6 @@
       <c r="AG23" t="b">
         <v>0</v>
       </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
       <c r="AJ23" t="inlineStr">
         <is>
           <t>sälg</t>
@@ -3520,14 +3323,9 @@
           <t>Salix caprea</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3545,10 +3343,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129136001</v>
+        <v>129126633</v>
       </c>
       <c r="B24" t="n">
-        <v>79070</v>
+        <v>80432</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3556,21 +3354,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3580,13 +3378,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>520012</v>
+        <v>520226</v>
       </c>
       <c r="R24" t="n">
-        <v>7001652</v>
+        <v>7001438</v>
       </c>
       <c r="S24" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3615,7 +3413,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3625,7 +3423,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>På grovbarkad gammal asp.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3636,6 +3439,31 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3652,10 +3480,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129126703</v>
+        <v>129127211</v>
       </c>
       <c r="B25" t="n">
-        <v>79070</v>
+        <v>80432</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3663,37 +3491,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>520253</v>
+        <v>520158</v>
       </c>
       <c r="R25" t="n">
-        <v>7001454</v>
+        <v>7001448</v>
       </c>
       <c r="S25" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3722,7 +3555,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3732,7 +3565,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3751,22 +3584,22 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3784,10 +3617,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129131479</v>
+        <v>129127604</v>
       </c>
       <c r="B26" t="n">
-        <v>79070</v>
+        <v>80432</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3795,34 +3628,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>520712</v>
+        <v>520243</v>
       </c>
       <c r="R26" t="n">
-        <v>7001363</v>
+        <v>7001423</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3854,7 +3692,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3864,7 +3702,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Fertil lunglav på en sälg med doftticka.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3878,27 +3721,27 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3916,10 +3759,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129127211</v>
+        <v>129128023</v>
       </c>
       <c r="B27" t="n">
-        <v>80175</v>
+        <v>80432</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3956,13 +3799,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>520158</v>
+        <v>520326</v>
       </c>
       <c r="R27" t="n">
-        <v>7001448</v>
+        <v>7001449</v>
       </c>
       <c r="S27" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3991,7 +3834,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4001,7 +3844,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Rikligt med bålar på en rakväxt björk.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4020,12 +3868,12 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
@@ -4035,7 +3883,7 @@
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark on living woody plant # Betula</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4053,10 +3901,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129131418</v>
+        <v>129128162</v>
       </c>
       <c r="B28" t="n">
-        <v>79070</v>
+        <v>80432</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4064,37 +3912,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>520682</v>
+        <v>520355</v>
       </c>
       <c r="R28" t="n">
-        <v>7001354</v>
+        <v>7001412</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4123,7 +3976,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4133,7 +3986,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4152,22 +4005,22 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4185,10 +4038,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129124933</v>
+        <v>129135454</v>
       </c>
       <c r="B29" t="n">
-        <v>57740</v>
+        <v>80432</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4196,27 +4049,27 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -4225,13 +4078,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>519886</v>
+        <v>520630</v>
       </c>
       <c r="R29" t="n">
-        <v>7001592</v>
+        <v>7001400</v>
       </c>
       <c r="S29" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4260,7 +4113,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4270,12 +4123,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran i hyggeskanten.</t>
+          <t>På både gran och sälg.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4289,7 +4142,7 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
@@ -4304,12 +4157,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4327,52 +4180,38 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129127084</v>
+        <v>129135649</v>
       </c>
       <c r="B30" t="n">
-        <v>98756</v>
+        <v>80432</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4381,13 +4220,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>520203</v>
+        <v>520419</v>
       </c>
       <c r="R30" t="n">
-        <v>7001453</v>
+        <v>7001495</v>
       </c>
       <c r="S30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4416,7 +4255,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4426,7 +4265,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4440,7 +4279,27 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Betula</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4458,10 +4317,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129135649</v>
+        <v>129135692</v>
       </c>
       <c r="B31" t="n">
-        <v>80175</v>
+        <v>80432</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4498,13 +4357,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>520419</v>
+        <v>520343</v>
       </c>
       <c r="R31" t="n">
-        <v>7001495</v>
+        <v>7001533</v>
       </c>
       <c r="S31" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4533,7 +4392,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4543,7 +4402,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4562,12 +4421,12 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
@@ -4577,7 +4436,7 @@
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Betula</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4595,10 +4454,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129125106</v>
+        <v>129193550</v>
       </c>
       <c r="B32" t="n">
-        <v>80175</v>
+        <v>80432</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4624,24 +4483,19 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Kajsadalen, Kajsadalen, Jmt</t>
+          <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>519989</v>
+        <v>520344</v>
       </c>
       <c r="R32" t="n">
-        <v>7001538</v>
+        <v>7001502</v>
       </c>
       <c r="S32" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4668,21 +4522,11 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>09:48</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>09:48</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4691,41 +4535,26 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129128345</v>
+        <v>129193557</v>
       </c>
       <c r="B33" t="n">
-        <v>79070</v>
+        <v>80432</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4733,37 +4562,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Kajsadalen, Kajsadalen, Jmt</t>
+          <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>520362</v>
+        <v>520374</v>
       </c>
       <c r="R33" t="n">
-        <v>7001381</v>
+        <v>7001329</v>
       </c>
       <c r="S33" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4790,26 +4619,11 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>12:26</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>12:26</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4818,100 +4632,61 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129135770</v>
+        <v>129193558</v>
       </c>
       <c r="B34" t="n">
-        <v>98756</v>
+        <v>80432</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Kajsadalen, Kajsadalen, Jmt</t>
+          <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>520226</v>
+        <v>520415</v>
       </c>
       <c r="R34" t="n">
-        <v>7001601</v>
+        <v>7001416</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4941,26 +4716,11 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>18:11</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>18:11</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Minst 120 plantor inom ca 1 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4969,31 +4729,26 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129128023</v>
+        <v>129193559</v>
       </c>
       <c r="B35" t="n">
-        <v>80175</v>
+        <v>80432</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5019,21 +4774,16 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Kajsadalen, Kajsadalen, Jmt</t>
+          <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>520326</v>
+        <v>520330</v>
       </c>
       <c r="R35" t="n">
-        <v>7001449</v>
+        <v>7001396</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5063,26 +4813,11 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>12:09</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>12:09</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Rikligt med bålar på en rakväxt björk.</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -5091,51 +4826,26 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Betula</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129135454</v>
+        <v>129193560</v>
       </c>
       <c r="B36" t="n">
-        <v>80175</v>
+        <v>80432</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5161,21 +4871,16 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Kajsadalen, Kajsadalen, Jmt</t>
+          <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>520630</v>
+        <v>520346</v>
       </c>
       <c r="R36" t="n">
-        <v>7001400</v>
+        <v>7001396</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5205,26 +4910,11 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>17:51</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>17:51</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>På både gran och sälg.</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -5233,51 +4923,26 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129135677</v>
+        <v>129193561</v>
       </c>
       <c r="B37" t="n">
-        <v>79070</v>
+        <v>80432</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5285,37 +4950,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Kajsadalen, Kajsadalen, Jmt</t>
+          <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>520346</v>
+        <v>520344</v>
       </c>
       <c r="R37" t="n">
-        <v>7001536</v>
+        <v>7001402</v>
       </c>
       <c r="S37" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5342,19 +5007,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>18:05</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>18:05</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5369,74 +5024,60 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129128320</v>
+        <v>129193562</v>
       </c>
       <c r="B38" t="n">
-        <v>98756</v>
+        <v>80432</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Kajsadalen, Kajsadalen, Jmt</t>
+          <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>520352</v>
+        <v>520335</v>
       </c>
       <c r="R38" t="n">
-        <v>7001397</v>
+        <v>7001429</v>
       </c>
       <c r="S38" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5463,26 +5104,11 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>12:20</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>12:20</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Minst 10 plantor inom ca 0,5 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -5491,74 +5117,64 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129135697</v>
+        <v>129193563</v>
       </c>
       <c r="B39" t="n">
-        <v>80204</v>
+        <v>80432</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Kajsadalen, Kajsadalen, Jmt</t>
+          <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>520344</v>
+        <v>520326</v>
       </c>
       <c r="R39" t="n">
-        <v>7001538</v>
+        <v>7001451</v>
       </c>
       <c r="S39" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5585,21 +5201,11 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>18:07</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>18:07</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -5608,51 +5214,26 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129193543</v>
+        <v>129193564</v>
       </c>
       <c r="B40" t="n">
-        <v>57740</v>
+        <v>80432</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5660,21 +5241,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5684,10 +5265,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>520321</v>
+        <v>520225</v>
       </c>
       <c r="R40" t="n">
-        <v>7001391</v>
+        <v>7001483</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5720,11 +5301,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5751,10 +5327,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129193558</v>
+        <v>129193565</v>
       </c>
       <c r="B41" t="n">
-        <v>80175</v>
+        <v>80432</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5786,10 +5362,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>520415</v>
+        <v>520156</v>
       </c>
       <c r="R41" t="n">
-        <v>7001416</v>
+        <v>7001442</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5848,10 +5424,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129193518</v>
+        <v>129193566</v>
       </c>
       <c r="B42" t="n">
-        <v>57740</v>
+        <v>80432</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5859,21 +5435,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5883,10 +5459,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>520676</v>
+        <v>520180</v>
       </c>
       <c r="R42" t="n">
-        <v>7001377</v>
+        <v>7001458</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5919,11 +5495,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5950,10 +5521,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129193568</v>
+        <v>129193567</v>
       </c>
       <c r="B43" t="n">
-        <v>80175</v>
+        <v>80432</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5985,10 +5556,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>520159</v>
+        <v>520184</v>
       </c>
       <c r="R43" t="n">
-        <v>7001489</v>
+        <v>7001482</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6047,32 +5618,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129193576</v>
+        <v>129193568</v>
       </c>
       <c r="B44" t="n">
-        <v>98756</v>
+        <v>80432</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -6082,10 +5653,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>520675</v>
+        <v>520159</v>
       </c>
       <c r="R44" t="n">
-        <v>7001377</v>
+        <v>7001489</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6144,61 +5715,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129193582</v>
+        <v>129193569</v>
       </c>
       <c r="B45" t="n">
-        <v>98756</v>
+        <v>80432</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>520388</v>
+        <v>520094</v>
       </c>
       <c r="R45" t="n">
-        <v>7001418</v>
+        <v>7001525</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6233,18 +5788,12 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Minst 50</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -6263,10 +5812,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129193542</v>
+        <v>129193570</v>
       </c>
       <c r="B46" t="n">
-        <v>57740</v>
+        <v>80432</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6274,21 +5823,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -6298,10 +5847,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>520422</v>
+        <v>519997</v>
       </c>
       <c r="R46" t="n">
-        <v>7001418</v>
+        <v>7001586</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6334,11 +5883,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6365,64 +5909,53 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129193583</v>
+        <v>129135697</v>
       </c>
       <c r="B47" t="n">
-        <v>98756</v>
+        <v>80461</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Fisksjölandsbodarna, Jmt</t>
+          <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>520338</v>
+        <v>520344</v>
       </c>
       <c r="R47" t="n">
-        <v>7001427</v>
+        <v>7001538</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6449,14 +5982,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>18:07</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Minst 100</t>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6465,29 +6003,53 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129193565</v>
+        <v>129124933</v>
       </c>
       <c r="B48" t="n">
-        <v>80175</v>
+        <v>57953</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6495,37 +6057,42 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Fisksjölandsbodarna, Jmt</t>
+          <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>520156</v>
+        <v>519886</v>
       </c>
       <c r="R48" t="n">
-        <v>7001442</v>
+        <v>7001592</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6552,11 +6119,26 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>09:39</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>09:39</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran i hyggeskanten.</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -6565,64 +6147,99 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129193591</v>
+        <v>129127182</v>
       </c>
       <c r="B49" t="n">
-        <v>92899</v>
+        <v>57953</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5964</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Fisksjölandsbodarna, Jmt</t>
+          <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>520063</v>
+        <v>520186</v>
       </c>
       <c r="R49" t="n">
-        <v>7001567</v>
+        <v>7001459</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6649,11 +6266,26 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen av en gran  intill en gammal sälg.</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -6662,26 +6294,51 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129193566</v>
+        <v>129127736</v>
       </c>
       <c r="B50" t="n">
-        <v>80175</v>
+        <v>57953</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6689,34 +6346,39 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Fisksjölandsbodarna, Jmt</t>
+          <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>520180</v>
+        <v>520237</v>
       </c>
       <c r="R50" t="n">
-        <v>7001458</v>
+        <v>7001416</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6746,11 +6408,26 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -6759,26 +6436,51 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129193590</v>
+        <v>129131350</v>
       </c>
       <c r="B51" t="n">
-        <v>79070</v>
+        <v>57953</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6786,37 +6488,47 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Fisksjölandsbodarna, Jmt</t>
+          <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>520187</v>
+        <v>520520</v>
       </c>
       <c r="R51" t="n">
-        <v>7001471</v>
+        <v>7001311</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6843,11 +6555,26 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack, enstaka färska och rikligt med äldre på en tall.</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -6856,26 +6583,51 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129193523</v>
+        <v>129193517</v>
       </c>
       <c r="B52" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6907,10 +6659,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>520478</v>
+        <v>520301</v>
       </c>
       <c r="R52" t="n">
-        <v>7001335</v>
+        <v>7001547</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6947,7 +6699,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6974,10 +6726,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129193517</v>
+        <v>129193518</v>
       </c>
       <c r="B53" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7009,10 +6761,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>520301</v>
+        <v>520676</v>
       </c>
       <c r="R53" t="n">
-        <v>7001547</v>
+        <v>7001377</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7049,7 +6801,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7076,61 +6828,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129193581</v>
+        <v>129193523</v>
       </c>
       <c r="B54" t="n">
-        <v>98756</v>
+        <v>57953</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>520425</v>
+        <v>520478</v>
       </c>
       <c r="R54" t="n">
-        <v>7001407</v>
+        <v>7001335</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7167,7 +6903,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Minst 80</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7176,7 +6912,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -7195,10 +6930,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129193570</v>
+        <v>129193524</v>
       </c>
       <c r="B55" t="n">
-        <v>80175</v>
+        <v>57953</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7206,21 +6941,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -7230,10 +6965,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>519997</v>
+        <v>520478</v>
       </c>
       <c r="R55" t="n">
-        <v>7001586</v>
+        <v>7001328</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7266,6 +7001,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7292,10 +7032,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129193550</v>
+        <v>129193542</v>
       </c>
       <c r="B56" t="n">
-        <v>80175</v>
+        <v>57953</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7303,21 +7043,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7327,10 +7067,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>520344</v>
+        <v>520422</v>
       </c>
       <c r="R56" t="n">
-        <v>7001502</v>
+        <v>7001418</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7363,6 +7103,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7389,10 +7134,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129193524</v>
+        <v>129193543</v>
       </c>
       <c r="B57" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7424,10 +7169,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>520478</v>
+        <v>520321</v>
       </c>
       <c r="R57" t="n">
-        <v>7001328</v>
+        <v>7001391</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7464,7 +7209,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7494,7 +7239,7 @@
         <v>129193544</v>
       </c>
       <c r="B58" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7593,10 +7338,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129193561</v>
+        <v>129193545</v>
       </c>
       <c r="B59" t="n">
-        <v>80175</v>
+        <v>57953</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7604,21 +7349,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7628,10 +7373,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>520344</v>
+        <v>519958</v>
       </c>
       <c r="R59" t="n">
-        <v>7001402</v>
+        <v>7001547</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7664,6 +7409,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7690,10 +7440,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129193567</v>
+        <v>129193546</v>
       </c>
       <c r="B60" t="n">
-        <v>80175</v>
+        <v>57953</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7701,21 +7451,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7725,10 +7475,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>520184</v>
+        <v>519958</v>
       </c>
       <c r="R60" t="n">
-        <v>7001482</v>
+        <v>7001542</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7761,6 +7511,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7787,10 +7542,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129193564</v>
+        <v>129193573</v>
       </c>
       <c r="B61" t="n">
-        <v>80175</v>
+        <v>58057</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7798,34 +7553,50 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>103031</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>520225</v>
+        <v>520153</v>
       </c>
       <c r="R61" t="n">
-        <v>7001483</v>
+        <v>7001500</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7884,48 +7655,53 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129193557</v>
+        <v>129135852</v>
       </c>
       <c r="B62" t="n">
-        <v>80175</v>
+        <v>99456</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>219880</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>gulnande löv/blad</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Fisksjölandsbodarna, Jmt</t>
+          <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>520374</v>
+        <v>520213</v>
       </c>
       <c r="R62" t="n">
-        <v>7001329</v>
+        <v>7001609</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7952,11 +7728,21 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>18:18</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>18:18</t>
+        </is>
+      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
@@ -7965,26 +7751,31 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129193585</v>
+        <v>129126843</v>
       </c>
       <c r="B63" t="n">
-        <v>98756</v>
+        <v>99118</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8011,7 +7802,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -8019,19 +7810,26 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Fisksjölandsbodarna, Jmt</t>
+          <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>520122</v>
+        <v>520211</v>
       </c>
       <c r="R63" t="n">
-        <v>7001476</v>
+        <v>7001475</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8061,14 +7859,24 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Fler än 200</t>
+          <t>Minst 100 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8077,67 +7885,90 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
+      </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129193560</v>
+        <v>129127084</v>
       </c>
       <c r="B64" t="n">
-        <v>80175</v>
+        <v>99118</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Fisksjölandsbodarna, Jmt</t>
+          <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>520346</v>
+        <v>520203</v>
       </c>
       <c r="R64" t="n">
-        <v>7001396</v>
+        <v>7001453</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8164,11 +7995,21 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
@@ -8177,64 +8018,83 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
+      </c>
+      <c r="AH64" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129193569</v>
+        <v>129128320</v>
       </c>
       <c r="B65" t="n">
-        <v>80175</v>
+        <v>99118</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Fisksjölandsbodarna, Jmt</t>
+          <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>520094</v>
+        <v>520352</v>
       </c>
       <c r="R65" t="n">
-        <v>7001525</v>
+        <v>7001397</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8261,11 +8121,26 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Minst 10 plantor inom ca 0,5 m2 yta.</t>
+        </is>
+      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
@@ -8274,64 +8149,83 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129193593</v>
+        <v>129135545</v>
       </c>
       <c r="B66" t="n">
-        <v>100945</v>
+        <v>99118</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Fisksjölandsbodarna, Jmt</t>
+          <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>520101</v>
+        <v>520564</v>
       </c>
       <c r="R66" t="n">
-        <v>7001658</v>
+        <v>7001441</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8358,11 +8252,21 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>17:54</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>17:54</t>
+        </is>
+      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
@@ -8371,61 +8275,80 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129193562</v>
+        <v>129135770</v>
       </c>
       <c r="B67" t="n">
-        <v>80175</v>
+        <v>99118</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Fisksjölandsbodarna, Jmt</t>
+          <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>520335</v>
+        <v>520226</v>
       </c>
       <c r="R67" t="n">
-        <v>7001429</v>
+        <v>7001601</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8455,11 +8378,26 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>18:11</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>18:11</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Minst 120 plantor inom ca 1 m2 yta.</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -8468,61 +8406,82 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129193545</v>
+        <v>129193575</v>
       </c>
       <c r="B68" t="n">
-        <v>57740</v>
+        <v>99118</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>519958</v>
+        <v>520528</v>
       </c>
       <c r="R68" t="n">
-        <v>7001547</v>
+        <v>7001465</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8559,7 +8518,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Minst 50</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8568,6 +8527,7 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -8586,61 +8546,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129193573</v>
+        <v>129193576</v>
       </c>
       <c r="B69" t="n">
-        <v>57834</v>
+        <v>99118</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>103031</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>520153</v>
+        <v>520675</v>
       </c>
       <c r="R69" t="n">
-        <v>7001500</v>
+        <v>7001377</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8699,10 +8643,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129193584</v>
+        <v>129193581</v>
       </c>
       <c r="B70" t="n">
-        <v>98756</v>
+        <v>99118</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8729,7 +8673,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -8750,10 +8694,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>520320</v>
+        <v>520425</v>
       </c>
       <c r="R70" t="n">
-        <v>7001451</v>
+        <v>7001407</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8790,7 +8734,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Minst 100</t>
+          <t>Minst 80</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8818,45 +8762,61 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129193563</v>
+        <v>129193582</v>
       </c>
       <c r="B71" t="n">
-        <v>80175</v>
+        <v>99118</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>520326</v>
+        <v>520388</v>
       </c>
       <c r="R71" t="n">
-        <v>7001451</v>
+        <v>7001418</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8891,12 +8851,18 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Minst 50</t>
+        </is>
+      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -8915,45 +8881,61 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129193548</v>
+        <v>129193583</v>
       </c>
       <c r="B72" t="n">
-        <v>92536</v>
+        <v>99118</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4769</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>520063</v>
+        <v>520338</v>
       </c>
       <c r="R72" t="n">
-        <v>7001569</v>
+        <v>7001427</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8988,12 +8970,18 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Minst 100</t>
+        </is>
+      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -9012,45 +9000,61 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129193559</v>
+        <v>129193584</v>
       </c>
       <c r="B73" t="n">
-        <v>80175</v>
+        <v>99118</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>520330</v>
+        <v>520320</v>
       </c>
       <c r="R73" t="n">
-        <v>7001396</v>
+        <v>7001451</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9085,12 +9089,18 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Minst 100</t>
+        </is>
+      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -9109,10 +9119,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129193575</v>
+        <v>129193585</v>
       </c>
       <c r="B74" t="n">
-        <v>98756</v>
+        <v>99118</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9139,7 +9149,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -9149,21 +9159,17 @@
       </c>
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
-      <c r="N74" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>520528</v>
+        <v>520122</v>
       </c>
       <c r="R74" t="n">
-        <v>7001465</v>
+        <v>7001476</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9200,7 +9206,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Minst 50</t>
+          <t>Fler än 200</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9228,45 +9234,59 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129193549</v>
+        <v>129135822</v>
       </c>
       <c r="B75" t="n">
-        <v>80176</v>
+        <v>104627</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2081</v>
+        <v>222412</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>bladfällning, vissnar</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Fisksjölandsbodarna, Jmt</t>
+          <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>520345</v>
+        <v>520219</v>
       </c>
       <c r="R75" t="n">
-        <v>7001396</v>
+        <v>7001610</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9296,11 +9316,21 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>18:16</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>18:16</t>
+        </is>
+      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
@@ -9309,64 +9339,74 @@
       </c>
       <c r="AG75" t="b">
         <v>0</v>
+      </c>
+      <c r="AH75" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129193546</v>
+        <v>129135867</v>
       </c>
       <c r="B76" t="n">
-        <v>57740</v>
+        <v>101325</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Fisksjölandsbodarna, Jmt</t>
+          <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>519958</v>
+        <v>520192</v>
       </c>
       <c r="R76" t="n">
-        <v>7001542</v>
+        <v>7001635</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9396,11 +9436,6 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9415,15 +9450,112 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>129193593</v>
+      </c>
+      <c r="B77" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Fisksjölandsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>520101</v>
+      </c>
+      <c r="R77" t="n">
+        <v>7001658</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
           <t>Benny Öwre</t>
         </is>
       </c>
-      <c r="AX76" t="inlineStr">
+      <c r="AX77" t="inlineStr">
         <is>
           <t>Benny Öwre</t>
         </is>
       </c>
-      <c r="AY76" t="inlineStr"/>
+      <c r="AY77" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 43533-2025 artfynd.xlsx
+++ b/artfynd/A 43533-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY77"/>
+  <dimension ref="A1:AZ77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -818,6 +823,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129127509</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -955,6 +965,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129128128</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1092,6 +1107,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129128148</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1189,6 +1209,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129193549</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1286,6 +1311,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129193548</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1383,6 +1413,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129193591</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1480,6 +1515,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129125122</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1612,6 +1652,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129126187</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1744,6 +1789,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129126703</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1866,6 +1916,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129128175</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2003,6 +2058,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129128345</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2125,6 +2185,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129131270</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2232,6 +2297,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129131389</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2364,6 +2434,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129131418</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2496,6 +2571,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129131479</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2603,6 +2683,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129135677</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2710,6 +2795,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129136001</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2807,6 +2897,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129193590</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2934,6 +3029,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129125106</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3076,6 +3176,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129126527</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3213,6 +3318,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129126547</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3340,6 +3450,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129126617</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3477,6 +3592,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129126633</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3614,6 +3734,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129127211</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3756,6 +3881,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129127604</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3898,6 +4028,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129128023</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -4035,6 +4170,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129128162</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4177,6 +4317,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129135454</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4314,6 +4459,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129135649</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4451,6 +4601,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129135692</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4548,6 +4703,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129193550</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4645,6 +4805,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129193557</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4742,6 +4907,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129193558</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4839,6 +5009,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129193559</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4936,6 +5111,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129193560</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -5033,6 +5213,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129193561</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5130,6 +5315,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129193562</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5227,6 +5417,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129193563</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5324,6 +5519,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129193564</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5421,6 +5621,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129193565</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5518,6 +5723,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129193566</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5615,6 +5825,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129193567</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5712,6 +5927,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129193568</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5809,6 +6029,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129193569</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5906,6 +6131,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129193570</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -6043,6 +6273,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129135697</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6185,6 +6420,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129124933</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6332,6 +6572,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129127182</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6474,6 +6719,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129127736</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6621,6 +6871,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129131350</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6723,6 +6978,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129193517</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6825,6 +7085,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129193518</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6927,6 +7192,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129193523</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -7029,6 +7299,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129193524</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -7131,6 +7406,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129193542</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7233,6 +7513,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129193543</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7335,6 +7620,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129193544</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7437,6 +7727,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129193545</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7539,6 +7834,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129193546</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7652,6 +7952,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129193573</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7769,6 +8074,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129135852</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7905,6 +8215,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129126843</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -8036,6 +8351,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129127084</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -8167,6 +8487,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129128320</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -8293,6 +8618,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129135545</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8424,6 +8754,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129135770</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8543,6 +8878,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129193575</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8640,6 +8980,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129193576</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8759,6 +9104,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129193581</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8878,6 +9228,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129193582</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8997,6 +9352,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129193583</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -9116,6 +9476,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129193584</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -9231,6 +9596,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129193585</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -9357,6 +9727,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129135822</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -9459,6 +9834,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129135867</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9556,8 +9936,91 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129193593</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>